--- a/salidas/empresas/MET.xlsx
+++ b/salidas/empresas/MET.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mensual" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="EPS" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Acciones" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Info" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Mensual" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="EPS" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Acciones" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Info" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -23,13 +23,16 @@
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD"/>
   </numFmts>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -40,7 +43,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -48,12 +51,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -435,58 +447,58 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>fecha</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>precio_ajustado</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>precio_cierre</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>volumen</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>eps_ttm</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>pe</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>acciones_circulacion</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>market_cap</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>rotacion</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" s="2" t="n">
         <v>38748</v>
       </c>
       <c r="B2" t="n">
-        <v>25.42773246765137</v>
+        <v>25.4277400970459</v>
       </c>
       <c r="C2" t="n">
         <v>44.70588302612305</v>
@@ -501,7 +513,7 @@
       <c r="I2" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" s="2" t="n">
         <v>38776</v>
       </c>
       <c r="B3" t="n">
@@ -520,11 +532,11 @@
       <c r="I3" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" s="2" t="n">
         <v>38807</v>
       </c>
       <c r="B4" t="n">
-        <v>24.52032470703125</v>
+        <v>24.52032089233398</v>
       </c>
       <c r="C4" t="n">
         <v>43.11051559448242</v>
@@ -539,11 +551,11 @@
       <c r="I4" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" s="2" t="n">
         <v>38837</v>
       </c>
       <c r="B5" t="n">
-        <v>26.41118240356445</v>
+        <v>26.41117668151855</v>
       </c>
       <c r="C5" t="n">
         <v>46.4349365234375</v>
@@ -558,11 +570,11 @@
       <c r="I5" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" s="2" t="n">
         <v>38868</v>
       </c>
       <c r="B6" t="n">
-        <v>26.09180641174316</v>
+        <v>26.09181976318359</v>
       </c>
       <c r="C6" t="n">
         <v>45.87343978881836</v>
@@ -577,11 +589,11 @@
       <c r="I6" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="A7" s="2" t="n">
         <v>38898</v>
       </c>
       <c r="B7" t="n">
-        <v>25.96000671386719</v>
+        <v>25.96001434326172</v>
       </c>
       <c r="C7" t="n">
         <v>45.6417121887207</v>
@@ -596,11 +608,11 @@
       <c r="I7" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="A8" s="2" t="n">
         <v>38929</v>
       </c>
       <c r="B8" t="n">
-        <v>26.36049652099609</v>
+        <v>26.3604907989502</v>
       </c>
       <c r="C8" t="n">
         <v>46.34580993652344</v>
@@ -615,11 +627,11 @@
       <c r="I8" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
+      <c r="A9" s="2" t="n">
         <v>38960</v>
       </c>
       <c r="B9" t="n">
-        <v>27.8964900970459</v>
+        <v>27.89649200439453</v>
       </c>
       <c r="C9" t="n">
         <v>49.04634475708008</v>
@@ -634,7 +646,7 @@
       <c r="I9" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
+      <c r="A10" s="2" t="n">
         <v>38990</v>
       </c>
       <c r="B10" t="n">
@@ -653,11 +665,11 @@
       <c r="I10" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
+      <c r="A11" s="2" t="n">
         <v>39021</v>
       </c>
       <c r="B11" t="n">
-        <v>28.96105194091797</v>
+        <v>28.9610481262207</v>
       </c>
       <c r="C11" t="n">
         <v>50.91800308227539</v>
@@ -672,11 +684,11 @@
       <c r="I11" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
+      <c r="A12" s="2" t="n">
         <v>39051</v>
       </c>
       <c r="B12" t="n">
-        <v>30.08024787902832</v>
+        <v>30.08026695251465</v>
       </c>
       <c r="C12" t="n">
         <v>52.34402847290039</v>
@@ -691,11 +703,11 @@
       <c r="I12" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n">
+      <c r="A13" s="2" t="n">
         <v>39082</v>
       </c>
       <c r="B13" t="n">
-        <v>30.22367286682129</v>
+        <v>30.22367858886719</v>
       </c>
       <c r="C13" t="n">
         <v>52.59358215332031</v>
@@ -710,7 +722,7 @@
       <c r="I13" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n">
+      <c r="A14" s="2" t="n">
         <v>39113</v>
       </c>
       <c r="B14" t="n">
@@ -729,11 +741,11 @@
       <c r="I14" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n">
+      <c r="A15" s="2" t="n">
         <v>39141</v>
       </c>
       <c r="B15" t="n">
-        <v>32.34920501708984</v>
+        <v>32.34921264648438</v>
       </c>
       <c r="C15" t="n">
         <v>56.29233551025391</v>
@@ -748,11 +760,11 @@
       <c r="I15" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n">
+      <c r="A16" s="2" t="n">
         <v>39172</v>
       </c>
       <c r="B16" t="n">
-        <v>32.34409332275391</v>
+        <v>32.34409713745117</v>
       </c>
       <c r="C16" t="n">
         <v>56.28342056274414</v>
@@ -767,11 +779,11 @@
       <c r="I16" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n">
+      <c r="A17" s="2" t="n">
         <v>39202</v>
       </c>
       <c r="B17" t="n">
-        <v>33.650146484375</v>
+        <v>33.65014266967773</v>
       </c>
       <c r="C17" t="n">
         <v>58.55614852905273</v>
@@ -786,7 +798,7 @@
       <c r="I17" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="n">
+      <c r="A18" s="2" t="n">
         <v>39233</v>
       </c>
       <c r="B18" t="n">
@@ -805,11 +817,11 @@
       <c r="I18" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="n">
+      <c r="A19" s="2" t="n">
         <v>39263</v>
       </c>
       <c r="B19" t="n">
-        <v>33.02529907226562</v>
+        <v>33.02528381347656</v>
       </c>
       <c r="C19" t="n">
         <v>57.46880722045898</v>
@@ -824,11 +836,11 @@
       <c r="I19" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="n">
+      <c r="A20" s="2" t="n">
         <v>39294</v>
       </c>
       <c r="B20" t="n">
-        <v>30.84340476989746</v>
+        <v>30.84339904785156</v>
       </c>
       <c r="C20" t="n">
         <v>53.67201232910156</v>
@@ -843,11 +855,11 @@
       <c r="I20" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="n">
+      <c r="A21" s="2" t="n">
         <v>39325</v>
       </c>
       <c r="B21" t="n">
-        <v>32.80505752563477</v>
+        <v>32.80504989624023</v>
       </c>
       <c r="C21" t="n">
         <v>57.0855598449707</v>
@@ -862,11 +874,11 @@
       <c r="I21" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="n">
+      <c r="A22" s="2" t="n">
         <v>39355</v>
       </c>
       <c r="B22" t="n">
-        <v>35.71422576904297</v>
+        <v>35.71421432495117</v>
       </c>
       <c r="C22" t="n">
         <v>62.14794921875</v>
@@ -881,7 +893,7 @@
       <c r="I22" t="inlineStr"/>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="n">
+      <c r="A23" s="2" t="n">
         <v>39386</v>
       </c>
       <c r="B23" t="n">
@@ -900,11 +912,11 @@
       <c r="I23" t="inlineStr"/>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="n">
+      <c r="A24" s="2" t="n">
         <v>39416</v>
       </c>
       <c r="B24" t="n">
-        <v>33.97748947143555</v>
+        <v>33.97749328613281</v>
       </c>
       <c r="C24" t="n">
         <v>58.45811080932617</v>
@@ -919,11 +931,11 @@
       <c r="I24" t="inlineStr"/>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="n">
+      <c r="A25" s="2" t="n">
         <v>39447</v>
       </c>
       <c r="B25" t="n">
-        <v>31.92092323303223</v>
+        <v>31.92091941833496</v>
       </c>
       <c r="C25" t="n">
         <v>54.91978454589844</v>
@@ -938,11 +950,11 @@
       <c r="I25" t="inlineStr"/>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="n">
+      <c r="A26" s="2" t="n">
         <v>39478</v>
       </c>
       <c r="B26" t="n">
-        <v>30.50151824951172</v>
+        <v>30.50153160095215</v>
       </c>
       <c r="C26" t="n">
         <v>52.47771835327148</v>
@@ -957,11 +969,11 @@
       <c r="I26" t="inlineStr"/>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="n">
+      <c r="A27" s="2" t="n">
         <v>39507</v>
       </c>
       <c r="B27" t="n">
-        <v>30.18034172058105</v>
+        <v>30.18034744262695</v>
       </c>
       <c r="C27" t="n">
         <v>51.92513275146484</v>
@@ -976,11 +988,11 @@
       <c r="I27" t="inlineStr"/>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="n">
+      <c r="A28" s="2" t="n">
         <v>39538</v>
       </c>
       <c r="B28" t="n">
-        <v>31.21640396118164</v>
+        <v>31.21640586853027</v>
       </c>
       <c r="C28" t="n">
         <v>53.70766448974609</v>
@@ -995,11 +1007,11 @@
       <c r="I28" t="inlineStr"/>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="n">
+      <c r="A29" s="2" t="n">
         <v>39568</v>
       </c>
       <c r="B29" t="n">
-        <v>31.52204513549805</v>
+        <v>31.52203941345215</v>
       </c>
       <c r="C29" t="n">
         <v>54.23351287841797</v>
@@ -1014,11 +1026,11 @@
       <c r="I29" t="inlineStr"/>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="n">
+      <c r="A30" s="2" t="n">
         <v>39599</v>
       </c>
       <c r="B30" t="n">
-        <v>31.09726524353027</v>
+        <v>31.09725952148438</v>
       </c>
       <c r="C30" t="n">
         <v>53.5026741027832</v>
@@ -1033,11 +1045,11 @@
       <c r="I30" t="inlineStr"/>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="n">
+      <c r="A31" s="2" t="n">
         <v>39629</v>
       </c>
       <c r="B31" t="n">
-        <v>27.33637237548828</v>
+        <v>27.33636474609375</v>
       </c>
       <c r="C31" t="n">
         <v>47.03208541870117</v>
@@ -1052,7 +1064,7 @@
       <c r="I31" t="inlineStr"/>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="n">
+      <c r="A32" s="2" t="n">
         <v>39660</v>
       </c>
       <c r="B32" t="n">
@@ -1071,11 +1083,11 @@
       <c r="I32" t="inlineStr"/>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="n">
+      <c r="A33" s="2" t="n">
         <v>39691</v>
       </c>
       <c r="B33" t="n">
-        <v>28.07714462280273</v>
+        <v>28.0771541595459</v>
       </c>
       <c r="C33" t="n">
         <v>48.30659484863281</v>
@@ -1090,11 +1102,11 @@
       <c r="I33" t="inlineStr"/>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="n">
+      <c r="A34" s="2" t="n">
         <v>39721</v>
       </c>
       <c r="B34" t="n">
-        <v>29.00959587097168</v>
+        <v>29.00959968566895</v>
       </c>
       <c r="C34" t="n">
         <v>49.91087341308594</v>
@@ -1109,11 +1121,11 @@
       <c r="I34" t="inlineStr"/>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="n">
+      <c r="A35" s="2" t="n">
         <v>39752</v>
       </c>
       <c r="B35" t="n">
-        <v>17.20891761779785</v>
+        <v>17.20891189575195</v>
       </c>
       <c r="C35" t="n">
         <v>29.60784339904785</v>
@@ -1128,11 +1140,11 @@
       <c r="I35" t="inlineStr"/>
     </row>
     <row r="36">
-      <c r="A36" s="1" t="n">
+      <c r="A36" s="2" t="n">
         <v>39782</v>
       </c>
       <c r="B36" t="n">
-        <v>15.21341419219971</v>
+        <v>15.21341133117676</v>
       </c>
       <c r="C36" t="n">
         <v>25.63279914855957</v>
@@ -1147,11 +1159,11 @@
       <c r="I36" t="inlineStr"/>
     </row>
     <row r="37">
-      <c r="A37" s="1" t="n">
+      <c r="A37" s="2" t="n">
         <v>39813</v>
       </c>
       <c r="B37" t="n">
-        <v>18.44018173217773</v>
+        <v>18.44017601013184</v>
       </c>
       <c r="C37" t="n">
         <v>31.06951904296875</v>
@@ -1166,11 +1178,11 @@
       <c r="I37" t="inlineStr"/>
     </row>
     <row r="38">
-      <c r="A38" s="1" t="n">
+      <c r="A38" s="2" t="n">
         <v>39844</v>
       </c>
       <c r="B38" t="n">
-        <v>15.19753742218018</v>
+        <v>15.19754791259766</v>
       </c>
       <c r="C38" t="n">
         <v>25.6060619354248</v>
@@ -1185,11 +1197,11 @@
       <c r="I38" t="inlineStr"/>
     </row>
     <row r="39">
-      <c r="A39" s="1" t="n">
+      <c r="A39" s="2" t="n">
         <v>39872</v>
       </c>
       <c r="B39" t="n">
-        <v>9.764933586120605</v>
+        <v>9.764934539794922</v>
       </c>
       <c r="C39" t="n">
         <v>16.45276260375977</v>
@@ -1204,11 +1216,11 @@
       <c r="I39" t="inlineStr"/>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="n">
+      <c r="A40" s="2" t="n">
         <v>39903</v>
       </c>
       <c r="B40" t="n">
-        <v>12.04483509063721</v>
+        <v>12.04483318328857</v>
       </c>
       <c r="C40" t="n">
         <v>20.29411888122559</v>
@@ -1223,11 +1235,11 @@
       <c r="I40" t="inlineStr"/>
     </row>
     <row r="41">
-      <c r="A41" s="1" t="n">
+      <c r="A41" s="2" t="n">
         <v>39933</v>
       </c>
       <c r="B41" t="n">
-        <v>15.73710536956787</v>
+        <v>15.73709774017334</v>
       </c>
       <c r="C41" t="n">
         <v>26.51515197753906</v>
@@ -1242,11 +1254,11 @@
       <c r="I41" t="inlineStr"/>
     </row>
     <row r="42">
-      <c r="A42" s="1" t="n">
+      <c r="A42" s="2" t="n">
         <v>39964</v>
       </c>
       <c r="B42" t="n">
-        <v>16.66280555725098</v>
+        <v>16.66281890869141</v>
       </c>
       <c r="C42" t="n">
         <v>28.07486534118652</v>
@@ -1261,11 +1273,11 @@
       <c r="I42" t="inlineStr"/>
     </row>
     <row r="43">
-      <c r="A43" s="1" t="n">
+      <c r="A43" s="2" t="n">
         <v>39994</v>
       </c>
       <c r="B43" t="n">
-        <v>15.87463092803955</v>
+        <v>15.87463283538818</v>
       </c>
       <c r="C43" t="n">
         <v>26.74688148498535</v>
@@ -1280,11 +1292,11 @@
       <c r="I43" t="inlineStr"/>
     </row>
     <row r="44">
-      <c r="A44" s="1" t="n">
+      <c r="A44" s="2" t="n">
         <v>40025</v>
       </c>
       <c r="B44" t="n">
-        <v>17.95880699157715</v>
+        <v>17.95879745483398</v>
       </c>
       <c r="C44" t="n">
         <v>30.25846672058105</v>
@@ -1299,11 +1311,11 @@
       <c r="I44" t="inlineStr"/>
     </row>
     <row r="45">
-      <c r="A45" s="1" t="n">
+      <c r="A45" s="2" t="n">
         <v>40056</v>
       </c>
       <c r="B45" t="n">
-        <v>19.97421646118164</v>
+        <v>19.97421455383301</v>
       </c>
       <c r="C45" t="n">
         <v>33.65419006347656</v>
@@ -1324,7 +1336,7 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="1" t="n">
+      <c r="A46" s="2" t="n">
         <v>40086</v>
       </c>
       <c r="B46" t="n">
@@ -1349,11 +1361,11 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="1" t="n">
+      <c r="A47" s="2" t="n">
         <v>40117</v>
       </c>
       <c r="B47" t="n">
-        <v>18.00112724304199</v>
+        <v>18.00112152099609</v>
       </c>
       <c r="C47" t="n">
         <v>30.32976722717285</v>
@@ -1374,11 +1386,11 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="1" t="n">
+      <c r="A48" s="2" t="n">
         <v>40147</v>
       </c>
       <c r="B48" t="n">
-        <v>18.49503898620605</v>
+        <v>18.49504280090332</v>
       </c>
       <c r="C48" t="n">
         <v>30.47237014770508</v>
@@ -1399,11 +1411,11 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="1" t="n">
+      <c r="A49" s="2" t="n">
         <v>40178</v>
       </c>
       <c r="B49" t="n">
-        <v>19.12254524230957</v>
+        <v>19.12253952026367</v>
       </c>
       <c r="C49" t="n">
         <v>31.50623893737793</v>
@@ -1424,11 +1436,11 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="1" t="n">
+      <c r="A50" s="2" t="n">
         <v>40209</v>
       </c>
       <c r="B50" t="n">
-        <v>19.10630798339844</v>
+        <v>19.10632133483887</v>
       </c>
       <c r="C50" t="n">
         <v>31.47950172424316</v>
@@ -1449,7 +1461,7 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="1" t="n">
+      <c r="A51" s="2" t="n">
         <v>40237</v>
       </c>
       <c r="B51" t="n">
@@ -1474,11 +1486,11 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="1" t="n">
+      <c r="A52" s="2" t="n">
         <v>40268</v>
       </c>
       <c r="B52" t="n">
-        <v>23.44472122192383</v>
+        <v>23.44471740722656</v>
       </c>
       <c r="C52" t="n">
         <v>38.6274528503418</v>
@@ -1499,11 +1511,11 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="1" t="n">
+      <c r="A53" s="2" t="n">
         <v>40298</v>
       </c>
       <c r="B53" t="n">
-        <v>24.65644645690918</v>
+        <v>24.65645408630371</v>
       </c>
       <c r="C53" t="n">
         <v>40.62388610839844</v>
@@ -1524,11 +1536,11 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="1" t="n">
+      <c r="A54" s="2" t="n">
         <v>40329</v>
       </c>
       <c r="B54" t="n">
-        <v>21.90303230285645</v>
+        <v>21.90301895141602</v>
       </c>
       <c r="C54" t="n">
         <v>36.08734512329102</v>
@@ -1549,11 +1561,11 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="1" t="n">
+      <c r="A55" s="2" t="n">
         <v>40359</v>
       </c>
       <c r="B55" t="n">
-        <v>20.42623519897461</v>
+        <v>20.42622756958008</v>
       </c>
       <c r="C55" t="n">
         <v>33.65419006347656</v>
@@ -1574,11 +1586,11 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="1" t="n">
+      <c r="A56" s="2" t="n">
         <v>40390</v>
       </c>
       <c r="B56" t="n">
-        <v>22.75230979919434</v>
+        <v>22.7523136138916</v>
       </c>
       <c r="C56" t="n">
         <v>37.48662948608398</v>
@@ -1599,11 +1611,11 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="1" t="n">
+      <c r="A57" s="2" t="n">
         <v>40421</v>
       </c>
       <c r="B57" t="n">
-        <v>20.36672401428223</v>
+        <v>20.36672210693359</v>
       </c>
       <c r="C57" t="n">
         <v>33.55614852905273</v>
@@ -1624,11 +1636,11 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="1" t="n">
+      <c r="A58" s="2" t="n">
         <v>40451</v>
       </c>
       <c r="B58" t="n">
-        <v>20.79948043823242</v>
+        <v>20.79948425292969</v>
       </c>
       <c r="C58" t="n">
         <v>34.26916122436523</v>
@@ -1649,11 +1661,11 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="1" t="n">
+      <c r="A59" s="2" t="n">
         <v>40482</v>
       </c>
       <c r="B59" t="n">
-        <v>21.81646728515625</v>
+        <v>21.81647682189941</v>
       </c>
       <c r="C59" t="n">
         <v>35.94474029541016</v>
@@ -1674,11 +1686,11 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="1" t="n">
+      <c r="A60" s="2" t="n">
         <v>40512</v>
       </c>
       <c r="B60" t="n">
-        <v>20.99943161010742</v>
+        <v>20.99942779541016</v>
       </c>
       <c r="C60" t="n">
         <v>34.00178146362305</v>
@@ -1699,7 +1711,7 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="1" t="n">
+      <c r="A61" s="2" t="n">
         <v>40543</v>
       </c>
       <c r="B61" t="n">
@@ -1724,11 +1736,11 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="1" t="n">
+      <c r="A62" s="2" t="n">
         <v>40574</v>
       </c>
       <c r="B62" t="n">
-        <v>25.19380378723145</v>
+        <v>25.19380569458008</v>
       </c>
       <c r="C62" t="n">
         <v>40.7932243347168</v>
@@ -1749,11 +1761,11 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="1" t="n">
+      <c r="A63" s="2" t="n">
         <v>40602</v>
       </c>
       <c r="B63" t="n">
-        <v>26.06902313232422</v>
+        <v>26.06900787353516</v>
       </c>
       <c r="C63" t="n">
         <v>42.2103385925293</v>
@@ -1778,7 +1790,7 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="1" t="n">
+      <c r="A64" s="2" t="n">
         <v>40633</v>
       </c>
       <c r="B64" t="n">
@@ -1807,7 +1819,7 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="1" t="n">
+      <c r="A65" s="2" t="n">
         <v>40663</v>
       </c>
       <c r="B65" t="n">
@@ -1836,11 +1848,11 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="1" t="n">
+      <c r="A66" s="2" t="n">
         <v>40694</v>
       </c>
       <c r="B66" t="n">
-        <v>24.27456092834473</v>
+        <v>24.27456283569336</v>
       </c>
       <c r="C66" t="n">
         <v>39.30481338500977</v>
@@ -1865,11 +1877,11 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="1" t="n">
+      <c r="A67" s="2" t="n">
         <v>40724</v>
       </c>
       <c r="B67" t="n">
-        <v>24.14796447753906</v>
+        <v>24.1479663848877</v>
       </c>
       <c r="C67" t="n">
         <v>39.09982299804688</v>
@@ -1894,11 +1906,11 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="1" t="n">
+      <c r="A68" s="2" t="n">
         <v>40755</v>
       </c>
       <c r="B68" t="n">
-        <v>22.68378448486328</v>
+        <v>22.68378067016602</v>
       </c>
       <c r="C68" t="n">
         <v>36.72905349731445</v>
@@ -1923,11 +1935,11 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="1" t="n">
+      <c r="A69" s="2" t="n">
         <v>40786</v>
       </c>
       <c r="B69" t="n">
-        <v>18.49490928649902</v>
+        <v>18.49490547180176</v>
       </c>
       <c r="C69" t="n">
         <v>29.94652366638184</v>
@@ -1952,11 +1964,11 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="1" t="n">
+      <c r="A70" s="2" t="n">
         <v>40816</v>
       </c>
       <c r="B70" t="n">
-        <v>15.41793155670166</v>
+        <v>15.41793346405029</v>
       </c>
       <c r="C70" t="n">
         <v>24.9643497467041</v>
@@ -1981,11 +1993,11 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="1" t="n">
+      <c r="A71" s="2" t="n">
         <v>40847</v>
       </c>
       <c r="B71" t="n">
-        <v>19.35360145568848</v>
+        <v>19.35360336303711</v>
       </c>
       <c r="C71" t="n">
         <v>31.33689880371094</v>
@@ -2010,11 +2022,11 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="1" t="n">
+      <c r="A72" s="2" t="n">
         <v>40877</v>
       </c>
       <c r="B72" t="n">
-        <v>17.70477676391602</v>
+        <v>17.70477294921875</v>
       </c>
       <c r="C72" t="n">
         <v>28.05704116821289</v>
@@ -2039,11 +2051,11 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="1" t="n">
+      <c r="A73" s="2" t="n">
         <v>40908</v>
       </c>
       <c r="B73" t="n">
-        <v>17.53604507446289</v>
+        <v>17.53605079650879</v>
       </c>
       <c r="C73" t="n">
         <v>27.7896614074707</v>
@@ -2068,11 +2080,11 @@
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="1" t="n">
+      <c r="A74" s="2" t="n">
         <v>40939</v>
       </c>
       <c r="B74" t="n">
-        <v>19.87006378173828</v>
+        <v>19.87006187438965</v>
       </c>
       <c r="C74" t="n">
         <v>31.4884147644043</v>
@@ -2097,7 +2109,7 @@
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="1" t="n">
+      <c r="A75" s="2" t="n">
         <v>40968</v>
       </c>
       <c r="B75" t="n">
@@ -2126,11 +2138,11 @@
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="1" t="n">
+      <c r="A76" s="2" t="n">
         <v>40999</v>
       </c>
       <c r="B76" t="n">
-        <v>21.00614356994629</v>
+        <v>21.00613403320312</v>
       </c>
       <c r="C76" t="n">
         <v>33.28876876831055</v>
@@ -2155,11 +2167,11 @@
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="1" t="n">
+      <c r="A77" s="2" t="n">
         <v>41029</v>
       </c>
       <c r="B77" t="n">
-        <v>20.26375770568848</v>
+        <v>20.26375389099121</v>
       </c>
       <c r="C77" t="n">
         <v>32.11230087280273</v>
@@ -2184,11 +2196,11 @@
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="1" t="n">
+      <c r="A78" s="2" t="n">
         <v>41060</v>
       </c>
       <c r="B78" t="n">
-        <v>16.4281005859375</v>
+        <v>16.42809677124023</v>
       </c>
       <c r="C78" t="n">
         <v>26.03386878967285</v>
@@ -2213,11 +2225,11 @@
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="1" t="n">
+      <c r="A79" s="2" t="n">
         <v>41090</v>
       </c>
       <c r="B79" t="n">
-        <v>17.35045433044434</v>
+        <v>17.35045051574707</v>
       </c>
       <c r="C79" t="n">
         <v>27.49554443359375</v>
@@ -2242,11 +2254,11 @@
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="1" t="n">
+      <c r="A80" s="2" t="n">
         <v>41121</v>
       </c>
       <c r="B80" t="n">
-        <v>17.30545806884766</v>
+        <v>17.30545425415039</v>
       </c>
       <c r="C80" t="n">
         <v>27.42424201965332</v>
@@ -2271,7 +2283,7 @@
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="1" t="n">
+      <c r="A81" s="2" t="n">
         <v>41152</v>
       </c>
       <c r="B81" t="n">
@@ -2300,11 +2312,11 @@
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="1" t="n">
+      <c r="A82" s="2" t="n">
         <v>41182</v>
       </c>
       <c r="B82" t="n">
-        <v>19.38076019287109</v>
+        <v>19.38076400756836</v>
       </c>
       <c r="C82" t="n">
         <v>30.7130126953125</v>
@@ -2329,11 +2341,11 @@
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="1" t="n">
+      <c r="A83" s="2" t="n">
         <v>41213</v>
       </c>
       <c r="B83" t="n">
-        <v>19.96005058288574</v>
+        <v>19.96005439758301</v>
       </c>
       <c r="C83" t="n">
         <v>31.63101577758789</v>
@@ -2358,11 +2370,11 @@
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="1" t="n">
+      <c r="A84" s="2" t="n">
         <v>41243</v>
       </c>
       <c r="B84" t="n">
-        <v>19.0693359375</v>
+        <v>19.0693302154541</v>
       </c>
       <c r="C84" t="n">
         <v>29.58110427856445</v>
@@ -2387,11 +2399,11 @@
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="1" t="n">
+      <c r="A85" s="2" t="n">
         <v>41274</v>
       </c>
       <c r="B85" t="n">
-        <v>18.92570114135742</v>
+        <v>18.92569923400879</v>
       </c>
       <c r="C85" t="n">
         <v>29.35828971862793</v>
@@ -2416,11 +2428,11 @@
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="1" t="n">
+      <c r="A86" s="2" t="n">
         <v>41305</v>
       </c>
       <c r="B86" t="n">
-        <v>21.45372200012207</v>
+        <v>21.45372009277344</v>
       </c>
       <c r="C86" t="n">
         <v>33.27985763549805</v>
@@ -2445,11 +2457,11 @@
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="1" t="n">
+      <c r="A87" s="2" t="n">
         <v>41333</v>
       </c>
       <c r="B87" t="n">
-        <v>20.4611701965332</v>
+        <v>20.46116638183594</v>
       </c>
       <c r="C87" t="n">
         <v>31.58645248413086</v>
@@ -2474,11 +2486,11 @@
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="1" t="n">
+      <c r="A88" s="2" t="n">
         <v>41364</v>
       </c>
       <c r="B88" t="n">
-        <v>21.95071601867676</v>
+        <v>21.95071983337402</v>
       </c>
       <c r="C88" t="n">
         <v>33.88591766357422</v>
@@ -2503,7 +2515,7 @@
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="1" t="n">
+      <c r="A89" s="2" t="n">
         <v>41394</v>
       </c>
       <c r="B89" t="n">
@@ -2532,11 +2544,11 @@
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="1" t="n">
+      <c r="A90" s="2" t="n">
         <v>41425</v>
       </c>
       <c r="B90" t="n">
-        <v>25.69791793823242</v>
+        <v>25.69791984558105</v>
       </c>
       <c r="C90" t="n">
         <v>39.40285110473633</v>
@@ -2561,7 +2573,7 @@
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="1" t="n">
+      <c r="A91" s="2" t="n">
         <v>41455</v>
       </c>
       <c r="B91" t="n">
@@ -2590,7 +2602,7 @@
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="1" t="n">
+      <c r="A92" s="2" t="n">
         <v>41486</v>
       </c>
       <c r="B92" t="n">
@@ -2619,11 +2631,11 @@
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="1" t="n">
+      <c r="A93" s="2" t="n">
         <v>41517</v>
       </c>
       <c r="B93" t="n">
-        <v>26.99858474731445</v>
+        <v>26.99857902526855</v>
       </c>
       <c r="C93" t="n">
         <v>41.16755676269531</v>
@@ -2648,11 +2660,11 @@
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="1" t="n">
+      <c r="A94" s="2" t="n">
         <v>41547</v>
       </c>
       <c r="B94" t="n">
-        <v>27.44281578063965</v>
+        <v>27.44282341003418</v>
       </c>
       <c r="C94" t="n">
         <v>41.84492111206055</v>
@@ -2677,7 +2689,7 @@
       </c>
     </row>
     <row r="95">
-      <c r="A95" s="1" t="n">
+      <c r="A95" s="2" t="n">
         <v>41578</v>
       </c>
       <c r="B95" t="n">
@@ -2706,11 +2718,11 @@
       </c>
     </row>
     <row r="96">
-      <c r="A96" s="1" t="n">
+      <c r="A96" s="2" t="n">
         <v>41608</v>
       </c>
       <c r="B96" t="n">
-        <v>30.68116188049316</v>
+        <v>30.68117713928223</v>
       </c>
       <c r="C96" t="n">
         <v>46.51515197753906</v>
@@ -2735,11 +2747,11 @@
       </c>
     </row>
     <row r="97">
-      <c r="A97" s="1" t="n">
+      <c r="A97" s="2" t="n">
         <v>41639</v>
       </c>
       <c r="B97" t="n">
-        <v>31.69819450378418</v>
+        <v>31.69819259643555</v>
       </c>
       <c r="C97" t="n">
         <v>48.05704116821289</v>
@@ -2764,11 +2776,11 @@
       </c>
     </row>
     <row r="98">
-      <c r="A98" s="1" t="n">
+      <c r="A98" s="2" t="n">
         <v>41670</v>
       </c>
       <c r="B98" t="n">
-        <v>28.83523750305176</v>
+        <v>28.83523178100586</v>
       </c>
       <c r="C98" t="n">
         <v>43.71657943725586</v>
@@ -2793,11 +2805,11 @@
       </c>
     </row>
     <row r="99">
-      <c r="A99" s="1" t="n">
+      <c r="A99" s="2" t="n">
         <v>41698</v>
       </c>
       <c r="B99" t="n">
-        <v>29.96269035339355</v>
+        <v>29.96268272399902</v>
       </c>
       <c r="C99" t="n">
         <v>45.16042709350586</v>
@@ -2822,11 +2834,11 @@
       </c>
     </row>
     <row r="100">
-      <c r="A100" s="1" t="n">
+      <c r="A100" s="2" t="n">
         <v>41729</v>
       </c>
       <c r="B100" t="n">
-        <v>31.22222518920898</v>
+        <v>31.22222900390625</v>
       </c>
       <c r="C100" t="n">
         <v>47.05882263183594</v>
@@ -2851,11 +2863,11 @@
       </c>
     </row>
     <row r="101">
-      <c r="A101" s="1" t="n">
+      <c r="A101" s="2" t="n">
         <v>41759</v>
       </c>
       <c r="B101" t="n">
-        <v>30.95612525939941</v>
+        <v>30.95611381530762</v>
       </c>
       <c r="C101" t="n">
         <v>46.65775299072266</v>
@@ -2880,11 +2892,11 @@
       </c>
     </row>
     <row r="102">
-      <c r="A102" s="1" t="n">
+      <c r="A102" s="2" t="n">
         <v>41790</v>
       </c>
       <c r="B102" t="n">
-        <v>30.32898902893066</v>
+        <v>30.32900428771973</v>
       </c>
       <c r="C102" t="n">
         <v>45.39215850830078</v>
@@ -2909,11 +2921,11 @@
       </c>
     </row>
     <row r="103">
-      <c r="A103" s="1" t="n">
+      <c r="A103" s="2" t="n">
         <v>41820</v>
       </c>
       <c r="B103" t="n">
-        <v>33.08618545532227</v>
+        <v>33.08617782592773</v>
       </c>
       <c r="C103" t="n">
         <v>49.51871871948242</v>
@@ -2938,11 +2950,11 @@
       </c>
     </row>
     <row r="104">
-      <c r="A104" s="1" t="n">
+      <c r="A104" s="2" t="n">
         <v>41851</v>
       </c>
       <c r="B104" t="n">
-        <v>31.3234806060791</v>
+        <v>31.32348442077637</v>
       </c>
       <c r="C104" t="n">
         <v>46.88056945800781</v>
@@ -2967,11 +2979,11 @@
       </c>
     </row>
     <row r="105">
-      <c r="A105" s="1" t="n">
+      <c r="A105" s="2" t="n">
         <v>41882</v>
       </c>
       <c r="B105" t="n">
-        <v>32.82016754150391</v>
+        <v>32.82018661499023</v>
       </c>
       <c r="C105" t="n">
         <v>48.78787994384766</v>
@@ -2996,11 +3008,11 @@
       </c>
     </row>
     <row r="106">
-      <c r="A106" s="1" t="n">
+      <c r="A106" s="2" t="n">
         <v>41912</v>
       </c>
       <c r="B106" t="n">
-        <v>32.2086181640625</v>
+        <v>32.2086296081543</v>
       </c>
       <c r="C106" t="n">
         <v>47.87878799438477</v>
@@ -3025,11 +3037,11 @@
       </c>
     </row>
     <row r="107">
-      <c r="A107" s="1" t="n">
+      <c r="A107" s="2" t="n">
         <v>41943</v>
       </c>
       <c r="B107" t="n">
-        <v>32.52040863037109</v>
+        <v>32.52040481567383</v>
       </c>
       <c r="C107" t="n">
         <v>48.34224700927734</v>
@@ -3054,11 +3066,11 @@
       </c>
     </row>
     <row r="108">
-      <c r="A108" s="1" t="n">
+      <c r="A108" s="2" t="n">
         <v>41973</v>
       </c>
       <c r="B108" t="n">
-        <v>33.55867004394531</v>
+        <v>33.55866622924805</v>
       </c>
       <c r="C108" t="n">
         <v>49.56327819824219</v>
@@ -3083,11 +3095,11 @@
       </c>
     </row>
     <row r="109">
-      <c r="A109" s="1" t="n">
+      <c r="A109" s="2" t="n">
         <v>42004</v>
       </c>
       <c r="B109" t="n">
-        <v>32.64140701293945</v>
+        <v>32.64139938354492</v>
       </c>
       <c r="C109" t="n">
         <v>48.20855712890625</v>
@@ -3112,11 +3124,11 @@
       </c>
     </row>
     <row r="110">
-      <c r="A110" s="1" t="n">
+      <c r="A110" s="2" t="n">
         <v>42035</v>
       </c>
       <c r="B110" t="n">
-        <v>28.06110954284668</v>
+        <v>28.06109809875488</v>
       </c>
       <c r="C110" t="n">
         <v>41.44385147094727</v>
@@ -3141,11 +3153,11 @@
       </c>
     </row>
     <row r="111">
-      <c r="A111" s="1" t="n">
+      <c r="A111" s="2" t="n">
         <v>42063</v>
       </c>
       <c r="B111" t="n">
-        <v>30.89428520202637</v>
+        <v>30.894287109375</v>
       </c>
       <c r="C111" t="n">
         <v>45.30302810668945</v>
@@ -3170,11 +3182,11 @@
       </c>
     </row>
     <row r="112">
-      <c r="A112" s="1" t="n">
+      <c r="A112" s="2" t="n">
         <v>42094</v>
       </c>
       <c r="B112" t="n">
-        <v>30.72409820556641</v>
+        <v>30.72410202026367</v>
       </c>
       <c r="C112" t="n">
         <v>45.05347442626953</v>
@@ -3199,11 +3211,11 @@
       </c>
     </row>
     <row r="113">
-      <c r="A113" s="1" t="n">
+      <c r="A113" s="2" t="n">
         <v>42124</v>
       </c>
       <c r="B113" t="n">
-        <v>31.17387199401855</v>
+        <v>31.17388153076172</v>
       </c>
       <c r="C113" t="n">
         <v>45.7130126953125</v>
@@ -3228,11 +3240,11 @@
       </c>
     </row>
     <row r="114">
-      <c r="A114" s="1" t="n">
+      <c r="A114" s="2" t="n">
         <v>42155</v>
       </c>
       <c r="B114" t="n">
-        <v>31.99514961242676</v>
+        <v>31.9951343536377</v>
       </c>
       <c r="C114" t="n">
         <v>46.57754135131836</v>
@@ -3257,11 +3269,11 @@
       </c>
     </row>
     <row r="115">
-      <c r="A115" s="1" t="n">
+      <c r="A115" s="2" t="n">
         <v>42185</v>
       </c>
       <c r="B115" t="n">
-        <v>34.27877807617188</v>
+        <v>34.27876663208008</v>
       </c>
       <c r="C115" t="n">
         <v>49.90196228027344</v>
@@ -3286,11 +3298,11 @@
       </c>
     </row>
     <row r="116">
-      <c r="A116" s="1" t="n">
+      <c r="A116" s="2" t="n">
         <v>42216</v>
       </c>
       <c r="B116" t="n">
-        <v>34.12571716308594</v>
+        <v>34.12570953369141</v>
       </c>
       <c r="C116" t="n">
         <v>49.67914581298828</v>
@@ -3315,7 +3327,7 @@
       </c>
     </row>
     <row r="117">
-      <c r="A117" s="1" t="n">
+      <c r="A117" s="2" t="n">
         <v>42247</v>
       </c>
       <c r="B117" t="n">
@@ -3344,11 +3356,11 @@
       </c>
     </row>
     <row r="118">
-      <c r="A118" s="1" t="n">
+      <c r="A118" s="2" t="n">
         <v>42277</v>
       </c>
       <c r="B118" t="n">
-        <v>29.06150436401367</v>
+        <v>29.06150245666504</v>
       </c>
       <c r="C118" t="n">
         <v>42.02317428588867</v>
@@ -3373,11 +3385,11 @@
       </c>
     </row>
     <row r="119">
-      <c r="A119" s="1" t="n">
+      <c r="A119" s="2" t="n">
         <v>42308</v>
       </c>
       <c r="B119" t="n">
-        <v>31.05235862731934</v>
+        <v>31.05236053466797</v>
       </c>
       <c r="C119" t="n">
         <v>44.90196228027344</v>
@@ -3402,11 +3414,11 @@
       </c>
     </row>
     <row r="120">
-      <c r="A120" s="1" t="n">
+      <c r="A120" s="2" t="n">
         <v>42338</v>
       </c>
       <c r="B120" t="n">
-        <v>31.72139930725098</v>
+        <v>31.72140502929688</v>
       </c>
       <c r="C120" t="n">
         <v>45.53475952148438</v>
@@ -3431,11 +3443,11 @@
       </c>
     </row>
     <row r="121">
-      <c r="A121" s="1" t="n">
+      <c r="A121" s="2" t="n">
         <v>42369</v>
       </c>
       <c r="B121" t="n">
-        <v>29.93323516845703</v>
+        <v>29.9332332611084</v>
       </c>
       <c r="C121" t="n">
         <v>42.96791458129883</v>
@@ -3460,11 +3472,11 @@
       </c>
     </row>
     <row r="122">
-      <c r="A122" s="1" t="n">
+      <c r="A122" s="2" t="n">
         <v>42400</v>
       </c>
       <c r="B122" t="n">
-        <v>27.72285842895508</v>
+        <v>27.72285461425781</v>
       </c>
       <c r="C122" t="n">
         <v>39.79500961303711</v>
@@ -3489,11 +3501,11 @@
       </c>
     </row>
     <row r="123">
-      <c r="A123" s="1" t="n">
+      <c r="A123" s="2" t="n">
         <v>42429</v>
       </c>
       <c r="B123" t="n">
-        <v>24.77983283996582</v>
+        <v>24.77983093261719</v>
       </c>
       <c r="C123" t="n">
         <v>35.25846862792969</v>
@@ -3518,11 +3530,11 @@
       </c>
     </row>
     <row r="124">
-      <c r="A124" s="1" t="n">
+      <c r="A124" s="2" t="n">
         <v>42460</v>
       </c>
       <c r="B124" t="n">
-        <v>27.52339553833008</v>
+        <v>27.52340126037598</v>
       </c>
       <c r="C124" t="n">
         <v>39.16220855712891</v>
@@ -3547,11 +3559,11 @@
       </c>
     </row>
     <row r="125">
-      <c r="A125" s="1" t="n">
+      <c r="A125" s="2" t="n">
         <v>42490</v>
       </c>
       <c r="B125" t="n">
-        <v>28.25000953674316</v>
+        <v>28.2500114440918</v>
       </c>
       <c r="C125" t="n">
         <v>40.19607925415039</v>
@@ -3576,11 +3588,11 @@
       </c>
     </row>
     <row r="126">
-      <c r="A126" s="1" t="n">
+      <c r="A126" s="2" t="n">
         <v>42521</v>
       </c>
       <c r="B126" t="n">
-        <v>28.79400634765625</v>
+        <v>28.79400253295898</v>
       </c>
       <c r="C126" t="n">
         <v>40.59714889526367</v>
@@ -3605,11 +3617,11 @@
       </c>
     </row>
     <row r="127">
-      <c r="A127" s="1" t="n">
+      <c r="A127" s="2" t="n">
         <v>42551</v>
       </c>
       <c r="B127" t="n">
-        <v>25.17815589904785</v>
+        <v>25.17815780639648</v>
       </c>
       <c r="C127" t="n">
         <v>35.49910736083984</v>
@@ -3634,11 +3646,11 @@
       </c>
     </row>
     <row r="128">
-      <c r="A128" s="1" t="n">
+      <c r="A128" s="2" t="n">
         <v>42582</v>
       </c>
       <c r="B128" t="n">
-        <v>27.01769065856934</v>
+        <v>27.01768112182617</v>
       </c>
       <c r="C128" t="n">
         <v>38.09269332885742</v>
@@ -3663,11 +3675,11 @@
       </c>
     </row>
     <row r="129">
-      <c r="A129" s="1" t="n">
+      <c r="A129" s="2" t="n">
         <v>42613</v>
       </c>
       <c r="B129" t="n">
-        <v>27.68833541870117</v>
+        <v>27.68833923339844</v>
       </c>
       <c r="C129" t="n">
         <v>38.68092727661133</v>
@@ -3692,11 +3704,11 @@
       </c>
     </row>
     <row r="130">
-      <c r="A130" s="1" t="n">
+      <c r="A130" s="2" t="n">
         <v>42643</v>
       </c>
       <c r="B130" t="n">
-        <v>28.34545516967773</v>
+        <v>28.3454647064209</v>
       </c>
       <c r="C130" t="n">
         <v>39.59893035888672</v>
@@ -3721,11 +3733,11 @@
       </c>
     </row>
     <row r="131">
-      <c r="A131" s="1" t="n">
+      <c r="A131" s="2" t="n">
         <v>42674</v>
       </c>
       <c r="B131" t="n">
-        <v>29.95954513549805</v>
+        <v>29.95954322814941</v>
       </c>
       <c r="C131" t="n">
         <v>41.85383224487305</v>
@@ -3750,7 +3762,7 @@
       </c>
     </row>
     <row r="132">
-      <c r="A132" s="1" t="n">
+      <c r="A132" s="2" t="n">
         <v>42704</v>
       </c>
       <c r="B132" t="n">
@@ -3779,11 +3791,11 @@
       </c>
     </row>
     <row r="133">
-      <c r="A133" s="1" t="n">
+      <c r="A133" s="2" t="n">
         <v>42735</v>
       </c>
       <c r="B133" t="n">
-        <v>34.68010330200195</v>
+        <v>34.68011474609375</v>
       </c>
       <c r="C133" t="n">
         <v>48.03030395507812</v>
@@ -3808,7 +3820,7 @@
       </c>
     </row>
     <row r="134">
-      <c r="A134" s="1" t="n">
+      <c r="A134" s="2" t="n">
         <v>42766</v>
       </c>
       <c r="B134" t="n">
@@ -3837,11 +3849,11 @@
       </c>
     </row>
     <row r="135">
-      <c r="A135" s="1" t="n">
+      <c r="A135" s="2" t="n">
         <v>42794</v>
       </c>
       <c r="B135" t="n">
-        <v>33.99732971191406</v>
+        <v>33.99733734130859</v>
       </c>
       <c r="C135" t="n">
         <v>46.73796844482422</v>
@@ -3866,7 +3878,7 @@
       </c>
     </row>
     <row r="136">
-      <c r="A136" s="1" t="n">
+      <c r="A136" s="2" t="n">
         <v>42825</v>
       </c>
       <c r="B136" t="n">
@@ -3895,11 +3907,11 @@
       </c>
     </row>
     <row r="137">
-      <c r="A137" s="1" t="n">
+      <c r="A137" s="2" t="n">
         <v>42855</v>
       </c>
       <c r="B137" t="n">
-        <v>33.58889007568359</v>
+        <v>33.58888626098633</v>
       </c>
       <c r="C137" t="n">
         <v>46.17647171020508</v>
@@ -3924,11 +3936,11 @@
       </c>
     </row>
     <row r="138">
-      <c r="A138" s="1" t="n">
+      <c r="A138" s="2" t="n">
         <v>42886</v>
       </c>
       <c r="B138" t="n">
-        <v>33.05171585083008</v>
+        <v>33.05171203613281</v>
       </c>
       <c r="C138" t="n">
         <v>45.08912658691406</v>
@@ -3951,7 +3963,7 @@
       </c>
     </row>
     <row r="139">
-      <c r="A139" s="1" t="n">
+      <c r="A139" s="2" t="n">
         <v>42916</v>
       </c>
       <c r="B139" t="n">
@@ -3978,11 +3990,11 @@
       </c>
     </row>
     <row r="140">
-      <c r="A140" s="1" t="n">
+      <c r="A140" s="2" t="n">
         <v>42947</v>
       </c>
       <c r="B140" t="n">
-        <v>35.93287658691406</v>
+        <v>35.93288040161133</v>
       </c>
       <c r="C140" t="n">
         <v>49.01960754394531</v>
@@ -4005,11 +4017,11 @@
       </c>
     </row>
     <row r="141">
-      <c r="A141" s="1" t="n">
+      <c r="A141" s="2" t="n">
         <v>42978</v>
       </c>
       <c r="B141" t="n">
-        <v>34.57712554931641</v>
+        <v>34.57711791992188</v>
       </c>
       <c r="C141" t="n">
         <v>46.83000183105469</v>
@@ -4034,11 +4046,11 @@
       </c>
     </row>
     <row r="142">
-      <c r="A142" s="1" t="n">
+      <c r="A142" s="2" t="n">
         <v>43008</v>
       </c>
       <c r="B142" t="n">
-        <v>38.35750198364258</v>
+        <v>38.35749435424805</v>
       </c>
       <c r="C142" t="n">
         <v>51.95000076293945</v>
@@ -4063,11 +4075,11 @@
       </c>
     </row>
     <row r="143">
-      <c r="A143" s="1" t="n">
+      <c r="A143" s="2" t="n">
         <v>43039</v>
       </c>
       <c r="B143" t="n">
-        <v>39.56101226806641</v>
+        <v>39.56099700927734</v>
       </c>
       <c r="C143" t="n">
         <v>53.58000183105469</v>
@@ -4092,11 +4104,11 @@
       </c>
     </row>
     <row r="144">
-      <c r="A144" s="1" t="n">
+      <c r="A144" s="2" t="n">
         <v>43069</v>
       </c>
       <c r="B144" t="n">
-        <v>39.92136764526367</v>
+        <v>39.92138290405273</v>
       </c>
       <c r="C144" t="n">
         <v>53.68000030517578</v>
@@ -4119,11 +4131,11 @@
       </c>
     </row>
     <row r="145">
-      <c r="A145" s="1" t="n">
+      <c r="A145" s="2" t="n">
         <v>43100</v>
       </c>
       <c r="B145" t="n">
-        <v>37.6010627746582</v>
+        <v>37.60106658935547</v>
       </c>
       <c r="C145" t="n">
         <v>50.56000137329102</v>
@@ -4146,11 +4158,11 @@
       </c>
     </row>
     <row r="146">
-      <c r="A146" s="1" t="n">
+      <c r="A146" s="2" t="n">
         <v>43131</v>
       </c>
       <c r="B146" t="n">
-        <v>35.74926376342773</v>
+        <v>35.749267578125</v>
       </c>
       <c r="C146" t="n">
         <v>48.06999969482422</v>
@@ -4173,11 +4185,11 @@
       </c>
     </row>
     <row r="147">
-      <c r="A147" s="1" t="n">
+      <c r="A147" s="2" t="n">
         <v>43159</v>
       </c>
       <c r="B147" t="n">
-        <v>34.63743591308594</v>
+        <v>34.63743209838867</v>
       </c>
       <c r="C147" t="n">
         <v>46.18999862670898</v>
@@ -4200,11 +4212,11 @@
       </c>
     </row>
     <row r="148">
-      <c r="A148" s="1" t="n">
+      <c r="A148" s="2" t="n">
         <v>43190</v>
       </c>
       <c r="B148" t="n">
-        <v>34.4124641418457</v>
+        <v>34.41246795654297</v>
       </c>
       <c r="C148" t="n">
         <v>45.88999938964844</v>
@@ -4229,11 +4241,11 @@
       </c>
     </row>
     <row r="149">
-      <c r="A149" s="1" t="n">
+      <c r="A149" s="2" t="n">
         <v>43220</v>
       </c>
       <c r="B149" t="n">
-        <v>35.74727249145508</v>
+        <v>35.74728012084961</v>
       </c>
       <c r="C149" t="n">
         <v>47.66999816894531</v>
@@ -4258,11 +4270,11 @@
       </c>
     </row>
     <row r="150">
-      <c r="A150" s="1" t="n">
+      <c r="A150" s="2" t="n">
         <v>43251</v>
       </c>
       <c r="B150" t="n">
-        <v>34.81487274169922</v>
+        <v>34.81486892700195</v>
       </c>
       <c r="C150" t="n">
         <v>45.9900016784668</v>
@@ -4287,11 +4299,11 @@
       </c>
     </row>
     <row r="151">
-      <c r="A151" s="1" t="n">
+      <c r="A151" s="2" t="n">
         <v>43281</v>
       </c>
       <c r="B151" t="n">
-        <v>33.0056266784668</v>
+        <v>33.00562286376953</v>
       </c>
       <c r="C151" t="n">
         <v>43.59999847412109</v>
@@ -4316,11 +4328,11 @@
       </c>
     </row>
     <row r="152">
-      <c r="A152" s="1" t="n">
+      <c r="A152" s="2" t="n">
         <v>43312</v>
       </c>
       <c r="B152" t="n">
-        <v>34.6256217956543</v>
+        <v>34.62562561035156</v>
       </c>
       <c r="C152" t="n">
         <v>45.7400016784668</v>
@@ -4345,11 +4357,11 @@
       </c>
     </row>
     <row r="153">
-      <c r="A153" s="1" t="n">
+      <c r="A153" s="2" t="n">
         <v>43343</v>
       </c>
       <c r="B153" t="n">
-        <v>35.05794525146484</v>
+        <v>35.05795288085938</v>
       </c>
       <c r="C153" t="n">
         <v>45.88999938964844</v>
@@ -4374,11 +4386,11 @@
       </c>
     </row>
     <row r="154">
-      <c r="A154" s="1" t="n">
+      <c r="A154" s="2" t="n">
         <v>43373</v>
       </c>
       <c r="B154" t="n">
-        <v>35.69203567504883</v>
+        <v>35.6920280456543</v>
       </c>
       <c r="C154" t="n">
         <v>46.72000122070312</v>
@@ -4403,11 +4415,11 @@
       </c>
     </row>
     <row r="155">
-      <c r="A155" s="1" t="n">
+      <c r="A155" s="2" t="n">
         <v>43404</v>
       </c>
       <c r="B155" t="n">
-        <v>31.46735763549805</v>
+        <v>31.46735954284668</v>
       </c>
       <c r="C155" t="n">
         <v>41.18999862670898</v>
@@ -4432,11 +4444,11 @@
       </c>
     </row>
     <row r="156">
-      <c r="A156" s="1" t="n">
+      <c r="A156" s="2" t="n">
         <v>43434</v>
       </c>
       <c r="B156" t="n">
-        <v>34.42701721191406</v>
+        <v>34.42700958251953</v>
       </c>
       <c r="C156" t="n">
         <v>44.63000106811523</v>
@@ -4461,11 +4473,11 @@
       </c>
     </row>
     <row r="157">
-      <c r="A157" s="1" t="n">
+      <c r="A157" s="2" t="n">
         <v>43465</v>
       </c>
       <c r="B157" t="n">
-        <v>31.67314910888672</v>
+        <v>31.67315483093262</v>
       </c>
       <c r="C157" t="n">
         <v>41.06000137329102</v>
@@ -4490,11 +4502,11 @@
       </c>
     </row>
     <row r="158">
-      <c r="A158" s="1" t="n">
+      <c r="A158" s="2" t="n">
         <v>43496</v>
       </c>
       <c r="B158" t="n">
-        <v>35.22925186157227</v>
+        <v>35.22924423217773</v>
       </c>
       <c r="C158" t="n">
         <v>45.66999816894531</v>
@@ -4519,11 +4531,11 @@
       </c>
     </row>
     <row r="159">
-      <c r="A159" s="1" t="n">
+      <c r="A159" s="2" t="n">
         <v>43524</v>
       </c>
       <c r="B159" t="n">
-        <v>35.18346405029297</v>
+        <v>35.18346786499023</v>
       </c>
       <c r="C159" t="n">
         <v>45.18999862670898</v>
@@ -4548,11 +4560,11 @@
       </c>
     </row>
     <row r="160">
-      <c r="A160" s="1" t="n">
+      <c r="A160" s="2" t="n">
         <v>43555</v>
       </c>
       <c r="B160" t="n">
-        <v>33.14361953735352</v>
+        <v>33.14363098144531</v>
       </c>
       <c r="C160" t="n">
         <v>42.56999969482422</v>
@@ -4577,11 +4589,11 @@
       </c>
     </row>
     <row r="161">
-      <c r="A161" s="1" t="n">
+      <c r="A161" s="2" t="n">
         <v>43585</v>
       </c>
       <c r="B161" t="n">
-        <v>35.91532516479492</v>
+        <v>35.91531753540039</v>
       </c>
       <c r="C161" t="n">
         <v>46.13000106811523</v>
@@ -4606,11 +4618,11 @@
       </c>
     </row>
     <row r="162">
-      <c r="A162" s="1" t="n">
+      <c r="A162" s="2" t="n">
         <v>43616</v>
       </c>
       <c r="B162" t="n">
-        <v>36.31046295166016</v>
+        <v>36.31045532226562</v>
       </c>
       <c r="C162" t="n">
         <v>46.20999908447266</v>
@@ -4635,11 +4647,11 @@
       </c>
     </row>
     <row r="163">
-      <c r="A163" s="1" t="n">
+      <c r="A163" s="2" t="n">
         <v>43646</v>
       </c>
       <c r="B163" t="n">
-        <v>39.02922439575195</v>
+        <v>39.02920913696289</v>
       </c>
       <c r="C163" t="n">
         <v>49.66999816894531</v>
@@ -4664,11 +4676,11 @@
       </c>
     </row>
     <row r="164">
-      <c r="A164" s="1" t="n">
+      <c r="A164" s="2" t="n">
         <v>43677</v>
       </c>
       <c r="B164" t="n">
-        <v>38.83277893066406</v>
+        <v>38.8327751159668</v>
       </c>
       <c r="C164" t="n">
         <v>49.41999816894531</v>
@@ -4693,11 +4705,11 @@
       </c>
     </row>
     <row r="165">
-      <c r="A165" s="1" t="n">
+      <c r="A165" s="2" t="n">
         <v>43708</v>
       </c>
       <c r="B165" t="n">
-        <v>35.13655090332031</v>
+        <v>35.13653945922852</v>
       </c>
       <c r="C165" t="n">
         <v>44.29999923706055</v>
@@ -4722,11 +4734,11 @@
       </c>
     </row>
     <row r="166">
-      <c r="A166" s="1" t="n">
+      <c r="A166" s="2" t="n">
         <v>43738</v>
       </c>
       <c r="B166" t="n">
-        <v>37.40496063232422</v>
+        <v>37.40495681762695</v>
       </c>
       <c r="C166" t="n">
         <v>47.15999984741211</v>
@@ -4751,11 +4763,11 @@
       </c>
     </row>
     <row r="167">
-      <c r="A167" s="1" t="n">
+      <c r="A167" s="2" t="n">
         <v>43769</v>
       </c>
       <c r="B167" t="n">
-        <v>37.11149597167969</v>
+        <v>37.11149215698242</v>
       </c>
       <c r="C167" t="n">
         <v>46.79000091552734</v>
@@ -4780,11 +4792,11 @@
       </c>
     </row>
     <row r="168">
-      <c r="A168" s="1" t="n">
+      <c r="A168" s="2" t="n">
         <v>43799</v>
       </c>
       <c r="B168" t="n">
-        <v>39.95813369750977</v>
+        <v>39.9581413269043</v>
       </c>
       <c r="C168" t="n">
         <v>49.90999984741211</v>
@@ -4809,7 +4821,7 @@
       </c>
     </row>
     <row r="169">
-      <c r="A169" s="1" t="n">
+      <c r="A169" s="2" t="n">
         <v>43830</v>
       </c>
       <c r="B169" t="n">
@@ -4838,11 +4850,11 @@
       </c>
     </row>
     <row r="170">
-      <c r="A170" s="1" t="n">
+      <c r="A170" s="2" t="n">
         <v>43861</v>
       </c>
       <c r="B170" t="n">
-        <v>39.79801559448242</v>
+        <v>39.79801940917969</v>
       </c>
       <c r="C170" t="n">
         <v>49.70999908447266</v>
@@ -4867,11 +4879,11 @@
       </c>
     </row>
     <row r="171">
-      <c r="A171" s="1" t="n">
+      <c r="A171" s="2" t="n">
         <v>43890</v>
       </c>
       <c r="B171" t="n">
-        <v>34.50724792480469</v>
+        <v>34.50723648071289</v>
       </c>
       <c r="C171" t="n">
         <v>42.72000122070312</v>
@@ -4896,11 +4908,11 @@
       </c>
     </row>
     <row r="172">
-      <c r="A172" s="1" t="n">
+      <c r="A172" s="2" t="n">
         <v>43921</v>
       </c>
       <c r="B172" t="n">
-        <v>24.69302749633789</v>
+        <v>24.69302940368652</v>
       </c>
       <c r="C172" t="n">
         <v>30.56999969482422</v>
@@ -4925,11 +4937,11 @@
       </c>
     </row>
     <row r="173">
-      <c r="A173" s="1" t="n">
+      <c r="A173" s="2" t="n">
         <v>43951</v>
       </c>
       <c r="B173" t="n">
-        <v>29.14374923706055</v>
+        <v>29.14374542236328</v>
       </c>
       <c r="C173" t="n">
         <v>36.08000183105469</v>
@@ -4954,11 +4966,11 @@
       </c>
     </row>
     <row r="174">
-      <c r="A174" s="1" t="n">
+      <c r="A174" s="2" t="n">
         <v>43982</v>
       </c>
       <c r="B174" t="n">
-        <v>29.4987735748291</v>
+        <v>29.49877548217773</v>
       </c>
       <c r="C174" t="n">
         <v>36.0099983215332</v>
@@ -4983,7 +4995,7 @@
       </c>
     </row>
     <row r="175">
-      <c r="A175" s="1" t="n">
+      <c r="A175" s="2" t="n">
         <v>44012</v>
       </c>
       <c r="B175" t="n">
@@ -5012,11 +5024,11 @@
       </c>
     </row>
     <row r="176">
-      <c r="A176" s="1" t="n">
+      <c r="A176" s="2" t="n">
         <v>44043</v>
       </c>
       <c r="B176" t="n">
-        <v>31.00606346130371</v>
+        <v>31.00607299804688</v>
       </c>
       <c r="C176" t="n">
         <v>37.84999847412109</v>
@@ -5041,11 +5053,11 @@
       </c>
     </row>
     <row r="177">
-      <c r="A177" s="1" t="n">
+      <c r="A177" s="2" t="n">
         <v>44074</v>
       </c>
       <c r="B177" t="n">
-        <v>31.89338111877441</v>
+        <v>31.89337730407715</v>
       </c>
       <c r="C177" t="n">
         <v>38.45999908447266</v>
@@ -5070,11 +5082,11 @@
       </c>
     </row>
     <row r="178">
-      <c r="A178" s="1" t="n">
+      <c r="A178" s="2" t="n">
         <v>44104</v>
       </c>
       <c r="B178" t="n">
-        <v>30.82363700866699</v>
+        <v>30.82362365722656</v>
       </c>
       <c r="C178" t="n">
         <v>37.16999816894531</v>
@@ -5099,11 +5111,11 @@
       </c>
     </row>
     <row r="179">
-      <c r="A179" s="1" t="n">
+      <c r="A179" s="2" t="n">
         <v>44135</v>
       </c>
       <c r="B179" t="n">
-        <v>31.38752365112305</v>
+        <v>31.38753509521484</v>
       </c>
       <c r="C179" t="n">
         <v>37.84999847412109</v>
@@ -5128,7 +5140,7 @@
       </c>
     </row>
     <row r="180">
-      <c r="A180" s="1" t="n">
+      <c r="A180" s="2" t="n">
         <v>44165</v>
       </c>
       <c r="B180" t="n">
@@ -5157,11 +5169,11 @@
       </c>
     </row>
     <row r="181">
-      <c r="A181" s="1" t="n">
+      <c r="A181" s="2" t="n">
         <v>44196</v>
       </c>
       <c r="B181" t="n">
-        <v>39.41280746459961</v>
+        <v>39.41280364990234</v>
       </c>
       <c r="C181" t="n">
         <v>46.95000076293945</v>
@@ -5186,11 +5198,11 @@
       </c>
     </row>
     <row r="182">
-      <c r="A182" s="1" t="n">
+      <c r="A182" s="2" t="n">
         <v>44227</v>
       </c>
       <c r="B182" t="n">
-        <v>40.4201545715332</v>
+        <v>40.420166015625</v>
       </c>
       <c r="C182" t="n">
         <v>48.15000152587891</v>
@@ -5215,7 +5227,7 @@
       </c>
     </row>
     <row r="183">
-      <c r="A183" s="1" t="n">
+      <c r="A183" s="2" t="n">
         <v>44255</v>
       </c>
       <c r="B183" t="n">
@@ -5244,11 +5256,11 @@
       </c>
     </row>
     <row r="184">
-      <c r="A184" s="1" t="n">
+      <c r="A184" s="2" t="n">
         <v>44286</v>
       </c>
       <c r="B184" t="n">
-        <v>51.51090621948242</v>
+        <v>51.51091384887695</v>
       </c>
       <c r="C184" t="n">
         <v>60.79000091552734</v>
@@ -5273,11 +5285,11 @@
       </c>
     </row>
     <row r="185">
-      <c r="A185" s="1" t="n">
+      <c r="A185" s="2" t="n">
         <v>44316</v>
       </c>
       <c r="B185" t="n">
-        <v>53.91741561889648</v>
+        <v>53.91742324829102</v>
       </c>
       <c r="C185" t="n">
         <v>63.63000106811523</v>
@@ -5302,11 +5314,11 @@
       </c>
     </row>
     <row r="186">
-      <c r="A186" s="1" t="n">
+      <c r="A186" s="2" t="n">
         <v>44347</v>
       </c>
       <c r="B186" t="n">
-        <v>55.78203964233398</v>
+        <v>55.78203582763672</v>
       </c>
       <c r="C186" t="n">
         <v>65.36000061035156</v>
@@ -5331,11 +5343,11 @@
       </c>
     </row>
     <row r="187">
-      <c r="A187" s="1" t="n">
+      <c r="A187" s="2" t="n">
         <v>44377</v>
       </c>
       <c r="B187" t="n">
-        <v>51.07947158813477</v>
+        <v>51.0794677734375</v>
       </c>
       <c r="C187" t="n">
         <v>59.84999847412109</v>
@@ -5360,11 +5372,11 @@
       </c>
     </row>
     <row r="188">
-      <c r="A188" s="1" t="n">
+      <c r="A188" s="2" t="n">
         <v>44408</v>
       </c>
       <c r="B188" t="n">
-        <v>49.24454116821289</v>
+        <v>49.24454879760742</v>
       </c>
       <c r="C188" t="n">
         <v>57.70000076293945</v>
@@ -5389,11 +5401,11 @@
       </c>
     </row>
     <row r="189">
-      <c r="A189" s="1" t="n">
+      <c r="A189" s="2" t="n">
         <v>44439</v>
       </c>
       <c r="B189" t="n">
-        <v>53.33611297607422</v>
+        <v>53.33610534667969</v>
       </c>
       <c r="C189" t="n">
         <v>62</v>
@@ -5418,11 +5430,11 @@
       </c>
     </row>
     <row r="190">
-      <c r="A190" s="1" t="n">
+      <c r="A190" s="2" t="n">
         <v>44469</v>
       </c>
       <c r="B190" t="n">
-        <v>53.10383224487305</v>
+        <v>53.10383605957031</v>
       </c>
       <c r="C190" t="n">
         <v>61.72999954223633</v>
@@ -5447,11 +5459,11 @@
       </c>
     </row>
     <row r="191">
-      <c r="A191" s="1" t="n">
+      <c r="A191" s="2" t="n">
         <v>44500</v>
       </c>
       <c r="B191" t="n">
-        <v>54.02430725097656</v>
+        <v>54.02431869506836</v>
       </c>
       <c r="C191" t="n">
         <v>62.79999923706055</v>
@@ -5476,11 +5488,11 @@
       </c>
     </row>
     <row r="192">
-      <c r="A192" s="1" t="n">
+      <c r="A192" s="2" t="n">
         <v>44530</v>
       </c>
       <c r="B192" t="n">
-        <v>50.84422302246094</v>
+        <v>50.8442268371582</v>
       </c>
       <c r="C192" t="n">
         <v>58.65999984741211</v>
@@ -5505,7 +5517,7 @@
       </c>
     </row>
     <row r="193">
-      <c r="A193" s="1" t="n">
+      <c r="A193" s="2" t="n">
         <v>44561</v>
       </c>
       <c r="B193" t="n">
@@ -5534,11 +5546,11 @@
       </c>
     </row>
     <row r="194">
-      <c r="A194" s="1" t="n">
+      <c r="A194" s="2" t="n">
         <v>44592</v>
       </c>
       <c r="B194" t="n">
-        <v>58.12501907348633</v>
+        <v>58.12502288818359</v>
       </c>
       <c r="C194" t="n">
         <v>67.05999755859375</v>
@@ -5563,11 +5575,11 @@
       </c>
     </row>
     <row r="195">
-      <c r="A195" s="1" t="n">
+      <c r="A195" s="2" t="n">
         <v>44620</v>
       </c>
       <c r="B195" t="n">
-        <v>58.9599494934082</v>
+        <v>58.95996475219727</v>
       </c>
       <c r="C195" t="n">
         <v>67.55000305175781</v>
@@ -5592,11 +5604,11 @@
       </c>
     </row>
     <row r="196">
-      <c r="A196" s="1" t="n">
+      <c r="A196" s="2" t="n">
         <v>44651</v>
       </c>
       <c r="B196" t="n">
-        <v>61.34280014038086</v>
+        <v>61.34278869628906</v>
       </c>
       <c r="C196" t="n">
         <v>70.27999877929688</v>
@@ -5621,11 +5633,11 @@
       </c>
     </row>
     <row r="197">
-      <c r="A197" s="1" t="n">
+      <c r="A197" s="2" t="n">
         <v>44681</v>
       </c>
       <c r="B197" t="n">
-        <v>57.32776260375977</v>
+        <v>57.32775115966797</v>
       </c>
       <c r="C197" t="n">
         <v>65.68000030517578</v>
@@ -5650,11 +5662,11 @@
       </c>
     </row>
     <row r="198">
-      <c r="A198" s="1" t="n">
+      <c r="A198" s="2" t="n">
         <v>44712</v>
       </c>
       <c r="B198" t="n">
-        <v>59.25900268554688</v>
+        <v>59.25899505615234</v>
       </c>
       <c r="C198" t="n">
         <v>67.38999938964844</v>
@@ -5679,11 +5691,11 @@
       </c>
     </row>
     <row r="199">
-      <c r="A199" s="1" t="n">
+      <c r="A199" s="2" t="n">
         <v>44742</v>
       </c>
       <c r="B199" t="n">
-        <v>55.21402359008789</v>
+        <v>55.21401977539062</v>
       </c>
       <c r="C199" t="n">
         <v>62.79000091552734</v>
@@ -5708,11 +5720,11 @@
       </c>
     </row>
     <row r="200">
-      <c r="A200" s="1" t="n">
+      <c r="A200" s="2" t="n">
         <v>44773</v>
       </c>
       <c r="B200" t="n">
-        <v>55.6185188293457</v>
+        <v>55.61851119995117</v>
       </c>
       <c r="C200" t="n">
         <v>63.25</v>
@@ -5737,11 +5749,11 @@
       </c>
     </row>
     <row r="201">
-      <c r="A201" s="1" t="n">
+      <c r="A201" s="2" t="n">
         <v>44804</v>
       </c>
       <c r="B201" t="n">
-        <v>57.01858520507812</v>
+        <v>57.01858139038086</v>
       </c>
       <c r="C201" t="n">
         <v>64.33000183105469</v>
@@ -5766,11 +5778,11 @@
       </c>
     </row>
     <row r="202">
-      <c r="A202" s="1" t="n">
+      <c r="A202" s="2" t="n">
         <v>44834</v>
       </c>
       <c r="B202" t="n">
-        <v>53.8720703125</v>
+        <v>53.87206649780273</v>
       </c>
       <c r="C202" t="n">
         <v>60.77999877929688</v>
@@ -5795,11 +5807,11 @@
       </c>
     </row>
     <row r="203">
-      <c r="A203" s="1" t="n">
+      <c r="A203" s="2" t="n">
         <v>44865</v>
       </c>
       <c r="B203" t="n">
-        <v>64.88932800292969</v>
+        <v>64.88933563232422</v>
       </c>
       <c r="C203" t="n">
         <v>73.20999908447266</v>
@@ -5824,11 +5836,11 @@
       </c>
     </row>
     <row r="204">
-      <c r="A204" s="1" t="n">
+      <c r="A204" s="2" t="n">
         <v>44895</v>
       </c>
       <c r="B204" t="n">
-        <v>68.4444580078125</v>
+        <v>68.44445037841797</v>
       </c>
       <c r="C204" t="n">
         <v>76.69999694824219</v>
@@ -5853,11 +5865,11 @@
       </c>
     </row>
     <row r="205">
-      <c r="A205" s="1" t="n">
+      <c r="A205" s="2" t="n">
         <v>44926</v>
       </c>
       <c r="B205" t="n">
-        <v>64.58051300048828</v>
+        <v>64.58049774169922</v>
       </c>
       <c r="C205" t="n">
         <v>72.37000274658203</v>
@@ -5882,7 +5894,7 @@
       </c>
     </row>
     <row r="206">
-      <c r="A206" s="1" t="n">
+      <c r="A206" s="2" t="n">
         <v>44957</v>
       </c>
       <c r="B206" t="n">
@@ -5911,11 +5923,11 @@
       </c>
     </row>
     <row r="207">
-      <c r="A207" s="1" t="n">
+      <c r="A207" s="2" t="n">
         <v>44985</v>
       </c>
       <c r="B207" t="n">
-        <v>64.47130584716797</v>
+        <v>64.47129821777344</v>
       </c>
       <c r="C207" t="n">
         <v>71.73000335693359</v>
@@ -5940,7 +5952,7 @@
       </c>
     </row>
     <row r="208">
-      <c r="A208" s="1" t="n">
+      <c r="A208" s="2" t="n">
         <v>45016</v>
       </c>
       <c r="B208" t="n">
@@ -5969,11 +5981,11 @@
       </c>
     </row>
     <row r="209">
-      <c r="A209" s="1" t="n">
+      <c r="A209" s="2" t="n">
         <v>45046</v>
       </c>
       <c r="B209" t="n">
-        <v>55.12372207641602</v>
+        <v>55.12371444702148</v>
       </c>
       <c r="C209" t="n">
         <v>61.33000183105469</v>
@@ -5998,7 +6010,7 @@
       </c>
     </row>
     <row r="210">
-      <c r="A210" s="1" t="n">
+      <c r="A210" s="2" t="n">
         <v>45077</v>
       </c>
       <c r="B210" t="n">
@@ -6027,7 +6039,7 @@
       </c>
     </row>
     <row r="211">
-      <c r="A211" s="1" t="n">
+      <c r="A211" s="2" t="n">
         <v>45107</v>
       </c>
       <c r="B211" t="n">
@@ -6056,11 +6068,11 @@
       </c>
     </row>
     <row r="212">
-      <c r="A212" s="1" t="n">
+      <c r="A212" s="2" t="n">
         <v>45138</v>
       </c>
       <c r="B212" t="n">
-        <v>57.14136505126953</v>
+        <v>57.14137268066406</v>
       </c>
       <c r="C212" t="n">
         <v>62.97000122070312</v>
@@ -6085,11 +6097,11 @@
       </c>
     </row>
     <row r="213">
-      <c r="A213" s="1" t="n">
+      <c r="A213" s="2" t="n">
         <v>45169</v>
       </c>
       <c r="B213" t="n">
-        <v>57.95145797729492</v>
+        <v>57.95145416259766</v>
       </c>
       <c r="C213" t="n">
         <v>63.34000015258789</v>
@@ -6114,7 +6126,7 @@
       </c>
     </row>
     <row r="214">
-      <c r="A214" s="1" t="n">
+      <c r="A214" s="2" t="n">
         <v>45199</v>
       </c>
       <c r="B214" t="n">
@@ -6143,11 +6155,11 @@
       </c>
     </row>
     <row r="215">
-      <c r="A215" s="1" t="n">
+      <c r="A215" s="2" t="n">
         <v>45230</v>
       </c>
       <c r="B215" t="n">
-        <v>54.90474700927734</v>
+        <v>54.90475082397461</v>
       </c>
       <c r="C215" t="n">
         <v>60.0099983215332</v>
@@ -6172,11 +6184,11 @@
       </c>
     </row>
     <row r="216">
-      <c r="A216" s="1" t="n">
+      <c r="A216" s="2" t="n">
         <v>45260</v>
       </c>
       <c r="B216" t="n">
-        <v>58.72531509399414</v>
+        <v>58.72531127929688</v>
       </c>
       <c r="C216" t="n">
         <v>63.63000106811523</v>
@@ -6201,7 +6213,7 @@
       </c>
     </row>
     <row r="217">
-      <c r="A217" s="1" t="n">
+      <c r="A217" s="2" t="n">
         <v>45291</v>
       </c>
       <c r="B217" t="n">
@@ -6230,11 +6242,11 @@
       </c>
     </row>
     <row r="218">
-      <c r="A218" s="1" t="n">
+      <c r="A218" s="2" t="n">
         <v>45322</v>
       </c>
       <c r="B218" t="n">
-        <v>63.97672271728516</v>
+        <v>63.97672653198242</v>
       </c>
       <c r="C218" t="n">
         <v>69.31999969482422</v>
@@ -6259,11 +6271,11 @@
       </c>
     </row>
     <row r="219">
-      <c r="A219" s="1" t="n">
+      <c r="A219" s="2" t="n">
         <v>45351</v>
       </c>
       <c r="B219" t="n">
-        <v>64.87587738037109</v>
+        <v>64.87586975097656</v>
       </c>
       <c r="C219" t="n">
         <v>69.73999786376953</v>
@@ -6288,11 +6300,11 @@
       </c>
     </row>
     <row r="220">
-      <c r="A220" s="1" t="n">
+      <c r="A220" s="2" t="n">
         <v>45382</v>
       </c>
       <c r="B220" t="n">
-        <v>68.94107818603516</v>
+        <v>68.94107055664062</v>
       </c>
       <c r="C220" t="n">
         <v>74.11000061035156</v>
@@ -6317,7 +6329,7 @@
       </c>
     </row>
     <row r="221">
-      <c r="A221" s="1" t="n">
+      <c r="A221" s="2" t="n">
         <v>45412</v>
       </c>
       <c r="B221" t="n">
@@ -6346,7 +6358,7 @@
       </c>
     </row>
     <row r="222">
-      <c r="A222" s="1" t="n">
+      <c r="A222" s="2" t="n">
         <v>45443</v>
       </c>
       <c r="B222" t="n">
@@ -6375,11 +6387,11 @@
       </c>
     </row>
     <row r="223">
-      <c r="A223" s="1" t="n">
+      <c r="A223" s="2" t="n">
         <v>45473</v>
       </c>
       <c r="B223" t="n">
-        <v>65.80303192138672</v>
+        <v>65.80303955078125</v>
       </c>
       <c r="C223" t="n">
         <v>70.19000244140625</v>
@@ -6404,7 +6416,7 @@
       </c>
     </row>
     <row r="224">
-      <c r="A224" s="1" t="n">
+      <c r="A224" s="2" t="n">
         <v>45504</v>
       </c>
       <c r="B224" t="n">
@@ -6433,7 +6445,7 @@
       </c>
     </row>
     <row r="225">
-      <c r="A225" s="1" t="n">
+      <c r="A225" s="2" t="n">
         <v>45535</v>
       </c>
       <c r="B225" t="n">
@@ -6462,7 +6474,7 @@
       </c>
     </row>
     <row r="226">
-      <c r="A226" s="1" t="n">
+      <c r="A226" s="2" t="n">
         <v>45565</v>
       </c>
       <c r="B226" t="n">
@@ -6491,11 +6503,11 @@
       </c>
     </row>
     <row r="227">
-      <c r="A227" s="1" t="n">
+      <c r="A227" s="2" t="n">
         <v>45596</v>
       </c>
       <c r="B227" t="n">
-        <v>74.11297607421875</v>
+        <v>74.11298370361328</v>
       </c>
       <c r="C227" t="n">
         <v>78.41999816894531</v>
@@ -6520,11 +6532,11 @@
       </c>
     </row>
     <row r="228">
-      <c r="A228" s="1" t="n">
+      <c r="A228" s="2" t="n">
         <v>45626</v>
       </c>
       <c r="B228" t="n">
-        <v>83.96672058105469</v>
+        <v>83.96671295166016</v>
       </c>
       <c r="C228" t="n">
         <v>88.23000335693359</v>
@@ -6549,7 +6561,7 @@
       </c>
     </row>
     <row r="229">
-      <c r="A229" s="1" t="n">
+      <c r="A229" s="2" t="n">
         <v>45657</v>
       </c>
       <c r="B229" t="n">
@@ -6578,11 +6590,11 @@
       </c>
     </row>
     <row r="230">
-      <c r="A230" s="1" t="n">
+      <c r="A230" s="2" t="n">
         <v>45688</v>
       </c>
       <c r="B230" t="n">
-        <v>82.32981872558594</v>
+        <v>82.32982635498047</v>
       </c>
       <c r="C230" t="n">
         <v>86.51000213623047</v>
@@ -6607,11 +6619,11 @@
       </c>
     </row>
     <row r="231">
-      <c r="A231" s="1" t="n">
+      <c r="A231" s="2" t="n">
         <v>45716</v>
       </c>
       <c r="B231" t="n">
-        <v>82.54196929931641</v>
+        <v>82.54198455810547</v>
       </c>
       <c r="C231" t="n">
         <v>86.18000030517578</v>
@@ -6636,11 +6648,11 @@
       </c>
     </row>
     <row r="232">
-      <c r="A232" s="1" t="n">
+      <c r="A232" s="2" t="n">
         <v>45747</v>
       </c>
       <c r="B232" t="n">
-        <v>76.90062713623047</v>
+        <v>76.90061950683594</v>
       </c>
       <c r="C232" t="n">
         <v>80.29000091552734</v>
@@ -6665,7 +6677,7 @@
       </c>
     </row>
     <row r="233">
-      <c r="A233" s="1" t="n">
+      <c r="A233" s="2" t="n">
         <v>45777</v>
       </c>
       <c r="B233" t="n">
@@ -6694,7 +6706,7 @@
       </c>
     </row>
     <row r="234">
-      <c r="A234" s="1" t="n">
+      <c r="A234" s="2" t="n">
         <v>45808</v>
       </c>
       <c r="B234" t="n">
@@ -6723,11 +6735,11 @@
       </c>
     </row>
     <row r="235">
-      <c r="A235" s="1" t="n">
+      <c r="A235" s="2" t="n">
         <v>45838</v>
       </c>
       <c r="B235" t="n">
-        <v>77.59449005126953</v>
+        <v>77.594482421875</v>
       </c>
       <c r="C235" t="n">
         <v>80.41999816894531</v>
@@ -6752,7 +6764,7 @@
       </c>
     </row>
     <row r="236">
-      <c r="A236" s="1" t="n">
+      <c r="A236" s="2" t="n">
         <v>45869</v>
       </c>
       <c r="B236" t="n">
@@ -6781,7 +6793,7 @@
       </c>
     </row>
     <row r="237">
-      <c r="A237" s="1" t="n">
+      <c r="A237" s="2" t="n">
         <v>45900</v>
       </c>
       <c r="B237" t="n">
@@ -6810,11 +6822,11 @@
       </c>
     </row>
     <row r="238">
-      <c r="A238" s="1" t="n">
+      <c r="A238" s="2" t="n">
         <v>45930</v>
       </c>
       <c r="B238" t="n">
-        <v>80.08384704589844</v>
+        <v>80.0838623046875</v>
       </c>
       <c r="C238" t="n">
         <v>82.37000274658203</v>
@@ -6839,11 +6851,11 @@
       </c>
     </row>
     <row r="239">
-      <c r="A239" s="1" t="n">
+      <c r="A239" s="2" t="n">
         <v>45961</v>
       </c>
       <c r="B239" t="n">
-        <v>77.6046142578125</v>
+        <v>77.60462188720703</v>
       </c>
       <c r="C239" t="n">
         <v>79.81999969482422</v>
@@ -6868,11 +6880,11 @@
       </c>
     </row>
     <row r="240">
-      <c r="A240" s="1" t="n">
+      <c r="A240" s="2" t="n">
         <v>45991</v>
       </c>
       <c r="B240" t="n">
-        <v>74.97272491455078</v>
+        <v>74.97271728515625</v>
       </c>
       <c r="C240" t="n">
         <v>76.55999755859375</v>
@@ -6897,7 +6909,7 @@
       </c>
     </row>
     <row r="241">
-      <c r="A241" s="1" t="n">
+      <c r="A241" s="2" t="n">
         <v>46022</v>
       </c>
       <c r="B241" t="n">
@@ -6926,11 +6938,11 @@
       </c>
     </row>
     <row r="242">
-      <c r="A242" s="1" t="n">
+      <c r="A242" s="2" t="n">
         <v>46053</v>
       </c>
       <c r="B242" t="n">
-        <v>77.24462127685547</v>
+        <v>77.24461364746094</v>
       </c>
       <c r="C242" t="n">
         <v>78.87999725341797</v>
@@ -6955,7 +6967,7 @@
       </c>
     </row>
     <row r="243">
-      <c r="A243" s="1" t="n">
+      <c r="A243" s="2" t="n">
         <v>46081</v>
       </c>
       <c r="B243" t="n">
@@ -6984,7 +6996,7 @@
       </c>
     </row>
     <row r="244">
-      <c r="A244" s="1" t="n">
+      <c r="A244" s="2" t="n">
         <v>46112</v>
       </c>
       <c r="B244" t="n">
@@ -7013,7 +7025,7 @@
       </c>
     </row>
     <row r="245">
-      <c r="A245" s="1" t="n">
+      <c r="A245" s="2" t="n">
         <v>46142</v>
       </c>
       <c r="B245" t="n">
@@ -7042,7 +7054,7 @@
       </c>
     </row>
     <row r="246">
-      <c r="A246" s="1" t="n">
+      <c r="A246" s="2" t="n">
         <v>46173</v>
       </c>
       <c r="B246" t="n">
@@ -7071,7 +7083,7 @@
       </c>
     </row>
     <row r="247">
-      <c r="A247" s="1" t="n">
+      <c r="A247" s="2" t="n">
         <v>46203</v>
       </c>
       <c r="B247" t="n">
@@ -7100,7 +7112,7 @@
       </c>
     </row>
     <row r="248">
-      <c r="A248" s="1" t="n">
+      <c r="A248" s="2" t="n">
         <v>46234</v>
       </c>
       <c r="B248" t="n">
@@ -7129,7 +7141,7 @@
       </c>
     </row>
     <row r="249">
-      <c r="A249" s="1" t="n">
+      <c r="A249" s="2" t="n">
         <v>46265</v>
       </c>
       <c r="B249" t="n">
@@ -7158,32 +7170,32 @@
       </c>
     </row>
     <row r="250">
-      <c r="A250" s="1" t="n">
+      <c r="A250" s="2" t="n">
         <v>46295</v>
       </c>
       <c r="B250" t="n">
-        <v>97.19999694824219</v>
+        <v>97.25</v>
       </c>
       <c r="C250" t="n">
-        <v>97.19999694824219</v>
+        <v>97.25</v>
       </c>
       <c r="D250" t="n">
-        <v>48733400</v>
+        <v>52176300</v>
       </c>
       <c r="E250" t="n">
         <v>5.23</v>
       </c>
       <c r="F250" t="n">
-        <v>18.58508545855491</v>
+        <v>18.59464627151052</v>
       </c>
       <c r="G250" t="n">
         <v>635476927</v>
       </c>
       <c r="H250" t="n">
-        <v>61768355365.07832</v>
+        <v>61800131150.75</v>
       </c>
       <c r="I250" t="n">
-        <v>0.07668791411525158</v>
+        <v>0.08210573473739984</v>
       </c>
     </row>
   </sheetData>
@@ -7215,75 +7227,75 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>start</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>end</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>filed</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>form</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>fy</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>fp</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>eps_trimestral</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>origen</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>eps_ttm</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>filed_ttm</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>factor</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>tag</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" s="2" t="n">
         <v>39539</v>
       </c>
-      <c r="B2" s="1" t="n">
+      <c r="B2" s="2" t="n">
         <v>39629</v>
       </c>
-      <c r="C2" s="1" t="n">
+      <c r="C2" s="2" t="n">
         <v>40029</v>
       </c>
       <c r="D2" t="inlineStr">
@@ -7319,13 +7331,13 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" s="2" t="n">
         <v>39630</v>
       </c>
-      <c r="B3" s="1" t="n">
+      <c r="B3" s="2" t="n">
         <v>39721</v>
       </c>
-      <c r="C3" s="1" t="n">
+      <c r="C3" s="2" t="n">
         <v>40121</v>
       </c>
       <c r="D3" t="inlineStr">
@@ -7361,13 +7373,13 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" s="2" t="n">
         <v>39814</v>
       </c>
-      <c r="B4" s="1" t="n">
+      <c r="B4" s="2" t="n">
         <v>39903</v>
       </c>
-      <c r="C4" s="1" t="n">
+      <c r="C4" s="2" t="n">
         <v>40303</v>
       </c>
       <c r="D4" t="inlineStr">
@@ -7403,13 +7415,13 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" s="2" t="n">
         <v>39904</v>
       </c>
-      <c r="B5" s="1" t="n">
+      <c r="B5" s="2" t="n">
         <v>39994</v>
       </c>
-      <c r="C5" s="1" t="n">
+      <c r="C5" s="2" t="n">
         <v>40029</v>
       </c>
       <c r="D5" t="inlineStr">
@@ -7445,13 +7457,13 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" s="2" t="n">
         <v>39995</v>
       </c>
-      <c r="B6" s="1" t="n">
+      <c r="B6" s="2" t="n">
         <v>40086</v>
       </c>
-      <c r="C6" s="1" t="n">
+      <c r="C6" s="2" t="n">
         <v>40121</v>
       </c>
       <c r="D6" t="inlineStr">
@@ -7487,13 +7499,13 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="A7" s="2" t="n">
         <v>40087</v>
       </c>
-      <c r="B7" s="1" t="n">
+      <c r="B7" s="2" t="n">
         <v>40178</v>
       </c>
-      <c r="C7" s="1" t="n">
+      <c r="C7" s="2" t="n">
         <v>40599</v>
       </c>
       <c r="D7" t="inlineStr">
@@ -7520,7 +7532,7 @@
       <c r="I7" t="n">
         <v>-2.575757575757576</v>
       </c>
-      <c r="J7" s="1" t="n">
+      <c r="J7" s="2" t="n">
         <v>40599</v>
       </c>
       <c r="K7" t="n">
@@ -7533,13 +7545,13 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="A8" s="2" t="n">
         <v>40179</v>
       </c>
-      <c r="B8" s="1" t="n">
+      <c r="B8" s="2" t="n">
         <v>40268</v>
       </c>
-      <c r="C8" s="1" t="n">
+      <c r="C8" s="2" t="n">
         <v>40303</v>
       </c>
       <c r="D8" t="inlineStr">
@@ -7566,7 +7578,7 @@
       <c r="I8" t="n">
         <v>-1.07843137254902</v>
       </c>
-      <c r="J8" s="1" t="n">
+      <c r="J8" s="2" t="n">
         <v>40599</v>
       </c>
       <c r="K8" t="n">
@@ -7579,13 +7591,13 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
+      <c r="A9" s="2" t="n">
         <v>40269</v>
       </c>
-      <c r="B9" s="1" t="n">
+      <c r="B9" s="2" t="n">
         <v>40359</v>
       </c>
-      <c r="C9" s="1" t="n">
+      <c r="C9" s="2" t="n">
         <v>40392</v>
       </c>
       <c r="D9" t="inlineStr">
@@ -7612,7 +7624,7 @@
       <c r="I9" t="n">
         <v>2.112299465240642</v>
       </c>
-      <c r="J9" s="1" t="n">
+      <c r="J9" s="2" t="n">
         <v>40599</v>
       </c>
       <c r="K9" t="n">
@@ -7625,13 +7637,13 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
+      <c r="A10" s="2" t="n">
         <v>40360</v>
       </c>
-      <c r="B10" s="1" t="n">
+      <c r="B10" s="2" t="n">
         <v>40451</v>
       </c>
-      <c r="C10" s="1" t="n">
+      <c r="C10" s="2" t="n">
         <v>40486</v>
       </c>
       <c r="D10" t="inlineStr">
@@ -7658,7 +7670,7 @@
       <c r="I10" t="n">
         <v>3.101604278074866</v>
       </c>
-      <c r="J10" s="1" t="n">
+      <c r="J10" s="2" t="n">
         <v>40599</v>
       </c>
       <c r="K10" t="n">
@@ -7671,13 +7683,13 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
+      <c r="A11" s="2" t="n">
         <v>40452</v>
       </c>
-      <c r="B11" s="1" t="n">
+      <c r="B11" s="2" t="n">
         <v>40543</v>
       </c>
-      <c r="C11" s="1" t="n">
+      <c r="C11" s="2" t="n">
         <v>40599</v>
       </c>
       <c r="D11" t="inlineStr">
@@ -7704,7 +7716,7 @@
       <c r="I11" t="n">
         <v>2.834224598930481</v>
       </c>
-      <c r="J11" s="1" t="n">
+      <c r="J11" s="2" t="n">
         <v>40599</v>
       </c>
       <c r="K11" t="n">
@@ -7717,13 +7729,13 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
+      <c r="A12" s="2" t="n">
         <v>40544</v>
       </c>
-      <c r="B12" s="1" t="n">
+      <c r="B12" s="2" t="n">
         <v>40633</v>
       </c>
-      <c r="C12" s="1" t="n">
+      <c r="C12" s="2" t="n">
         <v>40673</v>
       </c>
       <c r="D12" t="inlineStr">
@@ -7750,7 +7762,7 @@
       <c r="I12" t="n">
         <v>2.664884135472371</v>
       </c>
-      <c r="J12" s="1" t="n">
+      <c r="J12" s="2" t="n">
         <v>40673</v>
       </c>
       <c r="K12" t="n">
@@ -7763,13 +7775,13 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n">
+      <c r="A13" s="2" t="n">
         <v>40634</v>
       </c>
-      <c r="B13" s="1" t="n">
+      <c r="B13" s="2" t="n">
         <v>40724</v>
       </c>
-      <c r="C13" s="1" t="n">
+      <c r="C13" s="2" t="n">
         <v>40760</v>
       </c>
       <c r="D13" t="inlineStr">
@@ -7796,7 +7808,7 @@
       <c r="I13" t="n">
         <v>2.032085561497326</v>
       </c>
-      <c r="J13" s="1" t="n">
+      <c r="J13" s="2" t="n">
         <v>40760</v>
       </c>
       <c r="K13" t="n">
@@ -7809,13 +7821,13 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n">
+      <c r="A14" s="2" t="n">
         <v>40725</v>
       </c>
-      <c r="B14" s="1" t="n">
+      <c r="B14" s="2" t="n">
         <v>40816</v>
       </c>
-      <c r="C14" s="1" t="n">
+      <c r="C14" s="2" t="n">
         <v>40851</v>
       </c>
       <c r="D14" t="inlineStr">
@@ -7842,7 +7854,7 @@
       <c r="I14" t="n">
         <v>4.714795008912656</v>
       </c>
-      <c r="J14" s="1" t="n">
+      <c r="J14" s="2" t="n">
         <v>40851</v>
       </c>
       <c r="K14" t="n">
@@ -7855,13 +7867,13 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n">
+      <c r="A15" s="2" t="n">
         <v>40817</v>
       </c>
-      <c r="B15" s="1" t="n">
+      <c r="B15" s="2" t="n">
         <v>40908</v>
       </c>
-      <c r="C15" s="1" t="n">
+      <c r="C15" s="2" t="n">
         <v>40967</v>
       </c>
       <c r="D15" t="inlineStr">
@@ -7888,7 +7900,7 @@
       <c r="I15" t="n">
         <v>5.614973262032085</v>
       </c>
-      <c r="J15" s="1" t="n">
+      <c r="J15" s="2" t="n">
         <v>40967</v>
       </c>
       <c r="K15" t="n">
@@ -7901,13 +7913,13 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n">
+      <c r="A16" s="2" t="n">
         <v>40909</v>
       </c>
-      <c r="B16" s="1" t="n">
+      <c r="B16" s="2" t="n">
         <v>40999</v>
       </c>
-      <c r="C16" s="1" t="n">
+      <c r="C16" s="2" t="n">
         <v>41037</v>
       </c>
       <c r="D16" t="inlineStr">
@@ -7934,7 +7946,7 @@
       <c r="I16" t="n">
         <v>4.777183600713013</v>
       </c>
-      <c r="J16" s="1" t="n">
+      <c r="J16" s="2" t="n">
         <v>41037</v>
       </c>
       <c r="K16" t="n">
@@ -7947,13 +7959,13 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n">
+      <c r="A17" s="2" t="n">
         <v>41000</v>
       </c>
-      <c r="B17" s="1" t="n">
+      <c r="B17" s="2" t="n">
         <v>41090</v>
       </c>
-      <c r="C17" s="1" t="n">
+      <c r="C17" s="2" t="n">
         <v>41128</v>
       </c>
       <c r="D17" t="inlineStr">
@@ -7980,7 +7992,7 @@
       <c r="I17" t="n">
         <v>5.659536541889483</v>
       </c>
-      <c r="J17" s="1" t="n">
+      <c r="J17" s="2" t="n">
         <v>41128</v>
       </c>
       <c r="K17" t="n">
@@ -7993,13 +8005,13 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="n">
+      <c r="A18" s="2" t="n">
         <v>41091</v>
       </c>
-      <c r="B18" s="1" t="n">
+      <c r="B18" s="2" t="n">
         <v>41182</v>
       </c>
-      <c r="C18" s="1" t="n">
+      <c r="C18" s="2" t="n">
         <v>41220</v>
       </c>
       <c r="D18" t="inlineStr">
@@ -8026,7 +8038,7 @@
       <c r="I18" t="n">
         <v>1.871657754010695</v>
       </c>
-      <c r="J18" s="1" t="n">
+      <c r="J18" s="2" t="n">
         <v>41220</v>
       </c>
       <c r="K18" t="n">
@@ -8039,13 +8051,13 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="n">
+      <c r="A19" s="2" t="n">
         <v>41183</v>
       </c>
-      <c r="B19" s="1" t="n">
+      <c r="B19" s="2" t="n">
         <v>41274</v>
       </c>
-      <c r="C19" s="1" t="n">
+      <c r="C19" s="2" t="n">
         <v>41332</v>
       </c>
       <c r="D19" t="inlineStr">
@@ -8072,7 +8084,7 @@
       <c r="I19" t="n">
         <v>1.007130124777183</v>
       </c>
-      <c r="J19" s="1" t="n">
+      <c r="J19" s="2" t="n">
         <v>41332</v>
       </c>
       <c r="K19" t="n">
@@ -8085,13 +8097,13 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="n">
+      <c r="A20" s="2" t="n">
         <v>41275</v>
       </c>
-      <c r="B20" s="1" t="n">
+      <c r="B20" s="2" t="n">
         <v>41364</v>
       </c>
-      <c r="C20" s="1" t="n">
+      <c r="C20" s="2" t="n">
         <v>41401</v>
       </c>
       <c r="D20" t="inlineStr">
@@ -8118,7 +8130,7 @@
       <c r="I20" t="n">
         <v>1.925133689839572</v>
       </c>
-      <c r="J20" s="1" t="n">
+      <c r="J20" s="2" t="n">
         <v>41401</v>
       </c>
       <c r="K20" t="n">
@@ -8131,13 +8143,13 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="n">
+      <c r="A21" s="2" t="n">
         <v>41365</v>
       </c>
-      <c r="B21" s="1" t="n">
+      <c r="B21" s="2" t="n">
         <v>41455</v>
       </c>
-      <c r="C21" s="1" t="n">
+      <c r="C21" s="2" t="n">
         <v>41493</v>
       </c>
       <c r="D21" t="inlineStr">
@@ -8164,7 +8176,7 @@
       <c r="I21" t="n">
         <v>0.4188948306595363</v>
       </c>
-      <c r="J21" s="1" t="n">
+      <c r="J21" s="2" t="n">
         <v>41493</v>
       </c>
       <c r="K21" t="n">
@@ -8177,13 +8189,13 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="n">
+      <c r="A22" s="2" t="n">
         <v>41456</v>
       </c>
-      <c r="B22" s="1" t="n">
+      <c r="B22" s="2" t="n">
         <v>41547</v>
       </c>
-      <c r="C22" s="1" t="n">
+      <c r="C22" s="2" t="n">
         <v>41585</v>
       </c>
       <c r="D22" t="inlineStr">
@@ -8210,7 +8222,7 @@
       <c r="I22" t="n">
         <v>1.987522281639928</v>
       </c>
-      <c r="J22" s="1" t="n">
+      <c r="J22" s="2" t="n">
         <v>41585</v>
       </c>
       <c r="K22" t="n">
@@ -8223,13 +8235,13 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="n">
+      <c r="A23" s="2" t="n">
         <v>41548</v>
       </c>
-      <c r="B23" s="1" t="n">
+      <c r="B23" s="2" t="n">
         <v>41639</v>
       </c>
-      <c r="C23" s="1" t="n">
+      <c r="C23" s="2" t="n">
         <v>41697</v>
       </c>
       <c r="D23" t="inlineStr">
@@ -8256,7 +8268,7 @@
       <c r="I23" t="n">
         <v>2.593582887700534</v>
       </c>
-      <c r="J23" s="1" t="n">
+      <c r="J23" s="2" t="n">
         <v>41697</v>
       </c>
       <c r="K23" t="n">
@@ -8269,13 +8281,13 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="n">
+      <c r="A24" s="2" t="n">
         <v>41640</v>
       </c>
-      <c r="B24" s="1" t="n">
+      <c r="B24" s="2" t="n">
         <v>41729</v>
       </c>
-      <c r="C24" s="1" t="n">
+      <c r="C24" s="2" t="n">
         <v>41767</v>
       </c>
       <c r="D24" t="inlineStr">
@@ -8302,7 +8314,7 @@
       <c r="I24" t="n">
         <v>2.834224598930481</v>
       </c>
-      <c r="J24" s="1" t="n">
+      <c r="J24" s="2" t="n">
         <v>41767</v>
       </c>
       <c r="K24" t="n">
@@ -8315,13 +8327,13 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="n">
+      <c r="A25" s="2" t="n">
         <v>41730</v>
       </c>
-      <c r="B25" s="1" t="n">
+      <c r="B25" s="2" t="n">
         <v>41820</v>
       </c>
-      <c r="C25" s="1" t="n">
+      <c r="C25" s="2" t="n">
         <v>41859</v>
       </c>
       <c r="D25" t="inlineStr">
@@ -8348,7 +8360,7 @@
       <c r="I25" t="n">
         <v>3.493761140819964</v>
       </c>
-      <c r="J25" s="1" t="n">
+      <c r="J25" s="2" t="n">
         <v>41859</v>
       </c>
       <c r="K25" t="n">
@@ -8361,13 +8373,13 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="n">
+      <c r="A26" s="2" t="n">
         <v>41821</v>
       </c>
-      <c r="B26" s="1" t="n">
+      <c r="B26" s="2" t="n">
         <v>41912</v>
       </c>
-      <c r="C26" s="1" t="n">
+      <c r="C26" s="2" t="n">
         <v>41949</v>
       </c>
       <c r="D26" t="inlineStr">
@@ -8394,7 +8406,7 @@
       <c r="I26" t="n">
         <v>4.358288770053475</v>
       </c>
-      <c r="J26" s="1" t="n">
+      <c r="J26" s="2" t="n">
         <v>41949</v>
       </c>
       <c r="K26" t="n">
@@ -8407,13 +8419,13 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="n">
+      <c r="A27" s="2" t="n">
         <v>41913</v>
       </c>
-      <c r="B27" s="1" t="n">
+      <c r="B27" s="2" t="n">
         <v>42004</v>
       </c>
-      <c r="C27" s="1" t="n">
+      <c r="C27" s="2" t="n">
         <v>42062</v>
       </c>
       <c r="D27" t="inlineStr">
@@ -8440,7 +8452,7 @@
       <c r="I27" t="n">
         <v>4.830659536541889</v>
       </c>
-      <c r="J27" s="1" t="n">
+      <c r="J27" s="2" t="n">
         <v>42062</v>
       </c>
       <c r="K27" t="n">
@@ -8453,13 +8465,13 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="n">
+      <c r="A28" s="2" t="n">
         <v>42005</v>
       </c>
-      <c r="B28" s="1" t="n">
+      <c r="B28" s="2" t="n">
         <v>42094</v>
       </c>
-      <c r="C28" s="1" t="n">
+      <c r="C28" s="2" t="n">
         <v>42132</v>
       </c>
       <c r="D28" t="inlineStr">
@@ -8486,7 +8498,7 @@
       <c r="I28" t="n">
         <v>5.481283422459892</v>
       </c>
-      <c r="J28" s="1" t="n">
+      <c r="J28" s="2" t="n">
         <v>42132</v>
       </c>
       <c r="K28" t="n">
@@ -8499,13 +8511,13 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="n">
+      <c r="A29" s="2" t="n">
         <v>42095</v>
       </c>
-      <c r="B29" s="1" t="n">
+      <c r="B29" s="2" t="n">
         <v>42185</v>
       </c>
-      <c r="C29" s="1" t="n">
+      <c r="C29" s="2" t="n">
         <v>42222</v>
       </c>
       <c r="D29" t="inlineStr">
@@ -8532,7 +8544,7 @@
       <c r="I29" t="n">
         <v>5.258467023172904</v>
       </c>
-      <c r="J29" s="1" t="n">
+      <c r="J29" s="2" t="n">
         <v>42222</v>
       </c>
       <c r="K29" t="n">
@@ -8545,13 +8557,13 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="n">
+      <c r="A30" s="2" t="n">
         <v>42186</v>
       </c>
-      <c r="B30" s="1" t="n">
+      <c r="B30" s="2" t="n">
         <v>42277</v>
       </c>
-      <c r="C30" s="1" t="n">
+      <c r="C30" s="2" t="n">
         <v>42313</v>
       </c>
       <c r="D30" t="inlineStr">
@@ -8578,7 +8590,7 @@
       <c r="I30" t="n">
         <v>4.590017825311943</v>
       </c>
-      <c r="J30" s="1" t="n">
+      <c r="J30" s="2" t="n">
         <v>42313</v>
       </c>
       <c r="K30" t="n">
@@ -8591,13 +8603,13 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="n">
+      <c r="A31" s="2" t="n">
         <v>42278</v>
       </c>
-      <c r="B31" s="1" t="n">
+      <c r="B31" s="2" t="n">
         <v>42369</v>
       </c>
-      <c r="C31" s="1" t="n">
+      <c r="C31" s="2" t="n">
         <v>42425</v>
       </c>
       <c r="D31" t="inlineStr">
@@ -8624,7 +8636,7 @@
       <c r="I31" t="n">
         <v>4.055258467023172</v>
       </c>
-      <c r="J31" s="1" t="n">
+      <c r="J31" s="2" t="n">
         <v>42425</v>
       </c>
       <c r="K31" t="n">
@@ -8637,13 +8649,13 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="n">
+      <c r="A32" s="2" t="n">
         <v>42370</v>
       </c>
-      <c r="B32" s="1" t="n">
+      <c r="B32" s="2" t="n">
         <v>42460</v>
       </c>
-      <c r="C32" s="1" t="n">
+      <c r="C32" s="2" t="n">
         <v>42496</v>
       </c>
       <c r="D32" t="inlineStr">
@@ -8670,7 +8682,7 @@
       <c r="I32" t="n">
         <v>4.153297682709447</v>
       </c>
-      <c r="J32" s="1" t="n">
+      <c r="J32" s="2" t="n">
         <v>42496</v>
       </c>
       <c r="K32" t="n">
@@ -8683,13 +8695,13 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="n">
+      <c r="A33" s="2" t="n">
         <v>42461</v>
       </c>
-      <c r="B33" s="1" t="n">
+      <c r="B33" s="2" t="n">
         <v>42551</v>
       </c>
-      <c r="C33" s="1" t="n">
+      <c r="C33" s="2" t="n">
         <v>42587</v>
       </c>
       <c r="D33" t="inlineStr">
@@ -8716,7 +8728,7 @@
       <c r="I33" t="n">
         <v>3.38680926916221</v>
       </c>
-      <c r="J33" s="1" t="n">
+      <c r="J33" s="2" t="n">
         <v>42587</v>
       </c>
       <c r="K33" t="n">
@@ -8729,13 +8741,13 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="n">
+      <c r="A34" s="2" t="n">
         <v>42552</v>
       </c>
-      <c r="B34" s="1" t="n">
+      <c r="B34" s="2" t="n">
         <v>42643</v>
       </c>
-      <c r="C34" s="1" t="n">
+      <c r="C34" s="2" t="n">
         <v>42677</v>
       </c>
       <c r="D34" t="inlineStr">
@@ -8762,7 +8774,7 @@
       <c r="I34" t="n">
         <v>2.896613190730837</v>
       </c>
-      <c r="J34" s="1" t="n">
+      <c r="J34" s="2" t="n">
         <v>42677</v>
       </c>
       <c r="K34" t="n">
@@ -8775,13 +8787,13 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="n">
+      <c r="A35" s="2" t="n">
         <v>42644</v>
       </c>
-      <c r="B35" s="1" t="n">
+      <c r="B35" s="2" t="n">
         <v>42735</v>
       </c>
-      <c r="C35" s="1" t="n">
+      <c r="C35" s="2" t="n">
         <v>42795</v>
       </c>
       <c r="D35" t="inlineStr">
@@ -8808,7 +8820,7 @@
       <c r="I35" t="n">
         <v>0.5436720142602496</v>
       </c>
-      <c r="J35" s="1" t="n">
+      <c r="J35" s="2" t="n">
         <v>42795</v>
       </c>
       <c r="K35" t="n">
@@ -8821,13 +8833,13 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="1" t="n">
+      <c r="A36" s="2" t="n">
         <v>42736</v>
       </c>
-      <c r="B36" s="1" t="n">
+      <c r="B36" s="2" t="n">
         <v>42825</v>
       </c>
-      <c r="C36" s="1" t="n">
+      <c r="C36" s="2" t="n">
         <v>42860</v>
       </c>
       <c r="D36" t="inlineStr">
@@ -8854,7 +8866,7 @@
       <c r="I36" t="n">
         <v>-0.5525846702317291</v>
       </c>
-      <c r="J36" s="1" t="n">
+      <c r="J36" s="2" t="n">
         <v>42860</v>
       </c>
       <c r="K36" t="n">
@@ -8867,13 +8879,13 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="1" t="n">
+      <c r="A37" s="2" t="n">
         <v>42826</v>
       </c>
-      <c r="B37" s="1" t="n">
+      <c r="B37" s="2" t="n">
         <v>42916</v>
       </c>
-      <c r="C37" s="1" t="n">
+      <c r="C37" s="2" t="n">
         <v>42951</v>
       </c>
       <c r="D37" t="inlineStr">
@@ -8900,7 +8912,7 @@
       <c r="I37" t="n">
         <v>0.0802139037433155</v>
       </c>
-      <c r="J37" s="1" t="n">
+      <c r="J37" s="2" t="n">
         <v>42951</v>
       </c>
       <c r="K37" t="n">
@@ -8913,13 +8925,13 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="1" t="n">
+      <c r="A38" s="2" t="n">
         <v>42917</v>
       </c>
-      <c r="B38" s="1" t="n">
+      <c r="B38" s="2" t="n">
         <v>43008</v>
       </c>
-      <c r="C38" s="1" t="n">
+      <c r="C38" s="2" t="n">
         <v>43045</v>
       </c>
       <c r="D38" t="inlineStr">
@@ -8946,7 +8958,7 @@
       <c r="I38" t="n">
         <v>-0.4543315508021391</v>
       </c>
-      <c r="J38" s="1" t="n">
+      <c r="J38" s="2" t="n">
         <v>43045</v>
       </c>
       <c r="K38" t="n">
@@ -8959,13 +8971,13 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="1" t="n">
+      <c r="A39" s="2" t="n">
         <v>43009</v>
       </c>
-      <c r="B39" s="1" t="n">
+      <c r="B39" s="2" t="n">
         <v>43100</v>
       </c>
-      <c r="C39" s="1" t="n">
+      <c r="C39" s="2" t="n">
         <v>43160</v>
       </c>
       <c r="D39" t="inlineStr">
@@ -8992,7 +9004,7 @@
       <c r="I39" t="n">
         <v>3.414723707664884</v>
       </c>
-      <c r="J39" s="1" t="n">
+      <c r="J39" s="2" t="n">
         <v>43160</v>
       </c>
       <c r="K39" t="n">
@@ -9005,13 +9017,13 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="n">
+      <c r="A40" s="2" t="n">
         <v>43101</v>
       </c>
-      <c r="B40" s="1" t="n">
+      <c r="B40" s="2" t="n">
         <v>43190</v>
       </c>
-      <c r="C40" s="1" t="n">
+      <c r="C40" s="2" t="n">
         <v>43228</v>
       </c>
       <c r="D40" t="inlineStr">
@@ -9038,7 +9050,7 @@
       <c r="I40" t="n">
         <v>3.936274509803921</v>
       </c>
-      <c r="J40" s="1" t="n">
+      <c r="J40" s="2" t="n">
         <v>43228</v>
       </c>
       <c r="K40" t="n">
@@ -9051,13 +9063,13 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="1" t="n">
+      <c r="A41" s="2" t="n">
         <v>43191</v>
       </c>
-      <c r="B41" s="1" t="n">
+      <c r="B41" s="2" t="n">
         <v>43281</v>
       </c>
-      <c r="C41" s="1" t="n">
+      <c r="C41" s="2" t="n">
         <v>43319</v>
       </c>
       <c r="D41" t="inlineStr">
@@ -9084,7 +9096,7 @@
       <c r="I41" t="n">
         <v>4.08</v>
       </c>
-      <c r="J41" s="1" t="n">
+      <c r="J41" s="2" t="n">
         <v>43319</v>
       </c>
       <c r="K41" t="n">
@@ -9097,13 +9109,13 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="1" t="n">
+      <c r="A42" s="2" t="n">
         <v>43282</v>
       </c>
-      <c r="B42" s="1" t="n">
+      <c r="B42" s="2" t="n">
         <v>43373</v>
       </c>
-      <c r="C42" s="1" t="n">
+      <c r="C42" s="2" t="n">
         <v>43412</v>
       </c>
       <c r="D42" t="inlineStr">
@@ -9130,7 +9142,7 @@
       <c r="I42" t="n">
         <v>5.04</v>
       </c>
-      <c r="J42" s="1" t="n">
+      <c r="J42" s="2" t="n">
         <v>43412</v>
       </c>
       <c r="K42" t="n">
@@ -9143,13 +9155,13 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="1" t="n">
+      <c r="A43" s="2" t="n">
         <v>43374</v>
       </c>
-      <c r="B43" s="1" t="n">
+      <c r="B43" s="2" t="n">
         <v>43465</v>
       </c>
-      <c r="C43" s="1" t="n">
+      <c r="C43" s="2" t="n">
         <v>43518</v>
       </c>
       <c r="D43" t="inlineStr">
@@ -9176,7 +9188,7 @@
       <c r="I43" t="n">
         <v>4.94</v>
       </c>
-      <c r="J43" s="1" t="n">
+      <c r="J43" s="2" t="n">
         <v>43518</v>
       </c>
       <c r="K43" t="n">
@@ -9189,13 +9201,13 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="1" t="n">
+      <c r="A44" s="2" t="n">
         <v>43466</v>
       </c>
-      <c r="B44" s="1" t="n">
+      <c r="B44" s="2" t="n">
         <v>43555</v>
       </c>
-      <c r="C44" s="1" t="n">
+      <c r="C44" s="2" t="n">
         <v>43593</v>
       </c>
       <c r="D44" t="inlineStr">
@@ -9222,7 +9234,7 @@
       <c r="I44" t="n">
         <v>5.15</v>
       </c>
-      <c r="J44" s="1" t="n">
+      <c r="J44" s="2" t="n">
         <v>43593</v>
       </c>
       <c r="K44" t="n">
@@ -9235,13 +9247,13 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="1" t="n">
+      <c r="A45" s="2" t="n">
         <v>43556</v>
       </c>
-      <c r="B45" s="1" t="n">
+      <c r="B45" s="2" t="n">
         <v>43646</v>
       </c>
-      <c r="C45" s="1" t="n">
+      <c r="C45" s="2" t="n">
         <v>43683</v>
       </c>
       <c r="D45" t="inlineStr">
@@ -9268,7 +9280,7 @@
       <c r="I45" t="n">
         <v>6.09</v>
       </c>
-      <c r="J45" s="1" t="n">
+      <c r="J45" s="2" t="n">
         <v>43683</v>
       </c>
       <c r="K45" t="n">
@@ -9281,13 +9293,13 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="1" t="n">
+      <c r="A46" s="2" t="n">
         <v>43647</v>
       </c>
-      <c r="B46" s="1" t="n">
+      <c r="B46" s="2" t="n">
         <v>43738</v>
       </c>
-      <c r="C46" s="1" t="n">
+      <c r="C46" s="2" t="n">
         <v>43774</v>
       </c>
       <c r="D46" t="inlineStr">
@@ -9314,7 +9326,7 @@
       <c r="I46" t="n">
         <v>7.51</v>
       </c>
-      <c r="J46" s="1" t="n">
+      <c r="J46" s="2" t="n">
         <v>43774</v>
       </c>
       <c r="K46" t="n">
@@ -9327,13 +9339,13 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="1" t="n">
+      <c r="A47" s="2" t="n">
         <v>43739</v>
       </c>
-      <c r="B47" s="1" t="n">
+      <c r="B47" s="2" t="n">
         <v>43830</v>
       </c>
-      <c r="C47" s="1" t="n">
+      <c r="C47" s="2" t="n">
         <v>43882</v>
       </c>
       <c r="D47" t="inlineStr">
@@ -9360,7 +9372,7 @@
       <c r="I47" t="n">
         <v>6.05</v>
       </c>
-      <c r="J47" s="1" t="n">
+      <c r="J47" s="2" t="n">
         <v>43882</v>
       </c>
       <c r="K47" t="n">
@@ -9373,13 +9385,13 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="1" t="n">
+      <c r="A48" s="2" t="n">
         <v>43831</v>
       </c>
-      <c r="B48" s="1" t="n">
+      <c r="B48" s="2" t="n">
         <v>43921</v>
       </c>
-      <c r="C48" s="1" t="n">
+      <c r="C48" s="2" t="n">
         <v>43959</v>
       </c>
       <c r="D48" t="inlineStr">
@@ -9406,7 +9418,7 @@
       <c r="I48" t="n">
         <v>9.4</v>
       </c>
-      <c r="J48" s="1" t="n">
+      <c r="J48" s="2" t="n">
         <v>43959</v>
       </c>
       <c r="K48" t="n">
@@ -9419,13 +9431,13 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="1" t="n">
+      <c r="A49" s="2" t="n">
         <v>43922</v>
       </c>
-      <c r="B49" s="1" t="n">
+      <c r="B49" s="2" t="n">
         <v>44012</v>
       </c>
-      <c r="C49" s="1" t="n">
+      <c r="C49" s="2" t="n">
         <v>44050</v>
       </c>
       <c r="D49" t="inlineStr">
@@ -9452,7 +9464,7 @@
       <c r="I49" t="n">
         <v>7.7</v>
       </c>
-      <c r="J49" s="1" t="n">
+      <c r="J49" s="2" t="n">
         <v>44050</v>
       </c>
       <c r="K49" t="n">
@@ -9465,13 +9477,13 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="1" t="n">
+      <c r="A50" s="2" t="n">
         <v>44013</v>
       </c>
-      <c r="B50" s="1" t="n">
+      <c r="B50" s="2" t="n">
         <v>44104</v>
       </c>
-      <c r="C50" s="1" t="n">
+      <c r="C50" s="2" t="n">
         <v>44144</v>
       </c>
       <c r="D50" t="inlineStr">
@@ -9498,7 +9510,7 @@
       <c r="I50" t="n">
         <v>6.09</v>
       </c>
-      <c r="J50" s="1" t="n">
+      <c r="J50" s="2" t="n">
         <v>44144</v>
       </c>
       <c r="K50" t="n">
@@ -9511,13 +9523,13 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="1" t="n">
+      <c r="A51" s="2" t="n">
         <v>44105</v>
       </c>
-      <c r="B51" s="1" t="n">
+      <c r="B51" s="2" t="n">
         <v>44196</v>
       </c>
-      <c r="C51" s="1" t="n">
+      <c r="C51" s="2" t="n">
         <v>44246</v>
       </c>
       <c r="D51" t="inlineStr">
@@ -9544,7 +9556,7 @@
       <c r="I51" t="n">
         <v>5.65</v>
       </c>
-      <c r="J51" s="1" t="n">
+      <c r="J51" s="2" t="n">
         <v>44246</v>
       </c>
       <c r="K51" t="n">
@@ -9557,13 +9569,13 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="1" t="n">
+      <c r="A52" s="2" t="n">
         <v>44197</v>
       </c>
-      <c r="B52" s="1" t="n">
+      <c r="B52" s="2" t="n">
         <v>44286</v>
       </c>
-      <c r="C52" s="1" t="n">
+      <c r="C52" s="2" t="n">
         <v>44322</v>
       </c>
       <c r="D52" t="inlineStr">
@@ -9590,7 +9602,7 @@
       <c r="I52" t="n">
         <v>1.23</v>
       </c>
-      <c r="J52" s="1" t="n">
+      <c r="J52" s="2" t="n">
         <v>44322</v>
       </c>
       <c r="K52" t="n">
@@ -9603,13 +9615,13 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="1" t="n">
+      <c r="A53" s="2" t="n">
         <v>44287</v>
       </c>
-      <c r="B53" s="1" t="n">
+      <c r="B53" s="2" t="n">
         <v>44377</v>
       </c>
-      <c r="C53" s="1" t="n">
+      <c r="C53" s="2" t="n">
         <v>44414</v>
       </c>
       <c r="D53" t="inlineStr">
@@ -9636,7 +9648,7 @@
       <c r="I53" t="n">
         <v>4.99</v>
       </c>
-      <c r="J53" s="1" t="n">
+      <c r="J53" s="2" t="n">
         <v>44414</v>
       </c>
       <c r="K53" t="n">
@@ -9649,13 +9661,13 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="1" t="n">
+      <c r="A54" s="2" t="n">
         <v>44378</v>
       </c>
-      <c r="B54" s="1" t="n">
+      <c r="B54" s="2" t="n">
         <v>44469</v>
       </c>
-      <c r="C54" s="1" t="n">
+      <c r="C54" s="2" t="n">
         <v>44509</v>
       </c>
       <c r="D54" t="inlineStr">
@@ -9682,7 +9694,7 @@
       <c r="I54" t="n">
         <v>6.07</v>
       </c>
-      <c r="J54" s="1" t="n">
+      <c r="J54" s="2" t="n">
         <v>44509</v>
       </c>
       <c r="K54" t="n">
@@ -9695,13 +9707,13 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="1" t="n">
+      <c r="A55" s="2" t="n">
         <v>44470</v>
       </c>
-      <c r="B55" s="1" t="n">
+      <c r="B55" s="2" t="n">
         <v>44561</v>
       </c>
-      <c r="C55" s="1" t="n">
+      <c r="C55" s="2" t="n">
         <v>44610</v>
       </c>
       <c r="D55" t="inlineStr">
@@ -9728,7 +9740,7 @@
       <c r="I55" t="n">
         <v>7.31</v>
       </c>
-      <c r="J55" s="1" t="n">
+      <c r="J55" s="2" t="n">
         <v>44610</v>
       </c>
       <c r="K55" t="n">
@@ -9741,13 +9753,13 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="1" t="n">
+      <c r="A56" s="2" t="n">
         <v>44562</v>
       </c>
-      <c r="B56" s="1" t="n">
+      <c r="B56" s="2" t="n">
         <v>44651</v>
       </c>
-      <c r="C56" s="1" t="n">
+      <c r="C56" s="2" t="n">
         <v>44686</v>
       </c>
       <c r="D56" t="inlineStr">
@@ -9774,7 +9786,7 @@
       <c r="I56" t="n">
         <v>7.71</v>
       </c>
-      <c r="J56" s="1" t="n">
+      <c r="J56" s="2" t="n">
         <v>44686</v>
       </c>
       <c r="K56" t="n">
@@ -9787,13 +9799,13 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="1" t="n">
+      <c r="A57" s="2" t="n">
         <v>44652</v>
       </c>
-      <c r="B57" s="1" t="n">
+      <c r="B57" s="2" t="n">
         <v>44742</v>
       </c>
-      <c r="C57" s="1" t="n">
+      <c r="C57" s="2" t="n">
         <v>44777</v>
       </c>
       <c r="D57" t="inlineStr">
@@ -9820,7 +9832,7 @@
       <c r="I57" t="n">
         <v>4.01</v>
       </c>
-      <c r="J57" s="1" t="n">
+      <c r="J57" s="2" t="n">
         <v>44777</v>
       </c>
       <c r="K57" t="n">
@@ -9833,13 +9845,13 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="1" t="n">
+      <c r="A58" s="2" t="n">
         <v>44743</v>
       </c>
-      <c r="B58" s="1" t="n">
+      <c r="B58" s="2" t="n">
         <v>44834</v>
       </c>
-      <c r="C58" s="1" t="n">
+      <c r="C58" s="2" t="n">
         <v>44868</v>
       </c>
       <c r="D58" t="inlineStr">
@@ -9866,7 +9878,7 @@
       <c r="I58" t="n">
         <v>2.65</v>
       </c>
-      <c r="J58" s="1" t="n">
+      <c r="J58" s="2" t="n">
         <v>44868</v>
       </c>
       <c r="K58" t="n">
@@ -9879,13 +9891,13 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="1" t="n">
+      <c r="A59" s="2" t="n">
         <v>44835</v>
       </c>
-      <c r="B59" s="1" t="n">
+      <c r="B59" s="2" t="n">
         <v>44926</v>
       </c>
-      <c r="C59" s="1" t="n">
+      <c r="C59" s="2" t="n">
         <v>44980</v>
       </c>
       <c r="D59" t="inlineStr">
@@ -9912,7 +9924,7 @@
       <c r="I59" t="n">
         <v>2.91</v>
       </c>
-      <c r="J59" s="1" t="n">
+      <c r="J59" s="2" t="n">
         <v>44980</v>
       </c>
       <c r="K59" t="n">
@@ -9925,13 +9937,13 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="1" t="n">
+      <c r="A60" s="2" t="n">
         <v>44927</v>
       </c>
-      <c r="B60" s="1" t="n">
+      <c r="B60" s="2" t="n">
         <v>45016</v>
       </c>
-      <c r="C60" s="1" t="n">
+      <c r="C60" s="2" t="n">
         <v>45050</v>
       </c>
       <c r="D60" t="inlineStr">
@@ -9958,7 +9970,7 @@
       <c r="I60" t="n">
         <v>2.2</v>
       </c>
-      <c r="J60" s="1" t="n">
+      <c r="J60" s="2" t="n">
         <v>45050</v>
       </c>
       <c r="K60" t="n">
@@ -9971,13 +9983,13 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="1" t="n">
+      <c r="A61" s="2" t="n">
         <v>45017</v>
       </c>
-      <c r="B61" s="1" t="n">
+      <c r="B61" s="2" t="n">
         <v>45107</v>
       </c>
-      <c r="C61" s="1" t="n">
+      <c r="C61" s="2" t="n">
         <v>45142</v>
       </c>
       <c r="D61" t="inlineStr">
@@ -10004,7 +10016,7 @@
       <c r="I61" t="n">
         <v>2.55</v>
       </c>
-      <c r="J61" s="1" t="n">
+      <c r="J61" s="2" t="n">
         <v>45142</v>
       </c>
       <c r="K61" t="n">
@@ -10017,13 +10029,13 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="1" t="n">
+      <c r="A62" s="2" t="n">
         <v>45108</v>
       </c>
-      <c r="B62" s="1" t="n">
+      <c r="B62" s="2" t="n">
         <v>45199</v>
       </c>
-      <c r="C62" s="1" t="n">
+      <c r="C62" s="2" t="n">
         <v>45232</v>
       </c>
       <c r="D62" t="inlineStr">
@@ -10050,7 +10062,7 @@
       <c r="I62" t="n">
         <v>2.7</v>
       </c>
-      <c r="J62" s="1" t="n">
+      <c r="J62" s="2" t="n">
         <v>45232</v>
       </c>
       <c r="K62" t="n">
@@ -10063,13 +10075,13 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="1" t="n">
+      <c r="A63" s="2" t="n">
         <v>45200</v>
       </c>
-      <c r="B63" s="1" t="n">
+      <c r="B63" s="2" t="n">
         <v>45291</v>
       </c>
-      <c r="C63" s="1" t="n">
+      <c r="C63" s="2" t="n">
         <v>45338</v>
       </c>
       <c r="D63" t="inlineStr">
@@ -10096,7 +10108,7 @@
       <c r="I63" t="n">
         <v>1.83</v>
       </c>
-      <c r="J63" s="1" t="n">
+      <c r="J63" s="2" t="n">
         <v>45338</v>
       </c>
       <c r="K63" t="n">
@@ -10109,13 +10121,13 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="1" t="n">
+      <c r="A64" s="2" t="n">
         <v>45292</v>
       </c>
-      <c r="B64" s="1" t="n">
+      <c r="B64" s="2" t="n">
         <v>45382</v>
       </c>
-      <c r="C64" s="1" t="n">
+      <c r="C64" s="2" t="n">
         <v>45414</v>
       </c>
       <c r="D64" t="inlineStr">
@@ -10142,7 +10154,7 @@
       <c r="I64" t="n">
         <v>2.91</v>
       </c>
-      <c r="J64" s="1" t="n">
+      <c r="J64" s="2" t="n">
         <v>45414</v>
       </c>
       <c r="K64" t="n">
@@ -10155,13 +10167,13 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="1" t="n">
+      <c r="A65" s="2" t="n">
         <v>45383</v>
       </c>
-      <c r="B65" s="1" t="n">
+      <c r="B65" s="2" t="n">
         <v>45473</v>
       </c>
-      <c r="C65" s="1" t="n">
+      <c r="C65" s="2" t="n">
         <v>45505</v>
       </c>
       <c r="D65" t="inlineStr">
@@ -10188,7 +10200,7 @@
       <c r="I65" t="n">
         <v>3.71</v>
       </c>
-      <c r="J65" s="1" t="n">
+      <c r="J65" s="2" t="n">
         <v>45505</v>
       </c>
       <c r="K65" t="n">
@@ -10201,13 +10213,13 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="1" t="n">
+      <c r="A66" s="2" t="n">
         <v>45474</v>
       </c>
-      <c r="B66" s="1" t="n">
+      <c r="B66" s="2" t="n">
         <v>45565</v>
       </c>
-      <c r="C66" s="1" t="n">
+      <c r="C66" s="2" t="n">
         <v>45597</v>
       </c>
       <c r="D66" t="inlineStr">
@@ -10234,7 +10246,7 @@
       <c r="I66" t="n">
         <v>4.96</v>
       </c>
-      <c r="J66" s="1" t="n">
+      <c r="J66" s="2" t="n">
         <v>45597</v>
       </c>
       <c r="K66" t="n">
@@ -10247,13 +10259,13 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="1" t="n">
+      <c r="A67" s="2" t="n">
         <v>45566</v>
       </c>
-      <c r="B67" s="1" t="n">
+      <c r="B67" s="2" t="n">
         <v>45657</v>
       </c>
-      <c r="C67" s="1" t="n">
+      <c r="C67" s="2" t="n">
         <v>45709</v>
       </c>
       <c r="D67" t="inlineStr">
@@ -10280,7 +10292,7 @@
       <c r="I67" t="n">
         <v>5.94</v>
       </c>
-      <c r="J67" s="1" t="n">
+      <c r="J67" s="2" t="n">
         <v>45709</v>
       </c>
       <c r="K67" t="n">
@@ -10293,13 +10305,13 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="1" t="n">
+      <c r="A68" s="2" t="n">
         <v>45658</v>
       </c>
-      <c r="B68" s="1" t="n">
+      <c r="B68" s="2" t="n">
         <v>45747</v>
       </c>
-      <c r="C68" s="1" t="n">
+      <c r="C68" s="2" t="n">
         <v>45778</v>
       </c>
       <c r="D68" t="inlineStr">
@@ -10326,7 +10338,7 @@
       <c r="I68" t="n">
         <v>6.120000000000001</v>
       </c>
-      <c r="J68" s="1" t="n">
+      <c r="J68" s="2" t="n">
         <v>45778</v>
       </c>
       <c r="K68" t="n">
@@ -10339,13 +10351,13 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="1" t="n">
+      <c r="A69" s="2" t="n">
         <v>45748</v>
       </c>
-      <c r="B69" s="1" t="n">
+      <c r="B69" s="2" t="n">
         <v>45838</v>
       </c>
-      <c r="C69" s="1" t="n">
+      <c r="C69" s="2" t="n">
         <v>45876</v>
       </c>
       <c r="D69" t="inlineStr">
@@ -10372,7 +10384,7 @@
       <c r="I69" t="n">
         <v>5.870000000000001</v>
       </c>
-      <c r="J69" s="1" t="n">
+      <c r="J69" s="2" t="n">
         <v>45876</v>
       </c>
       <c r="K69" t="n">
@@ -10385,13 +10397,13 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="1" t="n">
+      <c r="A70" s="2" t="n">
         <v>45839</v>
       </c>
-      <c r="B70" s="1" t="n">
+      <c r="B70" s="2" t="n">
         <v>45930</v>
       </c>
-      <c r="C70" s="1" t="n">
+      <c r="C70" s="2" t="n">
         <v>45968</v>
       </c>
       <c r="D70" t="inlineStr">
@@ -10418,7 +10430,7 @@
       <c r="I70" t="n">
         <v>5.280000000000001</v>
       </c>
-      <c r="J70" s="1" t="n">
+      <c r="J70" s="2" t="n">
         <v>45968</v>
       </c>
       <c r="K70" t="n">
@@ -10431,13 +10443,13 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="1" t="n">
+      <c r="A71" s="2" t="n">
         <v>45931</v>
       </c>
-      <c r="B71" s="1" t="n">
+      <c r="B71" s="2" t="n">
         <v>46022</v>
       </c>
-      <c r="C71" s="1" t="n">
+      <c r="C71" s="2" t="n">
         <v>46072</v>
       </c>
       <c r="D71" t="inlineStr">
@@ -10464,7 +10476,7 @@
       <c r="I71" t="n">
         <v>4.71</v>
       </c>
-      <c r="J71" s="1" t="n">
+      <c r="J71" s="2" t="n">
         <v>46072</v>
       </c>
       <c r="K71" t="n">
@@ -10477,13 +10489,13 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="1" t="n">
+      <c r="A72" s="2" t="n">
         <v>46023</v>
       </c>
-      <c r="B72" s="1" t="n">
+      <c r="B72" s="2" t="n">
         <v>46112</v>
       </c>
-      <c r="C72" s="1" t="n">
+      <c r="C72" s="2" t="n">
         <v>46149</v>
       </c>
       <c r="D72" t="inlineStr">
@@ -10510,7 +10522,7 @@
       <c r="I72" t="n">
         <v>5.17</v>
       </c>
-      <c r="J72" s="1" t="n">
+      <c r="J72" s="2" t="n">
         <v>46149</v>
       </c>
       <c r="K72" t="n">
@@ -10523,13 +10535,13 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="1" t="n">
+      <c r="A73" s="2" t="n">
         <v>46113</v>
       </c>
-      <c r="B73" s="1" t="n">
+      <c r="B73" s="2" t="n">
         <v>46203</v>
       </c>
-      <c r="C73" s="1" t="n">
+      <c r="C73" s="2" t="n">
         <v>46240</v>
       </c>
       <c r="D73" t="inlineStr">
@@ -10556,7 +10568,7 @@
       <c r="I73" t="n">
         <v>5.23</v>
       </c>
-      <c r="J73" s="1" t="n">
+      <c r="J73" s="2" t="n">
         <v>46240</v>
       </c>
       <c r="K73" t="n">
@@ -10593,52 +10605,52 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>end</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>filed</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>acciones</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>form</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>fy</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>fp</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>tag</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>factor</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" s="2" t="n">
         <v>40025</v>
       </c>
-      <c r="B2" s="1" t="n">
+      <c r="B2" s="2" t="n">
         <v>40029</v>
       </c>
       <c r="C2" t="n">
@@ -10667,10 +10679,10 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" s="2" t="n">
         <v>40119</v>
       </c>
-      <c r="B3" s="1" t="n">
+      <c r="B3" s="2" t="n">
         <v>40121</v>
       </c>
       <c r="C3" t="n">
@@ -10699,10 +10711,10 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" s="2" t="n">
         <v>40231</v>
       </c>
-      <c r="B4" s="1" t="n">
+      <c r="B4" s="2" t="n">
         <v>40235</v>
       </c>
       <c r="C4" t="n">
@@ -10731,10 +10743,10 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" s="2" t="n">
         <v>40298</v>
       </c>
-      <c r="B5" s="1" t="n">
+      <c r="B5" s="2" t="n">
         <v>40303</v>
       </c>
       <c r="C5" t="n">
@@ -10763,10 +10775,10 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" s="2" t="n">
         <v>40483</v>
       </c>
-      <c r="B6" s="1" t="n">
+      <c r="B6" s="2" t="n">
         <v>40486</v>
       </c>
       <c r="C6" t="n">
@@ -10795,10 +10807,10 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="A7" s="2" t="n">
         <v>40592</v>
       </c>
-      <c r="B7" s="1" t="n">
+      <c r="B7" s="2" t="n">
         <v>40599</v>
       </c>
       <c r="C7" t="n">
@@ -10827,10 +10839,10 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="A8" s="2" t="n">
         <v>40665</v>
       </c>
-      <c r="B8" s="1" t="n">
+      <c r="B8" s="2" t="n">
         <v>40673</v>
       </c>
       <c r="C8" t="n">
@@ -10859,10 +10871,10 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
+      <c r="A9" s="2" t="n">
         <v>40753</v>
       </c>
-      <c r="B9" s="1" t="n">
+      <c r="B9" s="2" t="n">
         <v>40760</v>
       </c>
       <c r="C9" t="n">
@@ -10891,10 +10903,10 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
+      <c r="A10" s="2" t="n">
         <v>40847</v>
       </c>
-      <c r="B10" s="1" t="n">
+      <c r="B10" s="2" t="n">
         <v>40851</v>
       </c>
       <c r="C10" t="n">
@@ -10923,10 +10935,10 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
+      <c r="A11" s="2" t="n">
         <v>40960</v>
       </c>
-      <c r="B11" s="1" t="n">
+      <c r="B11" s="2" t="n">
         <v>40967</v>
       </c>
       <c r="C11" t="n">
@@ -10955,10 +10967,10 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
+      <c r="A12" s="2" t="n">
         <v>41031</v>
       </c>
-      <c r="B12" s="1" t="n">
+      <c r="B12" s="2" t="n">
         <v>41037</v>
       </c>
       <c r="C12" t="n">
@@ -10987,10 +10999,10 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n">
+      <c r="A13" s="2" t="n">
         <v>41121</v>
       </c>
-      <c r="B13" s="1" t="n">
+      <c r="B13" s="2" t="n">
         <v>41128</v>
       </c>
       <c r="C13" t="n">
@@ -11019,10 +11031,10 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n">
+      <c r="A14" s="2" t="n">
         <v>41213</v>
       </c>
-      <c r="B14" s="1" t="n">
+      <c r="B14" s="2" t="n">
         <v>41220</v>
       </c>
       <c r="C14" t="n">
@@ -11051,10 +11063,10 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n">
+      <c r="A15" s="2" t="n">
         <v>41324</v>
       </c>
-      <c r="B15" s="1" t="n">
+      <c r="B15" s="2" t="n">
         <v>41332</v>
       </c>
       <c r="C15" t="n">
@@ -11083,10 +11095,10 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n">
+      <c r="A16" s="2" t="n">
         <v>41394</v>
       </c>
-      <c r="B16" s="1" t="n">
+      <c r="B16" s="2" t="n">
         <v>41401</v>
       </c>
       <c r="C16" t="n">
@@ -11115,10 +11127,10 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n">
+      <c r="A17" s="2" t="n">
         <v>41486</v>
       </c>
-      <c r="B17" s="1" t="n">
+      <c r="B17" s="2" t="n">
         <v>41493</v>
       </c>
       <c r="C17" t="n">
@@ -11147,10 +11159,10 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="n">
+      <c r="A18" s="2" t="n">
         <v>41578</v>
       </c>
-      <c r="B18" s="1" t="n">
+      <c r="B18" s="2" t="n">
         <v>41585</v>
       </c>
       <c r="C18" t="n">
@@ -11179,10 +11191,10 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="n">
+      <c r="A19" s="2" t="n">
         <v>41689</v>
       </c>
-      <c r="B19" s="1" t="n">
+      <c r="B19" s="2" t="n">
         <v>41697</v>
       </c>
       <c r="C19" t="n">
@@ -11211,10 +11223,10 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="n">
+      <c r="A20" s="2" t="n">
         <v>41759</v>
       </c>
-      <c r="B20" s="1" t="n">
+      <c r="B20" s="2" t="n">
         <v>41767</v>
       </c>
       <c r="C20" t="n">
@@ -11243,10 +11255,10 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="n">
+      <c r="A21" s="2" t="n">
         <v>41851</v>
       </c>
-      <c r="B21" s="1" t="n">
+      <c r="B21" s="2" t="n">
         <v>41859</v>
       </c>
       <c r="C21" t="n">
@@ -11275,10 +11287,10 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="n">
+      <c r="A22" s="2" t="n">
         <v>41943</v>
       </c>
-      <c r="B22" s="1" t="n">
+      <c r="B22" s="2" t="n">
         <v>41949</v>
       </c>
       <c r="C22" t="n">
@@ -11307,10 +11319,10 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="n">
+      <c r="A23" s="2" t="n">
         <v>42058</v>
       </c>
-      <c r="B23" s="1" t="n">
+      <c r="B23" s="2" t="n">
         <v>42062</v>
       </c>
       <c r="C23" t="n">
@@ -11339,10 +11351,10 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="n">
+      <c r="A24" s="2" t="n">
         <v>42124</v>
       </c>
-      <c r="B24" s="1" t="n">
+      <c r="B24" s="2" t="n">
         <v>42132</v>
       </c>
       <c r="C24" t="n">
@@ -11371,10 +11383,10 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="n">
+      <c r="A25" s="2" t="n">
         <v>42216</v>
       </c>
-      <c r="B25" s="1" t="n">
+      <c r="B25" s="2" t="n">
         <v>42222</v>
       </c>
       <c r="C25" t="n">
@@ -11403,10 +11415,10 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="n">
+      <c r="A26" s="2" t="n">
         <v>42307</v>
       </c>
-      <c r="B26" s="1" t="n">
+      <c r="B26" s="2" t="n">
         <v>42313</v>
       </c>
       <c r="C26" t="n">
@@ -11435,10 +11447,10 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="n">
+      <c r="A27" s="2" t="n">
         <v>42422</v>
       </c>
-      <c r="B27" s="1" t="n">
+      <c r="B27" s="2" t="n">
         <v>42425</v>
       </c>
       <c r="C27" t="n">
@@ -11467,10 +11479,10 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="n">
+      <c r="A28" s="2" t="n">
         <v>42489</v>
       </c>
-      <c r="B28" s="1" t="n">
+      <c r="B28" s="2" t="n">
         <v>42496</v>
       </c>
       <c r="C28" t="n">
@@ -11499,10 +11511,10 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="n">
+      <c r="A29" s="2" t="n">
         <v>42580</v>
       </c>
-      <c r="B29" s="1" t="n">
+      <c r="B29" s="2" t="n">
         <v>42587</v>
       </c>
       <c r="C29" t="n">
@@ -11531,10 +11543,10 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="n">
+      <c r="A30" s="2" t="n">
         <v>42674</v>
       </c>
-      <c r="B30" s="1" t="n">
+      <c r="B30" s="2" t="n">
         <v>42677</v>
       </c>
       <c r="C30" t="n">
@@ -11563,10 +11575,10 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="n">
+      <c r="A31" s="2" t="n">
         <v>42789</v>
       </c>
-      <c r="B31" s="1" t="n">
+      <c r="B31" s="2" t="n">
         <v>42795</v>
       </c>
       <c r="C31" t="n">
@@ -11595,10 +11607,10 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="n">
+      <c r="A32" s="2" t="n">
         <v>42853</v>
       </c>
-      <c r="B32" s="1" t="n">
+      <c r="B32" s="2" t="n">
         <v>42860</v>
       </c>
       <c r="C32" t="n">
@@ -11627,10 +11639,10 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="n">
+      <c r="A33" s="2" t="n">
         <v>42947</v>
       </c>
-      <c r="B33" s="1" t="n">
+      <c r="B33" s="2" t="n">
         <v>42951</v>
       </c>
       <c r="C33" t="n">
@@ -11659,10 +11671,10 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="n">
+      <c r="A34" s="2" t="n">
         <v>43033</v>
       </c>
-      <c r="B34" s="1" t="n">
+      <c r="B34" s="2" t="n">
         <v>43045</v>
       </c>
       <c r="C34" t="n">
@@ -11691,10 +11703,10 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="n">
+      <c r="A35" s="2" t="n">
         <v>43147</v>
       </c>
-      <c r="B35" s="1" t="n">
+      <c r="B35" s="2" t="n">
         <v>43160</v>
       </c>
       <c r="C35" t="n">
@@ -11723,10 +11735,10 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="1" t="n">
+      <c r="A36" s="2" t="n">
         <v>43220</v>
       </c>
-      <c r="B36" s="1" t="n">
+      <c r="B36" s="2" t="n">
         <v>43228</v>
       </c>
       <c r="C36" t="n">
@@ -11755,10 +11767,10 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="1" t="n">
+      <c r="A37" s="2" t="n">
         <v>43312</v>
       </c>
-      <c r="B37" s="1" t="n">
+      <c r="B37" s="2" t="n">
         <v>43319</v>
       </c>
       <c r="C37" t="n">
@@ -11787,10 +11799,10 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="1" t="n">
+      <c r="A38" s="2" t="n">
         <v>43404</v>
       </c>
-      <c r="B38" s="1" t="n">
+      <c r="B38" s="2" t="n">
         <v>43412</v>
       </c>
       <c r="C38" t="n">
@@ -11819,10 +11831,10 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="1" t="n">
+      <c r="A39" s="2" t="n">
         <v>43510</v>
       </c>
-      <c r="B39" s="1" t="n">
+      <c r="B39" s="2" t="n">
         <v>43518</v>
       </c>
       <c r="C39" t="n">
@@ -11851,10 +11863,10 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="n">
+      <c r="A40" s="2" t="n">
         <v>43585</v>
       </c>
-      <c r="B40" s="1" t="n">
+      <c r="B40" s="2" t="n">
         <v>43593</v>
       </c>
       <c r="C40" t="n">
@@ -11883,10 +11895,10 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="1" t="n">
+      <c r="A41" s="2" t="n">
         <v>43677</v>
       </c>
-      <c r="B41" s="1" t="n">
+      <c r="B41" s="2" t="n">
         <v>43683</v>
       </c>
       <c r="C41" t="n">
@@ -11915,10 +11927,10 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="1" t="n">
+      <c r="A42" s="2" t="n">
         <v>43769</v>
       </c>
-      <c r="B42" s="1" t="n">
+      <c r="B42" s="2" t="n">
         <v>43774</v>
       </c>
       <c r="C42" t="n">
@@ -11947,10 +11959,10 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="1" t="n">
+      <c r="A43" s="2" t="n">
         <v>43875</v>
       </c>
-      <c r="B43" s="1" t="n">
+      <c r="B43" s="2" t="n">
         <v>43882</v>
       </c>
       <c r="C43" t="n">
@@ -11979,10 +11991,10 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="1" t="n">
+      <c r="A44" s="2" t="n">
         <v>43951</v>
       </c>
-      <c r="B44" s="1" t="n">
+      <c r="B44" s="2" t="n">
         <v>43959</v>
       </c>
       <c r="C44" t="n">
@@ -12011,10 +12023,10 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="1" t="n">
+      <c r="A45" s="2" t="n">
         <v>44043</v>
       </c>
-      <c r="B45" s="1" t="n">
+      <c r="B45" s="2" t="n">
         <v>44050</v>
       </c>
       <c r="C45" t="n">
@@ -12043,10 +12055,10 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="1" t="n">
+      <c r="A46" s="2" t="n">
         <v>44134</v>
       </c>
-      <c r="B46" s="1" t="n">
+      <c r="B46" s="2" t="n">
         <v>44144</v>
       </c>
       <c r="C46" t="n">
@@ -12075,10 +12087,10 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="1" t="n">
+      <c r="A47" s="2" t="n">
         <v>44239</v>
       </c>
-      <c r="B47" s="1" t="n">
+      <c r="B47" s="2" t="n">
         <v>44246</v>
       </c>
       <c r="C47" t="n">
@@ -12107,10 +12119,10 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="1" t="n">
+      <c r="A48" s="2" t="n">
         <v>44316</v>
       </c>
-      <c r="B48" s="1" t="n">
+      <c r="B48" s="2" t="n">
         <v>44322</v>
       </c>
       <c r="C48" t="n">
@@ -12139,10 +12151,10 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="1" t="n">
+      <c r="A49" s="2" t="n">
         <v>44407</v>
       </c>
-      <c r="B49" s="1" t="n">
+      <c r="B49" s="2" t="n">
         <v>44414</v>
       </c>
       <c r="C49" t="n">
@@ -12171,10 +12183,10 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="1" t="n">
+      <c r="A50" s="2" t="n">
         <v>44498</v>
       </c>
-      <c r="B50" s="1" t="n">
+      <c r="B50" s="2" t="n">
         <v>44509</v>
       </c>
       <c r="C50" t="n">
@@ -12203,10 +12215,10 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="1" t="n">
+      <c r="A51" s="2" t="n">
         <v>44603</v>
       </c>
-      <c r="B51" s="1" t="n">
+      <c r="B51" s="2" t="n">
         <v>44610</v>
       </c>
       <c r="C51" t="n">
@@ -12235,10 +12247,10 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="1" t="n">
+      <c r="A52" s="2" t="n">
         <v>44680</v>
       </c>
-      <c r="B52" s="1" t="n">
+      <c r="B52" s="2" t="n">
         <v>44686</v>
       </c>
       <c r="C52" t="n">
@@ -12267,10 +12279,10 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="1" t="n">
+      <c r="A53" s="2" t="n">
         <v>44771</v>
       </c>
-      <c r="B53" s="1" t="n">
+      <c r="B53" s="2" t="n">
         <v>44777</v>
       </c>
       <c r="C53" t="n">
@@ -12299,10 +12311,10 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="1" t="n">
+      <c r="A54" s="2" t="n">
         <v>44865</v>
       </c>
-      <c r="B54" s="1" t="n">
+      <c r="B54" s="2" t="n">
         <v>44868</v>
       </c>
       <c r="C54" t="n">
@@ -12331,10 +12343,10 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="1" t="n">
+      <c r="A55" s="2" t="n">
         <v>44971</v>
       </c>
-      <c r="B55" s="1" t="n">
+      <c r="B55" s="2" t="n">
         <v>44980</v>
       </c>
       <c r="C55" t="n">
@@ -12363,10 +12375,10 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="1" t="n">
+      <c r="A56" s="2" t="n">
         <v>45044</v>
       </c>
-      <c r="B56" s="1" t="n">
+      <c r="B56" s="2" t="n">
         <v>45050</v>
       </c>
       <c r="C56" t="n">
@@ -12395,10 +12407,10 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="1" t="n">
+      <c r="A57" s="2" t="n">
         <v>45138</v>
       </c>
-      <c r="B57" s="1" t="n">
+      <c r="B57" s="2" t="n">
         <v>45142</v>
       </c>
       <c r="C57" t="n">
@@ -12427,10 +12439,10 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="1" t="n">
+      <c r="A58" s="2" t="n">
         <v>45229</v>
       </c>
-      <c r="B58" s="1" t="n">
+      <c r="B58" s="2" t="n">
         <v>45232</v>
       </c>
       <c r="C58" t="n">
@@ -12459,10 +12471,10 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="1" t="n">
+      <c r="A59" s="2" t="n">
         <v>45330</v>
       </c>
-      <c r="B59" s="1" t="n">
+      <c r="B59" s="2" t="n">
         <v>45338</v>
       </c>
       <c r="C59" t="n">
@@ -12491,10 +12503,10 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="1" t="n">
+      <c r="A60" s="2" t="n">
         <v>45412</v>
       </c>
-      <c r="B60" s="1" t="n">
+      <c r="B60" s="2" t="n">
         <v>45414</v>
       </c>
       <c r="C60" t="n">
@@ -12523,10 +12535,10 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="1" t="n">
+      <c r="A61" s="2" t="n">
         <v>45499</v>
       </c>
-      <c r="B61" s="1" t="n">
+      <c r="B61" s="2" t="n">
         <v>45505</v>
       </c>
       <c r="C61" t="n">
@@ -12555,10 +12567,10 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="1" t="n">
+      <c r="A62" s="2" t="n">
         <v>45593</v>
       </c>
-      <c r="B62" s="1" t="n">
+      <c r="B62" s="2" t="n">
         <v>45597</v>
       </c>
       <c r="C62" t="n">
@@ -12587,10 +12599,10 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="1" t="n">
+      <c r="A63" s="2" t="n">
         <v>45701</v>
       </c>
-      <c r="B63" s="1" t="n">
+      <c r="B63" s="2" t="n">
         <v>45709</v>
       </c>
       <c r="C63" t="n">
@@ -12619,10 +12631,10 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="1" t="n">
+      <c r="A64" s="2" t="n">
         <v>45775</v>
       </c>
-      <c r="B64" s="1" t="n">
+      <c r="B64" s="2" t="n">
         <v>45778</v>
       </c>
       <c r="C64" t="n">
@@ -12651,10 +12663,10 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="1" t="n">
+      <c r="A65" s="2" t="n">
         <v>45869</v>
       </c>
-      <c r="B65" s="1" t="n">
+      <c r="B65" s="2" t="n">
         <v>45876</v>
       </c>
       <c r="C65" t="n">
@@ -12683,10 +12695,10 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="1" t="n">
+      <c r="A66" s="2" t="n">
         <v>45961</v>
       </c>
-      <c r="B66" s="1" t="n">
+      <c r="B66" s="2" t="n">
         <v>45968</v>
       </c>
       <c r="C66" t="n">
@@ -12715,10 +12727,10 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="1" t="n">
+      <c r="A67" s="2" t="n">
         <v>46065</v>
       </c>
-      <c r="B67" s="1" t="n">
+      <c r="B67" s="2" t="n">
         <v>46072</v>
       </c>
       <c r="C67" t="n">
@@ -12747,10 +12759,10 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="1" t="n">
+      <c r="A68" s="2" t="n">
         <v>46142</v>
       </c>
-      <c r="B68" s="1" t="n">
+      <c r="B68" s="2" t="n">
         <v>46149</v>
       </c>
       <c r="C68" t="n">
@@ -12779,10 +12791,10 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="1" t="n">
+      <c r="A69" s="2" t="n">
         <v>46234</v>
       </c>
-      <c r="B69" s="1" t="n">
+      <c r="B69" s="2" t="n">
         <v>46240</v>
       </c>
       <c r="C69" t="n">
@@ -12829,12 +12841,12 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>campo</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>valor</t>
         </is>

--- a/salidas/empresas/MET.xlsx
+++ b/salidas/empresas/MET.xlsx
@@ -498,7 +498,7 @@
         <v>38748</v>
       </c>
       <c r="B2" t="n">
-        <v>25.4277400970459</v>
+        <v>25.42773628234863</v>
       </c>
       <c r="C2" t="n">
         <v>44.70588302612305</v>
@@ -517,7 +517,7 @@
         <v>38776</v>
       </c>
       <c r="B3" t="n">
-        <v>25.4074592590332</v>
+        <v>25.4074535369873</v>
       </c>
       <c r="C3" t="n">
         <v>44.67023086547852</v>
@@ -536,7 +536,7 @@
         <v>38807</v>
       </c>
       <c r="B4" t="n">
-        <v>24.52032089233398</v>
+        <v>24.52032279968262</v>
       </c>
       <c r="C4" t="n">
         <v>43.11051559448242</v>
@@ -555,7 +555,7 @@
         <v>38837</v>
       </c>
       <c r="B5" t="n">
-        <v>26.41117668151855</v>
+        <v>26.41118812561035</v>
       </c>
       <c r="C5" t="n">
         <v>46.4349365234375</v>
@@ -574,7 +574,7 @@
         <v>38868</v>
       </c>
       <c r="B6" t="n">
-        <v>26.09181976318359</v>
+        <v>26.09182357788086</v>
       </c>
       <c r="C6" t="n">
         <v>45.87343978881836</v>
@@ -593,7 +593,7 @@
         <v>38898</v>
       </c>
       <c r="B7" t="n">
-        <v>25.96001434326172</v>
+        <v>25.96001815795898</v>
       </c>
       <c r="C7" t="n">
         <v>45.6417121887207</v>
@@ -612,7 +612,7 @@
         <v>38929</v>
       </c>
       <c r="B8" t="n">
-        <v>26.3604907989502</v>
+        <v>26.36048316955566</v>
       </c>
       <c r="C8" t="n">
         <v>46.34580993652344</v>
@@ -631,7 +631,7 @@
         <v>38960</v>
       </c>
       <c r="B9" t="n">
-        <v>27.89649200439453</v>
+        <v>27.8964958190918</v>
       </c>
       <c r="C9" t="n">
         <v>49.04634475708008</v>
@@ -650,7 +650,7 @@
         <v>38990</v>
       </c>
       <c r="B10" t="n">
-        <v>28.73293685913086</v>
+        <v>28.73294067382812</v>
       </c>
       <c r="C10" t="n">
         <v>50.51693344116211</v>
@@ -669,7 +669,7 @@
         <v>39021</v>
       </c>
       <c r="B11" t="n">
-        <v>28.9610481262207</v>
+        <v>28.96105575561523</v>
       </c>
       <c r="C11" t="n">
         <v>50.91800308227539</v>
@@ -688,7 +688,7 @@
         <v>39051</v>
       </c>
       <c r="B12" t="n">
-        <v>30.08026695251465</v>
+        <v>30.08024787902832</v>
       </c>
       <c r="C12" t="n">
         <v>52.34402847290039</v>
@@ -707,7 +707,7 @@
         <v>39082</v>
       </c>
       <c r="B13" t="n">
-        <v>30.22367858886719</v>
+        <v>30.22366714477539</v>
       </c>
       <c r="C13" t="n">
         <v>52.59358215332031</v>
@@ -726,7 +726,7 @@
         <v>39113</v>
       </c>
       <c r="B14" t="n">
-        <v>31.81654930114746</v>
+        <v>31.81655120849609</v>
       </c>
       <c r="C14" t="n">
         <v>55.36541748046875</v>
@@ -745,7 +745,7 @@
         <v>39141</v>
       </c>
       <c r="B15" t="n">
-        <v>32.34921264648438</v>
+        <v>32.34920883178711</v>
       </c>
       <c r="C15" t="n">
         <v>56.29233551025391</v>
@@ -764,7 +764,7 @@
         <v>39172</v>
       </c>
       <c r="B16" t="n">
-        <v>32.34409713745117</v>
+        <v>32.34408187866211</v>
       </c>
       <c r="C16" t="n">
         <v>56.28342056274414</v>
@@ -783,7 +783,7 @@
         <v>39202</v>
       </c>
       <c r="B17" t="n">
-        <v>33.65014266967773</v>
+        <v>33.6501350402832</v>
       </c>
       <c r="C17" t="n">
         <v>58.55614852905273</v>
@@ -802,7 +802,7 @@
         <v>39233</v>
       </c>
       <c r="B18" t="n">
-        <v>34.82815551757812</v>
+        <v>34.82815933227539</v>
       </c>
       <c r="C18" t="n">
         <v>60.60606002807617</v>
@@ -821,7 +821,7 @@
         <v>39263</v>
       </c>
       <c r="B19" t="n">
-        <v>33.02528381347656</v>
+        <v>33.02528762817383</v>
       </c>
       <c r="C19" t="n">
         <v>57.46880722045898</v>
@@ -840,7 +840,7 @@
         <v>39294</v>
       </c>
       <c r="B20" t="n">
-        <v>30.84339904785156</v>
+        <v>30.84340667724609</v>
       </c>
       <c r="C20" t="n">
         <v>53.67201232910156</v>
@@ -859,7 +859,7 @@
         <v>39325</v>
       </c>
       <c r="B21" t="n">
-        <v>32.80504989624023</v>
+        <v>32.8050537109375</v>
       </c>
       <c r="C21" t="n">
         <v>57.0855598449707</v>
@@ -878,7 +878,7 @@
         <v>39355</v>
       </c>
       <c r="B22" t="n">
-        <v>35.71421432495117</v>
+        <v>35.71421051025391</v>
       </c>
       <c r="C22" t="n">
         <v>62.14794921875</v>
@@ -897,7 +897,7 @@
         <v>39386</v>
       </c>
       <c r="B23" t="n">
-        <v>35.26350402832031</v>
+        <v>35.26350784301758</v>
       </c>
       <c r="C23" t="n">
         <v>61.3636360168457</v>
@@ -916,7 +916,7 @@
         <v>39416</v>
       </c>
       <c r="B24" t="n">
-        <v>33.97749328613281</v>
+        <v>33.97749710083008</v>
       </c>
       <c r="C24" t="n">
         <v>58.45811080932617</v>
@@ -935,7 +935,7 @@
         <v>39447</v>
       </c>
       <c r="B25" t="n">
-        <v>31.92091941833496</v>
+        <v>31.92092514038086</v>
       </c>
       <c r="C25" t="n">
         <v>54.91978454589844</v>
@@ -954,7 +954,7 @@
         <v>39478</v>
       </c>
       <c r="B26" t="n">
-        <v>30.50153160095215</v>
+        <v>30.50152015686035</v>
       </c>
       <c r="C26" t="n">
         <v>52.47771835327148</v>
@@ -973,7 +973,7 @@
         <v>39507</v>
       </c>
       <c r="B27" t="n">
-        <v>30.18034744262695</v>
+        <v>30.18035888671875</v>
       </c>
       <c r="C27" t="n">
         <v>51.92513275146484</v>
@@ -992,7 +992,7 @@
         <v>39538</v>
       </c>
       <c r="B28" t="n">
-        <v>31.21640586853027</v>
+        <v>31.21639060974121</v>
       </c>
       <c r="C28" t="n">
         <v>53.70766448974609</v>
@@ -1011,7 +1011,7 @@
         <v>39568</v>
       </c>
       <c r="B29" t="n">
-        <v>31.52203941345215</v>
+        <v>31.52203178405762</v>
       </c>
       <c r="C29" t="n">
         <v>54.23351287841797</v>
@@ -1030,7 +1030,7 @@
         <v>39599</v>
       </c>
       <c r="B30" t="n">
-        <v>31.09725952148438</v>
+        <v>31.09726142883301</v>
       </c>
       <c r="C30" t="n">
         <v>53.5026741027832</v>
@@ -1049,7 +1049,7 @@
         <v>39629</v>
       </c>
       <c r="B31" t="n">
-        <v>27.33636474609375</v>
+        <v>27.33637619018555</v>
       </c>
       <c r="C31" t="n">
         <v>47.03208541870117</v>
@@ -1068,7 +1068,7 @@
         <v>39660</v>
       </c>
       <c r="B32" t="n">
-        <v>26.30031204223633</v>
+        <v>26.30031585693359</v>
       </c>
       <c r="C32" t="n">
         <v>45.24955368041992</v>
@@ -1087,7 +1087,7 @@
         <v>39691</v>
       </c>
       <c r="B33" t="n">
-        <v>28.0771541595459</v>
+        <v>28.0771598815918</v>
       </c>
       <c r="C33" t="n">
         <v>48.30659484863281</v>
@@ -1106,7 +1106,7 @@
         <v>39721</v>
       </c>
       <c r="B34" t="n">
-        <v>29.00959968566895</v>
+        <v>29.00959777832031</v>
       </c>
       <c r="C34" t="n">
         <v>49.91087341308594</v>
@@ -1125,7 +1125,7 @@
         <v>39752</v>
       </c>
       <c r="B35" t="n">
-        <v>17.20891189575195</v>
+        <v>17.20890617370605</v>
       </c>
       <c r="C35" t="n">
         <v>29.60784339904785</v>
@@ -1144,7 +1144,7 @@
         <v>39782</v>
       </c>
       <c r="B36" t="n">
-        <v>15.21341133117676</v>
+        <v>15.21340942382812</v>
       </c>
       <c r="C36" t="n">
         <v>25.63279914855957</v>
@@ -1163,7 +1163,7 @@
         <v>39813</v>
       </c>
       <c r="B37" t="n">
-        <v>18.44017601013184</v>
+        <v>18.44018173217773</v>
       </c>
       <c r="C37" t="n">
         <v>31.06951904296875</v>
@@ -1182,7 +1182,7 @@
         <v>39844</v>
       </c>
       <c r="B38" t="n">
-        <v>15.19754791259766</v>
+        <v>15.19754314422607</v>
       </c>
       <c r="C38" t="n">
         <v>25.6060619354248</v>
@@ -1201,7 +1201,7 @@
         <v>39872</v>
       </c>
       <c r="B39" t="n">
-        <v>9.764934539794922</v>
+        <v>9.764935493469238</v>
       </c>
       <c r="C39" t="n">
         <v>16.45276260375977</v>
@@ -1220,7 +1220,7 @@
         <v>39903</v>
       </c>
       <c r="B40" t="n">
-        <v>12.04483318328857</v>
+        <v>12.04483795166016</v>
       </c>
       <c r="C40" t="n">
         <v>20.29411888122559</v>
@@ -1239,7 +1239,7 @@
         <v>39933</v>
       </c>
       <c r="B41" t="n">
-        <v>15.73709774017334</v>
+        <v>15.73709678649902</v>
       </c>
       <c r="C41" t="n">
         <v>26.51515197753906</v>
@@ -1258,7 +1258,7 @@
         <v>39964</v>
       </c>
       <c r="B42" t="n">
-        <v>16.66281890869141</v>
+        <v>16.66280746459961</v>
       </c>
       <c r="C42" t="n">
         <v>28.07486534118652</v>
@@ -1277,7 +1277,7 @@
         <v>39994</v>
       </c>
       <c r="B43" t="n">
-        <v>15.87463283538818</v>
+        <v>15.8746395111084</v>
       </c>
       <c r="C43" t="n">
         <v>26.74688148498535</v>
@@ -1296,7 +1296,7 @@
         <v>40025</v>
       </c>
       <c r="B44" t="n">
-        <v>17.95879745483398</v>
+        <v>17.95880126953125</v>
       </c>
       <c r="C44" t="n">
         <v>30.25846672058105</v>
@@ -1315,7 +1315,7 @@
         <v>40056</v>
       </c>
       <c r="B45" t="n">
-        <v>19.97421455383301</v>
+        <v>19.97421073913574</v>
       </c>
       <c r="C45" t="n">
         <v>33.65419006347656</v>
@@ -1340,7 +1340,7 @@
         <v>40086</v>
       </c>
       <c r="B46" t="n">
-        <v>20.13819313049316</v>
+        <v>20.13819122314453</v>
       </c>
       <c r="C46" t="n">
         <v>33.93048095703125</v>
@@ -1365,7 +1365,7 @@
         <v>40117</v>
       </c>
       <c r="B47" t="n">
-        <v>18.00112152099609</v>
+        <v>18.00112724304199</v>
       </c>
       <c r="C47" t="n">
         <v>30.32976722717285</v>
@@ -1390,7 +1390,7 @@
         <v>40147</v>
       </c>
       <c r="B48" t="n">
-        <v>18.49504280090332</v>
+        <v>18.49504470825195</v>
       </c>
       <c r="C48" t="n">
         <v>30.47237014770508</v>
@@ -1415,7 +1415,7 @@
         <v>40178</v>
       </c>
       <c r="B49" t="n">
-        <v>19.12253952026367</v>
+        <v>19.1225414276123</v>
       </c>
       <c r="C49" t="n">
         <v>31.50623893737793</v>
@@ -1440,7 +1440,7 @@
         <v>40209</v>
       </c>
       <c r="B50" t="n">
-        <v>19.10632133483887</v>
+        <v>19.1063175201416</v>
       </c>
       <c r="C50" t="n">
         <v>31.47950172424316</v>
@@ -1465,7 +1465,7 @@
         <v>40237</v>
       </c>
       <c r="B51" t="n">
-        <v>19.68513488769531</v>
+        <v>19.68512344360352</v>
       </c>
       <c r="C51" t="n">
         <v>32.43315505981445</v>
@@ -1490,7 +1490,7 @@
         <v>40268</v>
       </c>
       <c r="B52" t="n">
-        <v>23.44471740722656</v>
+        <v>23.44472312927246</v>
       </c>
       <c r="C52" t="n">
         <v>38.6274528503418</v>
@@ -1515,7 +1515,7 @@
         <v>40298</v>
       </c>
       <c r="B53" t="n">
-        <v>24.65645408630371</v>
+        <v>24.65644454956055</v>
       </c>
       <c r="C53" t="n">
         <v>40.62388610839844</v>
@@ -1540,7 +1540,7 @@
         <v>40329</v>
       </c>
       <c r="B54" t="n">
-        <v>21.90301895141602</v>
+        <v>21.90302276611328</v>
       </c>
       <c r="C54" t="n">
         <v>36.08734512329102</v>
@@ -1565,7 +1565,7 @@
         <v>40359</v>
       </c>
       <c r="B55" t="n">
-        <v>20.42622756958008</v>
+        <v>20.42622947692871</v>
       </c>
       <c r="C55" t="n">
         <v>33.65419006347656</v>
@@ -1590,7 +1590,7 @@
         <v>40390</v>
       </c>
       <c r="B56" t="n">
-        <v>22.7523136138916</v>
+        <v>22.75230598449707</v>
       </c>
       <c r="C56" t="n">
         <v>37.48662948608398</v>
@@ -1615,7 +1615,7 @@
         <v>40421</v>
       </c>
       <c r="B57" t="n">
-        <v>20.36672210693359</v>
+        <v>20.36672973632812</v>
       </c>
       <c r="C57" t="n">
         <v>33.55614852905273</v>
@@ -1640,7 +1640,7 @@
         <v>40451</v>
       </c>
       <c r="B58" t="n">
-        <v>20.79948425292969</v>
+        <v>20.79948616027832</v>
       </c>
       <c r="C58" t="n">
         <v>34.26916122436523</v>
@@ -1690,7 +1690,7 @@
         <v>40512</v>
       </c>
       <c r="B60" t="n">
-        <v>20.99942779541016</v>
+        <v>20.99942207336426</v>
       </c>
       <c r="C60" t="n">
         <v>34.00178146362305</v>
@@ -1715,7 +1715,7 @@
         <v>40543</v>
       </c>
       <c r="B61" t="n">
-        <v>24.46171760559082</v>
+        <v>24.46171379089355</v>
       </c>
       <c r="C61" t="n">
         <v>39.60784149169922</v>
@@ -1740,7 +1740,7 @@
         <v>40574</v>
       </c>
       <c r="B62" t="n">
-        <v>25.19380569458008</v>
+        <v>25.19380760192871</v>
       </c>
       <c r="C62" t="n">
         <v>40.7932243347168</v>
@@ -1765,7 +1765,7 @@
         <v>40602</v>
       </c>
       <c r="B63" t="n">
-        <v>26.06900787353516</v>
+        <v>26.06900596618652</v>
       </c>
       <c r="C63" t="n">
         <v>42.2103385925293</v>
@@ -1794,7 +1794,7 @@
         <v>40633</v>
       </c>
       <c r="B64" t="n">
-        <v>24.62135314941406</v>
+        <v>24.62134552001953</v>
       </c>
       <c r="C64" t="n">
         <v>39.86631011962891</v>
@@ -1823,7 +1823,7 @@
         <v>40663</v>
       </c>
       <c r="B65" t="n">
-        <v>25.7552547454834</v>
+        <v>25.75525665283203</v>
       </c>
       <c r="C65" t="n">
         <v>41.70231628417969</v>
@@ -1852,7 +1852,7 @@
         <v>40694</v>
       </c>
       <c r="B66" t="n">
-        <v>24.27456283569336</v>
+        <v>24.27457809448242</v>
       </c>
       <c r="C66" t="n">
         <v>39.30481338500977</v>
@@ -1881,7 +1881,7 @@
         <v>40724</v>
       </c>
       <c r="B67" t="n">
-        <v>24.1479663848877</v>
+        <v>24.14796829223633</v>
       </c>
       <c r="C67" t="n">
         <v>39.09982299804688</v>
@@ -1910,7 +1910,7 @@
         <v>40755</v>
       </c>
       <c r="B68" t="n">
-        <v>22.68378067016602</v>
+        <v>22.68377876281738</v>
       </c>
       <c r="C68" t="n">
         <v>36.72905349731445</v>
@@ -1939,7 +1939,7 @@
         <v>40786</v>
       </c>
       <c r="B69" t="n">
-        <v>18.49490547180176</v>
+        <v>18.49490737915039</v>
       </c>
       <c r="C69" t="n">
         <v>29.94652366638184</v>
@@ -1968,7 +1968,7 @@
         <v>40816</v>
       </c>
       <c r="B70" t="n">
-        <v>15.41793346405029</v>
+        <v>15.41793155670166</v>
       </c>
       <c r="C70" t="n">
         <v>24.9643497467041</v>
@@ -2026,7 +2026,7 @@
         <v>40877</v>
       </c>
       <c r="B72" t="n">
-        <v>17.70477294921875</v>
+        <v>17.70477485656738</v>
       </c>
       <c r="C72" t="n">
         <v>28.05704116821289</v>
@@ -2084,7 +2084,7 @@
         <v>40939</v>
       </c>
       <c r="B74" t="n">
-        <v>19.87006187438965</v>
+        <v>19.87006568908691</v>
       </c>
       <c r="C74" t="n">
         <v>31.4884147644043</v>
@@ -2113,7 +2113,7 @@
         <v>40968</v>
       </c>
       <c r="B75" t="n">
-        <v>21.68103408813477</v>
+        <v>21.6810359954834</v>
       </c>
       <c r="C75" t="n">
         <v>34.3582878112793</v>
@@ -2200,7 +2200,7 @@
         <v>41060</v>
       </c>
       <c r="B78" t="n">
-        <v>16.42809677124023</v>
+        <v>16.42809867858887</v>
       </c>
       <c r="C78" t="n">
         <v>26.03386878967285</v>
@@ -2229,7 +2229,7 @@
         <v>41090</v>
       </c>
       <c r="B79" t="n">
-        <v>17.35045051574707</v>
+        <v>17.35045623779297</v>
       </c>
       <c r="C79" t="n">
         <v>27.49554443359375</v>
@@ -2258,7 +2258,7 @@
         <v>41121</v>
       </c>
       <c r="B80" t="n">
-        <v>17.30545425415039</v>
+        <v>17.30545806884766</v>
       </c>
       <c r="C80" t="n">
         <v>27.42424201965332</v>
@@ -2287,7 +2287,7 @@
         <v>41152</v>
       </c>
       <c r="B81" t="n">
-        <v>19.19516944885254</v>
+        <v>19.19517135620117</v>
       </c>
       <c r="C81" t="n">
         <v>30.41889572143555</v>
@@ -2316,7 +2316,7 @@
         <v>41182</v>
       </c>
       <c r="B82" t="n">
-        <v>19.38076400756836</v>
+        <v>19.38076782226562</v>
       </c>
       <c r="C82" t="n">
         <v>30.7130126953125</v>
@@ -2345,7 +2345,7 @@
         <v>41213</v>
       </c>
       <c r="B83" t="n">
-        <v>19.96005439758301</v>
+        <v>19.96004676818848</v>
       </c>
       <c r="C83" t="n">
         <v>31.63101577758789</v>
@@ -2374,7 +2374,7 @@
         <v>41243</v>
       </c>
       <c r="B84" t="n">
-        <v>19.0693302154541</v>
+        <v>19.06933784484863</v>
       </c>
       <c r="C84" t="n">
         <v>29.58110427856445</v>
@@ -2461,7 +2461,7 @@
         <v>41333</v>
       </c>
       <c r="B87" t="n">
-        <v>20.46116638183594</v>
+        <v>20.46116828918457</v>
       </c>
       <c r="C87" t="n">
         <v>31.58645248413086</v>
@@ -2490,7 +2490,7 @@
         <v>41364</v>
       </c>
       <c r="B88" t="n">
-        <v>21.95071983337402</v>
+        <v>21.95072364807129</v>
       </c>
       <c r="C88" t="n">
         <v>33.88591766357422</v>
@@ -2519,7 +2519,7 @@
         <v>41394</v>
       </c>
       <c r="B89" t="n">
-        <v>22.51074981689453</v>
+        <v>22.5107536315918</v>
       </c>
       <c r="C89" t="n">
         <v>34.75044631958008</v>
@@ -2548,7 +2548,7 @@
         <v>41425</v>
       </c>
       <c r="B90" t="n">
-        <v>25.69791984558105</v>
+        <v>25.69791412353516</v>
       </c>
       <c r="C90" t="n">
         <v>39.40285110473633</v>
@@ -2577,7 +2577,7 @@
         <v>41455</v>
       </c>
       <c r="B91" t="n">
-        <v>26.59888458251953</v>
+        <v>26.5988826751709</v>
       </c>
       <c r="C91" t="n">
         <v>40.7843132019043</v>
@@ -2606,7 +2606,7 @@
         <v>41486</v>
       </c>
       <c r="B92" t="n">
-        <v>28.14506340026855</v>
+        <v>28.14506912231445</v>
       </c>
       <c r="C92" t="n">
         <v>43.15507888793945</v>
@@ -2635,7 +2635,7 @@
         <v>41517</v>
       </c>
       <c r="B93" t="n">
-        <v>26.99857902526855</v>
+        <v>26.99858665466309</v>
       </c>
       <c r="C93" t="n">
         <v>41.16755676269531</v>
@@ -2664,7 +2664,7 @@
         <v>41547</v>
       </c>
       <c r="B94" t="n">
-        <v>27.44282341003418</v>
+        <v>27.44281387329102</v>
       </c>
       <c r="C94" t="n">
         <v>41.84492111206055</v>
@@ -2693,7 +2693,7 @@
         <v>41578</v>
       </c>
       <c r="B95" t="n">
-        <v>27.65322875976562</v>
+        <v>27.65323829650879</v>
       </c>
       <c r="C95" t="n">
         <v>42.16577529907227</v>
@@ -2780,7 +2780,7 @@
         <v>41670</v>
       </c>
       <c r="B98" t="n">
-        <v>28.83523178100586</v>
+        <v>28.83523750305176</v>
       </c>
       <c r="C98" t="n">
         <v>43.71657943725586</v>
@@ -2809,7 +2809,7 @@
         <v>41698</v>
       </c>
       <c r="B99" t="n">
-        <v>29.96268272399902</v>
+        <v>29.96269416809082</v>
       </c>
       <c r="C99" t="n">
         <v>45.16042709350586</v>
@@ -2838,7 +2838,7 @@
         <v>41729</v>
       </c>
       <c r="B100" t="n">
-        <v>31.22222900390625</v>
+        <v>31.22221755981445</v>
       </c>
       <c r="C100" t="n">
         <v>47.05882263183594</v>
@@ -2867,7 +2867,7 @@
         <v>41759</v>
       </c>
       <c r="B101" t="n">
-        <v>30.95611381530762</v>
+        <v>30.95612907409668</v>
       </c>
       <c r="C101" t="n">
         <v>46.65775299072266</v>
@@ -2896,7 +2896,7 @@
         <v>41790</v>
       </c>
       <c r="B102" t="n">
-        <v>30.32900428771973</v>
+        <v>30.32900238037109</v>
       </c>
       <c r="C102" t="n">
         <v>45.39215850830078</v>
@@ -2954,7 +2954,7 @@
         <v>41851</v>
       </c>
       <c r="B104" t="n">
-        <v>31.32348442077637</v>
+        <v>31.32347679138184</v>
       </c>
       <c r="C104" t="n">
         <v>46.88056945800781</v>
@@ -2983,7 +2983,7 @@
         <v>41882</v>
       </c>
       <c r="B105" t="n">
-        <v>32.82018661499023</v>
+        <v>32.82018280029297</v>
       </c>
       <c r="C105" t="n">
         <v>48.78787994384766</v>
@@ -3186,7 +3186,7 @@
         <v>42094</v>
       </c>
       <c r="B112" t="n">
-        <v>30.72410202026367</v>
+        <v>30.72410011291504</v>
       </c>
       <c r="C112" t="n">
         <v>45.05347442626953</v>
@@ -3215,7 +3215,7 @@
         <v>42124</v>
       </c>
       <c r="B113" t="n">
-        <v>31.17388153076172</v>
+        <v>31.17387962341309</v>
       </c>
       <c r="C113" t="n">
         <v>45.7130126953125</v>
@@ -3244,7 +3244,7 @@
         <v>42155</v>
       </c>
       <c r="B114" t="n">
-        <v>31.9951343536377</v>
+        <v>31.99514198303223</v>
       </c>
       <c r="C114" t="n">
         <v>46.57754135131836</v>
@@ -3273,7 +3273,7 @@
         <v>42185</v>
       </c>
       <c r="B115" t="n">
-        <v>34.27876663208008</v>
+        <v>34.27877426147461</v>
       </c>
       <c r="C115" t="n">
         <v>49.90196228027344</v>
@@ -3302,7 +3302,7 @@
         <v>42216</v>
       </c>
       <c r="B116" t="n">
-        <v>34.12570953369141</v>
+        <v>34.12571334838867</v>
       </c>
       <c r="C116" t="n">
         <v>49.67914581298828</v>
@@ -3331,7 +3331,7 @@
         <v>42247</v>
       </c>
       <c r="B117" t="n">
-        <v>30.87977027893066</v>
+        <v>30.87978553771973</v>
       </c>
       <c r="C117" t="n">
         <v>44.65240478515625</v>
@@ -3360,7 +3360,7 @@
         <v>42277</v>
       </c>
       <c r="B118" t="n">
-        <v>29.06150245666504</v>
+        <v>29.0615062713623</v>
       </c>
       <c r="C118" t="n">
         <v>42.02317428588867</v>
@@ -3389,7 +3389,7 @@
         <v>42308</v>
       </c>
       <c r="B119" t="n">
-        <v>31.05236053466797</v>
+        <v>31.05235862731934</v>
       </c>
       <c r="C119" t="n">
         <v>44.90196228027344</v>
@@ -3418,7 +3418,7 @@
         <v>42338</v>
       </c>
       <c r="B120" t="n">
-        <v>31.72140502929688</v>
+        <v>31.72140121459961</v>
       </c>
       <c r="C120" t="n">
         <v>45.53475952148438</v>
@@ -3447,7 +3447,7 @@
         <v>42369</v>
       </c>
       <c r="B121" t="n">
-        <v>29.9332332611084</v>
+        <v>29.93323516845703</v>
       </c>
       <c r="C121" t="n">
         <v>42.96791458129883</v>
@@ -3505,7 +3505,7 @@
         <v>42429</v>
       </c>
       <c r="B123" t="n">
-        <v>24.77983093261719</v>
+        <v>24.77983474731445</v>
       </c>
       <c r="C123" t="n">
         <v>35.25846862792969</v>
@@ -3534,7 +3534,7 @@
         <v>42460</v>
       </c>
       <c r="B124" t="n">
-        <v>27.52340126037598</v>
+        <v>27.52339744567871</v>
       </c>
       <c r="C124" t="n">
         <v>39.16220855712891</v>
@@ -3563,7 +3563,7 @@
         <v>42490</v>
       </c>
       <c r="B125" t="n">
-        <v>28.2500114440918</v>
+        <v>28.2500057220459</v>
       </c>
       <c r="C125" t="n">
         <v>40.19607925415039</v>
@@ -3592,7 +3592,7 @@
         <v>42521</v>
       </c>
       <c r="B126" t="n">
-        <v>28.79400253295898</v>
+        <v>28.79400062561035</v>
       </c>
       <c r="C126" t="n">
         <v>40.59714889526367</v>
@@ -3621,7 +3621,7 @@
         <v>42551</v>
       </c>
       <c r="B127" t="n">
-        <v>25.17815780639648</v>
+        <v>25.17816162109375</v>
       </c>
       <c r="C127" t="n">
         <v>35.49910736083984</v>
@@ -3650,7 +3650,7 @@
         <v>42582</v>
       </c>
       <c r="B128" t="n">
-        <v>27.01768112182617</v>
+        <v>27.0176887512207</v>
       </c>
       <c r="C128" t="n">
         <v>38.09269332885742</v>
@@ -3679,7 +3679,7 @@
         <v>42613</v>
       </c>
       <c r="B129" t="n">
-        <v>27.68833923339844</v>
+        <v>27.6883487701416</v>
       </c>
       <c r="C129" t="n">
         <v>38.68092727661133</v>
@@ -3708,7 +3708,7 @@
         <v>42643</v>
       </c>
       <c r="B130" t="n">
-        <v>28.3454647064209</v>
+        <v>28.34545135498047</v>
       </c>
       <c r="C130" t="n">
         <v>39.59893035888672</v>
@@ -3795,7 +3795,7 @@
         <v>42735</v>
       </c>
       <c r="B133" t="n">
-        <v>34.68011474609375</v>
+        <v>34.68009948730469</v>
       </c>
       <c r="C133" t="n">
         <v>48.03030395507812</v>
@@ -3824,7 +3824,7 @@
         <v>42766</v>
       </c>
       <c r="B134" t="n">
-        <v>35.01474380493164</v>
+        <v>35.01474761962891</v>
       </c>
       <c r="C134" t="n">
         <v>48.49375915527344</v>
@@ -3853,7 +3853,7 @@
         <v>42794</v>
       </c>
       <c r="B135" t="n">
-        <v>33.99733734130859</v>
+        <v>33.99732208251953</v>
       </c>
       <c r="C135" t="n">
         <v>46.73796844482422</v>
@@ -3882,7 +3882,7 @@
         <v>42825</v>
       </c>
       <c r="B136" t="n">
-        <v>34.24368286132812</v>
+        <v>34.24368667602539</v>
       </c>
       <c r="C136" t="n">
         <v>47.0766487121582</v>
@@ -3911,7 +3911,7 @@
         <v>42855</v>
       </c>
       <c r="B137" t="n">
-        <v>33.58888626098633</v>
+        <v>33.58889007568359</v>
       </c>
       <c r="C137" t="n">
         <v>46.17647171020508</v>
@@ -3940,7 +3940,7 @@
         <v>42886</v>
       </c>
       <c r="B138" t="n">
-        <v>33.05171203613281</v>
+        <v>33.05170440673828</v>
       </c>
       <c r="C138" t="n">
         <v>45.08912658691406</v>
@@ -3994,7 +3994,7 @@
         <v>42947</v>
       </c>
       <c r="B140" t="n">
-        <v>35.93288040161133</v>
+        <v>35.93287658691406</v>
       </c>
       <c r="C140" t="n">
         <v>49.01960754394531</v>
@@ -4050,7 +4050,7 @@
         <v>43008</v>
       </c>
       <c r="B142" t="n">
-        <v>38.35749435424805</v>
+        <v>38.35748672485352</v>
       </c>
       <c r="C142" t="n">
         <v>51.95000076293945</v>
@@ -4079,7 +4079,7 @@
         <v>43039</v>
       </c>
       <c r="B143" t="n">
-        <v>39.56099700927734</v>
+        <v>39.56100845336914</v>
       </c>
       <c r="C143" t="n">
         <v>53.58000183105469</v>
@@ -4108,7 +4108,7 @@
         <v>43069</v>
       </c>
       <c r="B144" t="n">
-        <v>39.92138290405273</v>
+        <v>39.92137145996094</v>
       </c>
       <c r="C144" t="n">
         <v>53.68000030517578</v>
@@ -4135,7 +4135,7 @@
         <v>43100</v>
       </c>
       <c r="B145" t="n">
-        <v>37.60106658935547</v>
+        <v>37.60105514526367</v>
       </c>
       <c r="C145" t="n">
         <v>50.56000137329102</v>
@@ -4162,7 +4162,7 @@
         <v>43131</v>
       </c>
       <c r="B146" t="n">
-        <v>35.749267578125</v>
+        <v>35.74927139282227</v>
       </c>
       <c r="C146" t="n">
         <v>48.06999969482422</v>
@@ -4189,7 +4189,7 @@
         <v>43159</v>
       </c>
       <c r="B147" t="n">
-        <v>34.63743209838867</v>
+        <v>34.63744354248047</v>
       </c>
       <c r="C147" t="n">
         <v>46.18999862670898</v>
@@ -4245,7 +4245,7 @@
         <v>43220</v>
       </c>
       <c r="B149" t="n">
-        <v>35.74728012084961</v>
+        <v>35.74727630615234</v>
       </c>
       <c r="C149" t="n">
         <v>47.66999816894531</v>
@@ -4274,7 +4274,7 @@
         <v>43251</v>
       </c>
       <c r="B150" t="n">
-        <v>34.81486892700195</v>
+        <v>34.81488037109375</v>
       </c>
       <c r="C150" t="n">
         <v>45.9900016784668</v>
@@ -4303,7 +4303,7 @@
         <v>43281</v>
       </c>
       <c r="B151" t="n">
-        <v>33.00562286376953</v>
+        <v>33.0056266784668</v>
       </c>
       <c r="C151" t="n">
         <v>43.59999847412109</v>
@@ -4361,7 +4361,7 @@
         <v>43343</v>
       </c>
       <c r="B153" t="n">
-        <v>35.05795288085938</v>
+        <v>35.05794906616211</v>
       </c>
       <c r="C153" t="n">
         <v>45.88999938964844</v>
@@ -4419,7 +4419,7 @@
         <v>43404</v>
       </c>
       <c r="B155" t="n">
-        <v>31.46735954284668</v>
+        <v>31.46736335754395</v>
       </c>
       <c r="C155" t="n">
         <v>41.18999862670898</v>
@@ -4448,7 +4448,7 @@
         <v>43434</v>
       </c>
       <c r="B156" t="n">
-        <v>34.42700958251953</v>
+        <v>34.42699432373047</v>
       </c>
       <c r="C156" t="n">
         <v>44.63000106811523</v>
@@ -4477,7 +4477,7 @@
         <v>43465</v>
       </c>
       <c r="B157" t="n">
-        <v>31.67315483093262</v>
+        <v>31.67315292358398</v>
       </c>
       <c r="C157" t="n">
         <v>41.06000137329102</v>
@@ -4506,7 +4506,7 @@
         <v>43496</v>
       </c>
       <c r="B158" t="n">
-        <v>35.22924423217773</v>
+        <v>35.22924041748047</v>
       </c>
       <c r="C158" t="n">
         <v>45.66999816894531</v>
@@ -4564,7 +4564,7 @@
         <v>43555</v>
       </c>
       <c r="B160" t="n">
-        <v>33.14363098144531</v>
+        <v>33.14361953735352</v>
       </c>
       <c r="C160" t="n">
         <v>42.56999969482422</v>
@@ -4593,7 +4593,7 @@
         <v>43585</v>
       </c>
       <c r="B161" t="n">
-        <v>35.91531753540039</v>
+        <v>35.91532897949219</v>
       </c>
       <c r="C161" t="n">
         <v>46.13000106811523</v>
@@ -4622,7 +4622,7 @@
         <v>43616</v>
       </c>
       <c r="B162" t="n">
-        <v>36.31045532226562</v>
+        <v>36.31045150756836</v>
       </c>
       <c r="C162" t="n">
         <v>46.20999908447266</v>
@@ -4651,7 +4651,7 @@
         <v>43646</v>
       </c>
       <c r="B163" t="n">
-        <v>39.02920913696289</v>
+        <v>39.02922439575195</v>
       </c>
       <c r="C163" t="n">
         <v>49.66999816894531</v>
@@ -4680,7 +4680,7 @@
         <v>43677</v>
       </c>
       <c r="B164" t="n">
-        <v>38.8327751159668</v>
+        <v>38.83277130126953</v>
       </c>
       <c r="C164" t="n">
         <v>49.41999816894531</v>
@@ -4709,7 +4709,7 @@
         <v>43708</v>
       </c>
       <c r="B165" t="n">
-        <v>35.13653945922852</v>
+        <v>35.13655471801758</v>
       </c>
       <c r="C165" t="n">
         <v>44.29999923706055</v>
@@ -4738,7 +4738,7 @@
         <v>43738</v>
       </c>
       <c r="B166" t="n">
-        <v>37.40495681762695</v>
+        <v>37.40496444702148</v>
       </c>
       <c r="C166" t="n">
         <v>47.15999984741211</v>
@@ -4767,7 +4767,7 @@
         <v>43769</v>
       </c>
       <c r="B167" t="n">
-        <v>37.11149215698242</v>
+        <v>37.11149978637695</v>
       </c>
       <c r="C167" t="n">
         <v>46.79000091552734</v>
@@ -4796,7 +4796,7 @@
         <v>43799</v>
       </c>
       <c r="B168" t="n">
-        <v>39.9581413269043</v>
+        <v>39.95814514160156</v>
       </c>
       <c r="C168" t="n">
         <v>49.90999984741211</v>
@@ -4825,7 +4825,7 @@
         <v>43830</v>
       </c>
       <c r="B169" t="n">
-        <v>40.80677795410156</v>
+        <v>40.80678558349609</v>
       </c>
       <c r="C169" t="n">
         <v>50.97000122070312</v>
@@ -4854,7 +4854,7 @@
         <v>43861</v>
       </c>
       <c r="B170" t="n">
-        <v>39.79801940917969</v>
+        <v>39.79802703857422</v>
       </c>
       <c r="C170" t="n">
         <v>49.70999908447266</v>
@@ -4883,7 +4883,7 @@
         <v>43890</v>
       </c>
       <c r="B171" t="n">
-        <v>34.50723648071289</v>
+        <v>34.50723266601562</v>
       </c>
       <c r="C171" t="n">
         <v>42.72000122070312</v>
@@ -4912,7 +4912,7 @@
         <v>43921</v>
       </c>
       <c r="B172" t="n">
-        <v>24.69302940368652</v>
+        <v>24.69302749633789</v>
       </c>
       <c r="C172" t="n">
         <v>30.56999969482422</v>
@@ -4941,7 +4941,7 @@
         <v>43951</v>
       </c>
       <c r="B173" t="n">
-        <v>29.14374542236328</v>
+        <v>29.14374923706055</v>
       </c>
       <c r="C173" t="n">
         <v>36.08000183105469</v>
@@ -4999,7 +4999,7 @@
         <v>44012</v>
       </c>
       <c r="B175" t="n">
-        <v>29.91656494140625</v>
+        <v>29.91655921936035</v>
       </c>
       <c r="C175" t="n">
         <v>36.52000045776367</v>
@@ -5028,7 +5028,7 @@
         <v>44043</v>
       </c>
       <c r="B176" t="n">
-        <v>31.00607299804688</v>
+        <v>31.00605964660645</v>
       </c>
       <c r="C176" t="n">
         <v>37.84999847412109</v>
@@ -5057,7 +5057,7 @@
         <v>44074</v>
       </c>
       <c r="B177" t="n">
-        <v>31.89337730407715</v>
+        <v>31.89338493347168</v>
       </c>
       <c r="C177" t="n">
         <v>38.45999908447266</v>
@@ -5086,7 +5086,7 @@
         <v>44104</v>
       </c>
       <c r="B178" t="n">
-        <v>30.82362365722656</v>
+        <v>30.82363319396973</v>
       </c>
       <c r="C178" t="n">
         <v>37.16999816894531</v>
@@ -5115,7 +5115,7 @@
         <v>44135</v>
       </c>
       <c r="B179" t="n">
-        <v>31.38753509521484</v>
+        <v>31.38752365112305</v>
       </c>
       <c r="C179" t="n">
         <v>37.84999847412109</v>
@@ -5144,7 +5144,7 @@
         <v>44165</v>
       </c>
       <c r="B180" t="n">
-        <v>38.75802230834961</v>
+        <v>38.75801849365234</v>
       </c>
       <c r="C180" t="n">
         <v>46.16999816894531</v>
@@ -5173,7 +5173,7 @@
         <v>44196</v>
       </c>
       <c r="B181" t="n">
-        <v>39.41280364990234</v>
+        <v>39.41280746459961</v>
       </c>
       <c r="C181" t="n">
         <v>46.95000076293945</v>
@@ -5202,7 +5202,7 @@
         <v>44227</v>
       </c>
       <c r="B182" t="n">
-        <v>40.420166015625</v>
+        <v>40.42015838623047</v>
       </c>
       <c r="C182" t="n">
         <v>48.15000152587891</v>
@@ -5260,7 +5260,7 @@
         <v>44286</v>
       </c>
       <c r="B184" t="n">
-        <v>51.51091384887695</v>
+        <v>51.51091766357422</v>
       </c>
       <c r="C184" t="n">
         <v>60.79000091552734</v>
@@ -5289,7 +5289,7 @@
         <v>44316</v>
       </c>
       <c r="B185" t="n">
-        <v>53.91742324829102</v>
+        <v>53.91741561889648</v>
       </c>
       <c r="C185" t="n">
         <v>63.63000106811523</v>
@@ -5347,7 +5347,7 @@
         <v>44377</v>
       </c>
       <c r="B187" t="n">
-        <v>51.0794677734375</v>
+        <v>51.0794792175293</v>
       </c>
       <c r="C187" t="n">
         <v>59.84999847412109</v>
@@ -5376,7 +5376,7 @@
         <v>44408</v>
       </c>
       <c r="B188" t="n">
-        <v>49.24454879760742</v>
+        <v>49.24453735351562</v>
       </c>
       <c r="C188" t="n">
         <v>57.70000076293945</v>
@@ -5405,7 +5405,7 @@
         <v>44439</v>
       </c>
       <c r="B189" t="n">
-        <v>53.33610534667969</v>
+        <v>53.33610153198242</v>
       </c>
       <c r="C189" t="n">
         <v>62</v>
@@ -5434,7 +5434,7 @@
         <v>44469</v>
       </c>
       <c r="B190" t="n">
-        <v>53.10383605957031</v>
+        <v>53.10382843017578</v>
       </c>
       <c r="C190" t="n">
         <v>61.72999954223633</v>
@@ -5463,7 +5463,7 @@
         <v>44500</v>
       </c>
       <c r="B191" t="n">
-        <v>54.02431869506836</v>
+        <v>54.02431106567383</v>
       </c>
       <c r="C191" t="n">
         <v>62.79999923706055</v>
@@ -5492,7 +5492,7 @@
         <v>44530</v>
       </c>
       <c r="B192" t="n">
-        <v>50.8442268371582</v>
+        <v>50.84423446655273</v>
       </c>
       <c r="C192" t="n">
         <v>58.65999984741211</v>
@@ -5521,7 +5521,7 @@
         <v>44561</v>
       </c>
       <c r="B193" t="n">
-        <v>54.16392135620117</v>
+        <v>54.1639289855957</v>
       </c>
       <c r="C193" t="n">
         <v>62.4900016784668</v>
@@ -5550,7 +5550,7 @@
         <v>44592</v>
       </c>
       <c r="B194" t="n">
-        <v>58.12502288818359</v>
+        <v>58.12503051757812</v>
       </c>
       <c r="C194" t="n">
         <v>67.05999755859375</v>
@@ -5579,7 +5579,7 @@
         <v>44620</v>
       </c>
       <c r="B195" t="n">
-        <v>58.95996475219727</v>
+        <v>58.95995712280273</v>
       </c>
       <c r="C195" t="n">
         <v>67.55000305175781</v>
@@ -5608,7 +5608,7 @@
         <v>44651</v>
       </c>
       <c r="B196" t="n">
-        <v>61.34278869628906</v>
+        <v>61.3427848815918</v>
       </c>
       <c r="C196" t="n">
         <v>70.27999877929688</v>
@@ -5666,7 +5666,7 @@
         <v>44712</v>
       </c>
       <c r="B198" t="n">
-        <v>59.25899505615234</v>
+        <v>59.25901031494141</v>
       </c>
       <c r="C198" t="n">
         <v>67.38999938964844</v>
@@ -5695,7 +5695,7 @@
         <v>44742</v>
       </c>
       <c r="B199" t="n">
-        <v>55.21401977539062</v>
+        <v>55.21401596069336</v>
       </c>
       <c r="C199" t="n">
         <v>62.79000091552734</v>
@@ -5724,7 +5724,7 @@
         <v>44773</v>
       </c>
       <c r="B200" t="n">
-        <v>55.61851119995117</v>
+        <v>55.61850738525391</v>
       </c>
       <c r="C200" t="n">
         <v>63.25</v>
@@ -5753,7 +5753,7 @@
         <v>44804</v>
       </c>
       <c r="B201" t="n">
-        <v>57.01858139038086</v>
+        <v>57.01859283447266</v>
       </c>
       <c r="C201" t="n">
         <v>64.33000183105469</v>
@@ -5840,7 +5840,7 @@
         <v>44895</v>
       </c>
       <c r="B204" t="n">
-        <v>68.44445037841797</v>
+        <v>68.44446563720703</v>
       </c>
       <c r="C204" t="n">
         <v>76.69999694824219</v>
@@ -5869,7 +5869,7 @@
         <v>44926</v>
       </c>
       <c r="B205" t="n">
-        <v>64.58049774169922</v>
+        <v>64.58052825927734</v>
       </c>
       <c r="C205" t="n">
         <v>72.37000274658203</v>
@@ -5927,7 +5927,7 @@
         <v>44985</v>
       </c>
       <c r="B207" t="n">
-        <v>64.47129821777344</v>
+        <v>64.47129058837891</v>
       </c>
       <c r="C207" t="n">
         <v>71.73000335693359</v>
@@ -5956,7 +5956,7 @@
         <v>45016</v>
       </c>
       <c r="B208" t="n">
-        <v>52.07676315307617</v>
+        <v>52.07676696777344</v>
       </c>
       <c r="C208" t="n">
         <v>57.93999862670898</v>
@@ -5985,7 +5985,7 @@
         <v>45046</v>
       </c>
       <c r="B209" t="n">
-        <v>55.12371444702148</v>
+        <v>55.12372207641602</v>
       </c>
       <c r="C209" t="n">
         <v>61.33000183105469</v>
@@ -6014,7 +6014,7 @@
         <v>45077</v>
       </c>
       <c r="B210" t="n">
-        <v>44.96355056762695</v>
+        <v>44.96354675292969</v>
       </c>
       <c r="C210" t="n">
         <v>49.54999923706055</v>
@@ -6043,7 +6043,7 @@
         <v>45107</v>
       </c>
       <c r="B211" t="n">
-        <v>51.29746627807617</v>
+        <v>51.29746246337891</v>
       </c>
       <c r="C211" t="n">
         <v>56.52999877929688</v>
@@ -6072,7 +6072,7 @@
         <v>45138</v>
       </c>
       <c r="B212" t="n">
-        <v>57.14137268066406</v>
+        <v>57.14136123657227</v>
       </c>
       <c r="C212" t="n">
         <v>62.97000122070312</v>
@@ -6101,7 +6101,7 @@
         <v>45169</v>
       </c>
       <c r="B213" t="n">
-        <v>57.95145416259766</v>
+        <v>57.95145797729492</v>
       </c>
       <c r="C213" t="n">
         <v>63.34000015258789</v>
@@ -6130,7 +6130,7 @@
         <v>45199</v>
       </c>
       <c r="B214" t="n">
-        <v>57.55804061889648</v>
+        <v>57.55803680419922</v>
       </c>
       <c r="C214" t="n">
         <v>62.90999984741211</v>
@@ -6159,7 +6159,7 @@
         <v>45230</v>
       </c>
       <c r="B215" t="n">
-        <v>54.90475082397461</v>
+        <v>54.90474700927734</v>
       </c>
       <c r="C215" t="n">
         <v>60.0099983215332</v>
@@ -6188,7 +6188,7 @@
         <v>45260</v>
       </c>
       <c r="B216" t="n">
-        <v>58.72531127929688</v>
+        <v>58.72531509399414</v>
       </c>
       <c r="C216" t="n">
         <v>63.63000106811523</v>
@@ -6217,7 +6217,7 @@
         <v>45291</v>
       </c>
       <c r="B217" t="n">
-        <v>61.03261566162109</v>
+        <v>61.03260803222656</v>
       </c>
       <c r="C217" t="n">
         <v>66.12999725341797</v>
@@ -6304,7 +6304,7 @@
         <v>45382</v>
       </c>
       <c r="B220" t="n">
-        <v>68.94107055664062</v>
+        <v>68.94107818603516</v>
       </c>
       <c r="C220" t="n">
         <v>74.11000061035156</v>
@@ -6362,7 +6362,7 @@
         <v>45443</v>
       </c>
       <c r="B222" t="n">
-        <v>67.84677886962891</v>
+        <v>67.84677124023438</v>
       </c>
       <c r="C222" t="n">
         <v>72.37000274658203</v>
@@ -6478,7 +6478,7 @@
         <v>45565</v>
       </c>
       <c r="B226" t="n">
-        <v>77.95001983642578</v>
+        <v>77.95001220703125</v>
       </c>
       <c r="C226" t="n">
         <v>82.48000335693359</v>
@@ -6507,7 +6507,7 @@
         <v>45596</v>
       </c>
       <c r="B227" t="n">
-        <v>74.11298370361328</v>
+        <v>74.11299896240234</v>
       </c>
       <c r="C227" t="n">
         <v>78.41999816894531</v>
@@ -6565,7 +6565,7 @@
         <v>45657</v>
       </c>
       <c r="B229" t="n">
-        <v>77.92353820800781</v>
+        <v>77.92354583740234</v>
       </c>
       <c r="C229" t="n">
         <v>81.87999725341797</v>
@@ -6594,7 +6594,7 @@
         <v>45688</v>
       </c>
       <c r="B230" t="n">
-        <v>82.32982635498047</v>
+        <v>82.329833984375</v>
       </c>
       <c r="C230" t="n">
         <v>86.51000213623047</v>
@@ -6623,7 +6623,7 @@
         <v>45716</v>
       </c>
       <c r="B231" t="n">
-        <v>82.54198455810547</v>
+        <v>82.54196929931641</v>
       </c>
       <c r="C231" t="n">
         <v>86.18000030517578</v>
@@ -6768,7 +6768,7 @@
         <v>45869</v>
       </c>
       <c r="B236" t="n">
-        <v>73.28153991699219</v>
+        <v>73.28152465820312</v>
       </c>
       <c r="C236" t="n">
         <v>75.94999694824219</v>
@@ -6797,7 +6797,7 @@
         <v>45900</v>
       </c>
       <c r="B237" t="n">
-        <v>79.10188293457031</v>
+        <v>79.10189056396484</v>
       </c>
       <c r="C237" t="n">
         <v>81.36000061035156</v>
@@ -6826,7 +6826,7 @@
         <v>45930</v>
       </c>
       <c r="B238" t="n">
-        <v>80.0838623046875</v>
+        <v>80.08385467529297</v>
       </c>
       <c r="C238" t="n">
         <v>82.37000274658203</v>
@@ -6942,7 +6942,7 @@
         <v>46053</v>
       </c>
       <c r="B242" t="n">
-        <v>77.24461364746094</v>
+        <v>77.24462127685547</v>
       </c>
       <c r="C242" t="n">
         <v>78.87999725341797</v>
